--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutoPartsCatalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Мой диск\AutoPartsCatalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="17580"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21270" windowHeight="13020"/>
   </bookViews>
   <sheets>
     <sheet name="Инвентаризация" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Да</t>
-  </si>
-  <si>
-    <t>Эталонная карточка</t>
   </si>
   <si>
     <t>Прибыль с единицы, ₸</t>
@@ -165,6 +162,21 @@
   </si>
   <si>
     <t>D3132H</t>
+  </si>
+  <si>
+    <t>ARMTEK</t>
+  </si>
+  <si>
+    <t>Эталонная карточка v1.2</t>
+  </si>
+  <si>
+    <t>Первая карточка проекта</t>
+  </si>
+  <si>
+    <t>D11173MH</t>
+  </si>
+  <si>
+    <t>Колодки тормозные передние</t>
   </si>
 </sst>
 </file>
@@ -531,7 +543,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>14</v>
@@ -591,13 +603,13 @@
       </c>
       <c r="O2" s="10"/>
       <c r="P2" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="8">
         <v>46236</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -605,10 +617,10 @@
         <v>46236</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>20</v>
@@ -625,30 +637,66 @@
       <c r="H3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="10"/>
+      <c r="I3" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="J3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="K3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="10">
+        <v>172843950</v>
+      </c>
       <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="10"/>
+      <c r="P3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>46236</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="8"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
+      <c r="A4" s="8">
+        <v>46236</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
@@ -10641,19 +10689,19 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>12</v>
@@ -10737,7 +10785,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="28.5">
       <c r="A3" s="10" t="str">
         <f>IF(Инвентаризация!C3="","",Инвентаризация!B3)</f>
         <v>MK KASHIYAMA</v>
@@ -10782,91 +10830,91 @@
         <f t="shared" si="4"/>
         <v>8000</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="10" t="str">
         <f>IF(Инвентаризация!C3="","",Инвентаризация!M3)</f>
-        <v>0</v>
+        <v>Да</v>
       </c>
       <c r="M3" s="10">
         <f>IF(Инвентаризация!C3="","",Инвентаризация!N3)</f>
-        <v>0</v>
+        <v>172843950</v>
       </c>
       <c r="N3" s="10">
         <f>IF(Инвентаризация!C3="","",Инвентаризация!O3)</f>
         <v>0</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="10" t="str">
         <f>IF(Инвентаризация!C3="","",Инвентаризация!P3)</f>
-        <v>0</v>
+        <v>ARMTEK</v>
       </c>
       <c r="P3" s="8">
         <f>IF(Инвентаризация!C3="","",Инвентаризация!Q3)</f>
-        <v>0</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="10" t="str">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!B4)</f>
-        <v/>
+        <v>MK KASHIYAMA</v>
       </c>
       <c r="B4" s="10" t="str">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!C4)</f>
-        <v/>
+        <v>D11173MH</v>
       </c>
       <c r="C4" s="5" t="str">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!D4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D4" s="11">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!E4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!F4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!G4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="12" t="str">
+        <v>12000</v>
+      </c>
+      <c r="G4" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H4" s="13" t="str">
+        <v>12000</v>
+      </c>
+      <c r="H4" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I4" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I4" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J4" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K4" s="12" t="str">
+        <v>12000</v>
+      </c>
+      <c r="K4" s="12">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L4" s="10" t="str">
+        <v>12000</v>
+      </c>
+      <c r="L4" s="10">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!M4)</f>
-        <v/>
-      </c>
-      <c r="M4" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!N4)</f>
-        <v/>
-      </c>
-      <c r="N4" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!O4)</f>
-        <v/>
-      </c>
-      <c r="O4" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!P4)</f>
-        <v/>
-      </c>
-      <c r="P4" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!Q4)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -43623,7 +43671,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -43631,13 +43679,13 @@
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>4</v>
@@ -43645,14 +43693,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <f>COUNTIF(Инвентаризация!E2:E500,0)</f>
@@ -43661,30 +43709,30 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!F2:F500)</f>
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <f>COUNTIF(Инвентаризация!K2:K500,"Нет")</f>
@@ -43693,14 +43741,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>22000</v>
+        <v>34000</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <f>COUNTIF(Инвентаризация!M2:M500,"Нет")</f>
@@ -43709,28 +43757,28 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>22000</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
       <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -43739,7 +43787,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -43748,7 +43796,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43757,7 +43805,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -43766,7 +43814,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -43775,7 +43823,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -43784,7 +43832,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -668,7 +668,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="8">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>45</v>
@@ -697,13 +697,21 @@
       <c r="J4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="10"/>
+      <c r="K4" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="M4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="10">
+        <v>172870174</v>
+      </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
-      <c r="Q4" s="8"/>
+      <c r="Q4" s="8">
+        <v>46236</v>
+      </c>
       <c r="R4" s="10"/>
     </row>
     <row r="5" spans="1:18">
@@ -10896,13 +10904,13 @@
         <f t="shared" si="4"/>
         <v>12000</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="10" t="str">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!M4)</f>
-        <v>0</v>
+        <v>Да</v>
       </c>
       <c r="M4" s="10">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!N4)</f>
-        <v>0</v>
+        <v>172870174</v>
       </c>
       <c r="N4" s="10">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!O4)</f>
@@ -10914,7 +10922,7 @@
       </c>
       <c r="P4" s="8">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!Q4)</f>
-        <v>0</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -43770,7 +43778,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -43814,7 +43822,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -43832,7 +43840,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>Колодки тормозные передние</t>
+  </si>
+  <si>
+    <t>D1231MH</t>
   </si>
 </sst>
 </file>
@@ -710,28 +713,58 @@
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="8">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="R4" s="10"/>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="8"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="A5" s="8">
+        <v>46237</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="M5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="10">
+        <v>172879327</v>
+      </c>
       <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="8"/>
+      <c r="P5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>46237</v>
+      </c>
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="1:18">
@@ -10859,7 +10892,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" ht="28.5">
       <c r="A4" s="10" t="str">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!B4)</f>
         <v>MK KASHIYAMA</v>
@@ -10922,73 +10955,73 @@
       </c>
       <c r="P4" s="8">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!Q4)</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="10" t="str">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!B5)</f>
-        <v/>
+        <v>MK KASHIYAMA</v>
       </c>
       <c r="B5" s="10" t="str">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!C5)</f>
-        <v/>
+        <v>D1231MH</v>
       </c>
       <c r="C5" s="5" t="str">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!D5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D5" s="11">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!E5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!F5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!G5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12" t="str">
+        <v>12000</v>
+      </c>
+      <c r="G5" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H5" s="13" t="str">
+        <v>12000</v>
+      </c>
+      <c r="H5" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I5" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J5" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K5" s="12" t="str">
+        <v>12000</v>
+      </c>
+      <c r="K5" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="L5" s="10" t="str">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!M5)</f>
-        <v/>
-      </c>
-      <c r="M5" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M5" s="10">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!N5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="10" t="str">
+        <v>172879327</v>
+      </c>
+      <c r="N5" s="10">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!O5)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O5" s="10" t="str">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!P5)</f>
-        <v/>
-      </c>
-      <c r="P5" s="8" t="str">
+        <v>ARMTEK</v>
+      </c>
+      <c r="P5" s="8">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!Q5)</f>
-        <v/>
+        <v>46237</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -43705,7 +43738,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43721,14 +43754,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43753,7 +43786,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>34000</v>
+        <v>46000</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -43769,7 +43802,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>34000</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -43778,7 +43811,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -43795,7 +43828,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -43804,7 +43837,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43813,7 +43846,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -43822,7 +43855,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -43840,7 +43873,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Склад" sheetId="2" r:id="rId2"/>
     <sheet name="Сводка" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>D1231MH</t>
+  </si>
+  <si>
+    <t>D11115MH</t>
   </si>
 </sst>
 </file>
@@ -683,7 +686,7 @@
         <v>51</v>
       </c>
       <c r="E4" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="7">
         <v>0</v>
@@ -703,7 +706,9 @@
       <c r="K4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="10"/>
+      <c r="L4" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="M4" s="10" t="s">
         <v>21</v>
       </c>
@@ -751,7 +756,9 @@
       <c r="K5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="10"/>
+      <c r="L5" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="M5" s="10" t="s">
         <v>21</v>
       </c>
@@ -768,23 +775,51 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="8"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="A6" s="8">
+        <v>46237</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
+      <c r="M6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="10">
+        <v>172886515</v>
+      </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="8">
+        <v>46237</v>
+      </c>
       <c r="R6" s="10"/>
     </row>
     <row r="7" spans="1:18">
@@ -10907,7 +10942,7 @@
       </c>
       <c r="D4" s="11">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!E4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="12">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!F4)</f>
@@ -10931,11 +10966,11 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="3"/>
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="4"/>
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>IF(Инвентаризация!C4="","",Инвентаризация!M4)</f>
@@ -10958,7 +10993,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="28.5">
       <c r="A5" s="10" t="str">
         <f>IF(Инвентаризация!C5="","",Инвентаризация!B5)</f>
         <v>MK KASHIYAMA</v>
@@ -11027,67 +11062,67 @@
     <row r="6" spans="1:16">
       <c r="A6" s="10" t="str">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!B6)</f>
-        <v/>
+        <v>MK KASHIYAMA</v>
       </c>
       <c r="B6" s="10" t="str">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!C6)</f>
-        <v/>
+        <v>D11115MH</v>
       </c>
       <c r="C6" s="5" t="str">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!D6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D6" s="11">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!E6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!F6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!G6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="12" t="str">
+        <v>11000</v>
+      </c>
+      <c r="G6" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H6" s="13" t="str">
+        <v>11000</v>
+      </c>
+      <c r="H6" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I6" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J6" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K6" s="12" t="str">
+        <v>11000</v>
+      </c>
+      <c r="K6" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>11000</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!M6)</f>
-        <v/>
-      </c>
-      <c r="M6" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M6" s="10">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!N6)</f>
-        <v/>
-      </c>
-      <c r="N6" s="10" t="str">
+        <v>172886515</v>
+      </c>
+      <c r="N6" s="10">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!O6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!P6)</f>
-        <v/>
-      </c>
-      <c r="P6" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!Q6)</f>
-        <v/>
+        <v>46237</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -43738,7 +43773,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43754,14 +43789,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43786,7 +43821,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>46000</v>
+        <v>69000</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -43802,7 +43837,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>46000</v>
+        <v>69000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -43811,7 +43846,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -43828,7 +43863,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -43837,7 +43872,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43846,7 +43881,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -43855,7 +43890,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -43864,7 +43899,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -43873,7 +43908,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="55">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>D11115MH</t>
+  </si>
+  <si>
+    <t>D6108H</t>
   </si>
 </sst>
 </file>
@@ -808,7 +811,9 @@
       <c r="K6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="10"/>
+      <c r="L6" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="M6" s="10" t="s">
         <v>21</v>
       </c>
@@ -823,23 +828,53 @@
       <c r="R6" s="10"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="8"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="A7" s="8">
+        <v>46237</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="M7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="10">
+        <v>172903965</v>
+      </c>
       <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="8"/>
+      <c r="P7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>46237</v>
+      </c>
       <c r="R7" s="10"/>
     </row>
     <row r="8" spans="1:18">
@@ -11059,7 +11094,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" ht="28.5">
       <c r="A6" s="10" t="str">
         <f>IF(Инвентаризация!C6="","",Инвентаризация!B6)</f>
         <v>MK KASHIYAMA</v>
@@ -11128,67 +11163,67 @@
     <row r="7" spans="1:16">
       <c r="A7" s="10" t="str">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!B7)</f>
-        <v/>
+        <v>MK KASHIYAMA</v>
       </c>
       <c r="B7" s="10" t="str">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!C7)</f>
-        <v/>
+        <v>D6108H</v>
       </c>
       <c r="C7" s="5" t="str">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!D7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D7" s="11">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!E7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!F7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!G7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12" t="str">
+        <v>6000</v>
+      </c>
+      <c r="G7" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H7" s="13" t="str">
+        <v>6000</v>
+      </c>
+      <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I7" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J7" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K7" s="12" t="str">
+        <v>6000</v>
+      </c>
+      <c r="K7" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!M7)</f>
-        <v/>
-      </c>
-      <c r="M7" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M7" s="10">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!N7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="10" t="str">
+        <v>172903965</v>
+      </c>
+      <c r="N7" s="10">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!O7)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O7" s="10" t="str">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!P7)</f>
-        <v/>
-      </c>
-      <c r="P7" s="8" t="str">
+        <v>ARMTEK</v>
+      </c>
+      <c r="P7" s="8">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!Q7)</f>
-        <v/>
+        <v>46237</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -43773,7 +43808,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43789,14 +43824,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43821,7 +43856,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>69000</v>
+        <v>75000</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -43837,7 +43872,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>69000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -43846,7 +43881,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -43863,7 +43898,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -43872,7 +43907,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43881,7 +43916,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -43890,7 +43925,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -43899,7 +43934,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -43908,7 +43943,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="56">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>D6108H</t>
+  </si>
+  <si>
+    <t>D2082MH</t>
   </si>
 </sst>
 </file>
@@ -878,23 +881,51 @@
       <c r="R7" s="10"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="8"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="A8" s="8">
+        <v>46238</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="M8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="10">
+        <v>172985889</v>
+      </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
-      <c r="Q8" s="8"/>
+      <c r="Q8" s="8">
+        <v>46238</v>
+      </c>
       <c r="R8" s="10"/>
     </row>
     <row r="9" spans="1:18">
@@ -11160,7 +11191,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" ht="28.5">
       <c r="A7" s="10" t="str">
         <f>IF(Инвентаризация!C7="","",Инвентаризация!B7)</f>
         <v>MK KASHIYAMA</v>
@@ -11226,70 +11257,70 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" ht="28.5">
       <c r="A8" s="10" t="str">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!B8)</f>
-        <v/>
+        <v>MK KASHIYAMA</v>
       </c>
       <c r="B8" s="10" t="str">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!C8)</f>
-        <v/>
+        <v>D2082MH</v>
       </c>
       <c r="C8" s="5" t="str">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!D8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D8" s="11">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!E8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!F8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!G8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="12" t="str">
+        <v>10000</v>
+      </c>
+      <c r="G8" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H8" s="13" t="str">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I8" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I8" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J8" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K8" s="12" t="str">
+        <v>10000</v>
+      </c>
+      <c r="K8" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!M8)</f>
-        <v/>
-      </c>
-      <c r="M8" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M8" s="10">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!N8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="10" t="str">
+        <v>172985889</v>
+      </c>
+      <c r="N8" s="10">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!O8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!P8)</f>
-        <v/>
-      </c>
-      <c r="P8" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
         <f>IF(Инвентаризация!C8="","",Инвентаризация!Q8)</f>
-        <v/>
+        <v>46238</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -43808,7 +43839,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43824,14 +43855,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43856,7 +43887,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>75000</v>
+        <v>85000</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -43872,7 +43903,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>75000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -43881,7 +43912,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -43898,7 +43929,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -43907,7 +43938,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43916,7 +43947,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -43925,7 +43956,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -43943,7 +43974,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -864,7 +864,9 @@
       <c r="K7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="10"/>
+      <c r="L7" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="M7" s="10" t="s">
         <v>21</v>
       </c>
@@ -914,7 +916,9 @@
       <c r="K8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="10"/>
+      <c r="L8" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="M8" s="10" t="s">
         <v>21</v>
       </c>
@@ -43965,7 +43969,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="58">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>D2082MH</t>
+  </si>
+  <si>
+    <t>K2333</t>
+  </si>
+  <si>
+    <t>Колодки тормозные задние  барабанные, комплект</t>
   </si>
 </sst>
 </file>
@@ -932,24 +938,54 @@
       </c>
       <c r="R8" s="10"/>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="8"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+    <row r="9" spans="1:18" ht="28.5">
+      <c r="A9" s="8">
+        <v>46239</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="10">
+        <v>172999972</v>
+      </c>
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
-      <c r="Q9" s="8"/>
+      <c r="Q9" s="8">
+        <v>46239</v>
+      </c>
       <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:18">
@@ -11327,70 +11363,70 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" ht="28.5">
       <c r="A9" s="10" t="str">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!B9)</f>
-        <v/>
+        <v>MK KASHIYAMA</v>
       </c>
       <c r="B9" s="10" t="str">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!C9)</f>
-        <v/>
+        <v>K2333</v>
       </c>
       <c r="C9" s="5" t="str">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!D9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="11" t="str">
+        <v>Колодки тормозные задние  барабанные, комплект</v>
+      </c>
+      <c r="D9" s="11">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!E9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!F9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!G9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="str">
+        <v>12000</v>
+      </c>
+      <c r="G9" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H9" s="13" t="str">
+        <v>12000</v>
+      </c>
+      <c r="H9" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I9" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J9" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K9" s="12" t="str">
+        <v>12000</v>
+      </c>
+      <c r="K9" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!M9)</f>
-        <v/>
-      </c>
-      <c r="M9" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M9" s="10">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!N9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="10" t="str">
+        <v>172999972</v>
+      </c>
+      <c r="N9" s="10">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!O9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!P9)</f>
-        <v/>
-      </c>
-      <c r="P9" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
         <f>IF(Инвентаризация!C9="","",Инвентаризация!Q9)</f>
-        <v/>
+        <v>46239</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -43843,7 +43879,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43859,14 +43895,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43891,7 +43927,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>85000</v>
+        <v>97000</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -43907,7 +43943,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>85000</v>
+        <v>97000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -43916,7 +43952,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -43933,7 +43969,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -43942,7 +43978,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43951,7 +43987,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -43960,7 +43996,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -43969,7 +44005,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -43978,7 +44014,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="60">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>Колодки тормозные задние  барабанные, комплект</t>
+  </si>
+  <si>
+    <t>HYUNDAI/KIA</t>
+  </si>
+  <si>
+    <t>583052WA00</t>
   </si>
 </sst>
 </file>
@@ -988,24 +994,54 @@
       </c>
       <c r="R9" s="10"/>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="8"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+    <row r="10" spans="1:18" ht="28.5">
+      <c r="A10" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>16000</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="10">
+        <v>173035824</v>
+      </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
-      <c r="Q10" s="8"/>
+      <c r="Q10" s="8">
+        <v>46239</v>
+      </c>
       <c r="R10" s="10"/>
     </row>
     <row r="11" spans="1:18">
@@ -11432,67 +11468,67 @@
     <row r="10" spans="1:16">
       <c r="A10" s="10" t="str">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!B10)</f>
-        <v/>
+        <v>HYUNDAI/KIA</v>
       </c>
       <c r="B10" s="10" t="str">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!C10)</f>
-        <v/>
+        <v>583052WA00</v>
       </c>
       <c r="C10" s="5" t="str">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!D10)</f>
-        <v/>
-      </c>
-      <c r="D10" s="11" t="str">
+        <v>Колодки тормозные задние  барабанные, комплект</v>
+      </c>
+      <c r="D10" s="11">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!E10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!F10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!G10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="12" t="str">
+        <v>16000</v>
+      </c>
+      <c r="G10" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H10" s="13" t="str">
+        <v>16000</v>
+      </c>
+      <c r="H10" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I10" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I10" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J10" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J10" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K10" s="12" t="str">
+        <v>16000</v>
+      </c>
+      <c r="K10" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>16000</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!M10)</f>
-        <v/>
-      </c>
-      <c r="M10" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M10" s="10">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!N10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="10" t="str">
+        <v>173035824</v>
+      </c>
+      <c r="N10" s="10">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!O10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O10" s="10">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!P10)</f>
-        <v/>
-      </c>
-      <c r="P10" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!Q10)</f>
-        <v/>
+        <v>46239</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -43879,7 +43915,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43895,14 +43931,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43927,7 +43963,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>97000</v>
+        <v>113000</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -43943,7 +43979,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>97000</v>
+        <v>113000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -43952,7 +43988,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -43969,7 +44005,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -43978,7 +44014,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43987,7 +44023,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -43996,7 +44032,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44005,7 +44041,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44014,7 +44050,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="62">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>583052WA00</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Колодки тормозные задние  барабанные ручного тормоза, комплект, </t>
   </si>
 </sst>
 </file>
@@ -1044,24 +1050,54 @@
       </c>
       <c r="R10" s="10"/>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="8"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+    <row r="11" spans="1:18" ht="42.75">
+      <c r="A11" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="10">
+        <v>9116</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>6800</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="10">
+        <v>173040235</v>
+      </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
-      <c r="Q11" s="8"/>
+      <c r="Q11" s="8">
+        <v>46239</v>
+      </c>
       <c r="R11" s="10"/>
     </row>
     <row r="12" spans="1:18">
@@ -11465,7 +11501,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" ht="28.5">
       <c r="A10" s="10" t="str">
         <f>IF(Инвентаризация!C10="","",Инвентаризация!B10)</f>
         <v>HYUNDAI/KIA</v>
@@ -11534,67 +11570,67 @@
     <row r="11" spans="1:16">
       <c r="A11" s="10" t="str">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!B11)</f>
-        <v/>
-      </c>
-      <c r="B11" s="10" t="str">
+        <v>ABS</v>
+      </c>
+      <c r="B11" s="10">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!C11)</f>
-        <v/>
+        <v>9116</v>
       </c>
       <c r="C11" s="5" t="str">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!D11)</f>
-        <v/>
-      </c>
-      <c r="D11" s="11" t="str">
+        <v xml:space="preserve">Колодки тормозные задние  барабанные ручного тормоза, комплект, </v>
+      </c>
+      <c r="D11" s="11">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!E11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!F11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!G11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="12" t="str">
+        <v>6800</v>
+      </c>
+      <c r="G11" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H11" s="13" t="str">
+        <v>6800</v>
+      </c>
+      <c r="H11" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I11" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J11" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J11" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K11" s="12" t="str">
+        <v>6800</v>
+      </c>
+      <c r="K11" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>6800</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!M11)</f>
-        <v/>
-      </c>
-      <c r="M11" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M11" s="10">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!N11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="10" t="str">
+        <v>173040235</v>
+      </c>
+      <c r="N11" s="10">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!O11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!P11)</f>
-        <v/>
-      </c>
-      <c r="P11" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!Q11)</f>
-        <v/>
+        <v>46239</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -43915,7 +43951,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43931,14 +43967,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43963,7 +43999,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>113000</v>
+        <v>119800</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -43979,7 +44015,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>113000</v>
+        <v>119800</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -43988,7 +44024,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -44005,7 +44041,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -44014,7 +44050,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -44023,7 +44059,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -44032,7 +44068,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44041,7 +44077,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44050,7 +44086,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="64">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t xml:space="preserve">Колодки тормозные задние  барабанные ручного тормоза, комплект, </t>
+  </si>
+  <si>
+    <t>PATRON</t>
+  </si>
+  <si>
+    <t>PSP284</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1008,7 @@
     </row>
     <row r="10" spans="1:18" ht="28.5">
       <c r="A10" s="8">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>58</v>
@@ -1052,7 +1058,7 @@
     </row>
     <row r="11" spans="1:18" ht="42.75">
       <c r="A11" s="8">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>60</v>
@@ -1100,24 +1106,54 @@
       </c>
       <c r="R11" s="10"/>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="8"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+    <row r="12" spans="1:18" ht="28.5">
+      <c r="A12" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="10">
+        <v>173088211</v>
+      </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
-      <c r="Q12" s="8"/>
+      <c r="Q12" s="8">
+        <v>46240</v>
+      </c>
       <c r="R12" s="10"/>
     </row>
     <row r="13" spans="1:18">
@@ -10902,6 +10938,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11567,7 +11604,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" ht="42.75">
       <c r="A11" s="10" t="str">
         <f>IF(Инвентаризация!C11="","",Инвентаризация!B11)</f>
         <v>ABS</v>
@@ -11636,67 +11673,67 @@
     <row r="12" spans="1:16">
       <c r="A12" s="10" t="str">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!B12)</f>
-        <v/>
+        <v>PATRON</v>
       </c>
       <c r="B12" s="10" t="str">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!C12)</f>
-        <v/>
+        <v>PSP284</v>
       </c>
       <c r="C12" s="5" t="str">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!D12)</f>
-        <v/>
-      </c>
-      <c r="D12" s="11" t="str">
+        <v>Колодки тормозные задние  барабанные, комплект</v>
+      </c>
+      <c r="D12" s="11">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!E12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!F12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!G12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="12" t="str">
+        <v>9000</v>
+      </c>
+      <c r="G12" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H12" s="13" t="str">
+        <v>9000</v>
+      </c>
+      <c r="H12" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I12" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I12" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J12" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K12" s="12" t="str">
+        <v>9000</v>
+      </c>
+      <c r="K12" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!M12)</f>
-        <v/>
-      </c>
-      <c r="M12" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M12" s="10">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!N12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="10" t="str">
+        <v>173088211</v>
+      </c>
+      <c r="N12" s="10">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!O12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O12" s="10">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!P12)</f>
-        <v/>
-      </c>
-      <c r="P12" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!Q12)</f>
-        <v/>
+        <v>46240</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -43951,7 +43988,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -43967,14 +44004,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -43999,7 +44036,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>119800</v>
+        <v>128800</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -44015,7 +44052,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>119800</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -44024,7 +44061,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -44041,7 +44078,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -44050,7 +44087,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -44059,7 +44096,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -44068,7 +44105,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44077,7 +44114,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44086,7 +44123,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="66">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>PSP284</t>
+  </si>
+  <si>
+    <t>AKEBONO</t>
+  </si>
+  <si>
+    <t>AN691WK</t>
   </si>
 </sst>
 </file>
@@ -1157,23 +1163,53 @@
       <c r="R12" s="10"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="8"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
+      <c r="A13" s="8">
+        <v>46241</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="10">
+        <v>173135153</v>
+      </c>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="8"/>
+      <c r="Q13" s="8">
+        <v>46241</v>
+      </c>
       <c r="R13" s="10"/>
     </row>
     <row r="14" spans="1:18">
@@ -11670,7 +11706,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" ht="28.5">
       <c r="A12" s="10" t="str">
         <f>IF(Инвентаризация!C12="","",Инвентаризация!B12)</f>
         <v>PATRON</v>
@@ -11739,67 +11775,67 @@
     <row r="13" spans="1:16">
       <c r="A13" s="10" t="str">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!B13)</f>
-        <v/>
+        <v>AKEBONO</v>
       </c>
       <c r="B13" s="10" t="str">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!C13)</f>
-        <v/>
+        <v>AN691WK</v>
       </c>
       <c r="C13" s="5" t="str">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!D13)</f>
-        <v/>
-      </c>
-      <c r="D13" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D13" s="11">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!E13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!F13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!G13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="12" t="str">
+        <v>9000</v>
+      </c>
+      <c r="G13" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H13" s="13" t="str">
+        <v>9000</v>
+      </c>
+      <c r="H13" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I13" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I13" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J13" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K13" s="12" t="str">
+        <v>9000</v>
+      </c>
+      <c r="K13" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="L13" s="10" t="str">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!M13)</f>
-        <v/>
-      </c>
-      <c r="M13" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M13" s="10">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!N13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="10" t="str">
+        <v>173135153</v>
+      </c>
+      <c r="N13" s="10">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!O13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!P13)</f>
-        <v/>
-      </c>
-      <c r="P13" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
         <f>IF(Инвентаризация!C13="","",Инвентаризация!Q13)</f>
-        <v/>
+        <v>46241</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -43988,7 +44024,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -44004,14 +44040,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -44036,7 +44072,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>128800</v>
+        <v>137800</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -44052,7 +44088,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>128800</v>
+        <v>137800</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -44061,7 +44097,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -44078,7 +44114,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -44087,7 +44123,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -44096,7 +44132,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -44105,7 +44141,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44114,7 +44150,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44123,7 +44159,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="67">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>AN691WK</t>
+  </si>
+  <si>
+    <t>TEXTAR</t>
   </si>
 </sst>
 </file>
@@ -1213,23 +1216,53 @@
       <c r="R13" s="10"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="8"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
+      <c r="A14" s="8">
+        <v>46241</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="10">
+        <v>2176603</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="10">
+        <v>173197265</v>
+      </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
-      <c r="Q14" s="8"/>
+      <c r="Q14" s="8">
+        <v>46242</v>
+      </c>
       <c r="R14" s="10"/>
     </row>
     <row r="15" spans="1:18">
@@ -11841,67 +11874,67 @@
     <row r="14" spans="1:16">
       <c r="A14" s="10" t="str">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!B14)</f>
-        <v/>
-      </c>
-      <c r="B14" s="10" t="str">
+        <v>TEXTAR</v>
+      </c>
+      <c r="B14" s="10">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!C14)</f>
-        <v/>
+        <v>2176603</v>
       </c>
       <c r="C14" s="5" t="str">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!D14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="11" t="str">
+        <v>Колодки тормозные задние</v>
+      </c>
+      <c r="D14" s="11">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!E14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!F14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!G14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="12" t="str">
+        <v>7000</v>
+      </c>
+      <c r="G14" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H14" s="13" t="str">
+        <v>7000</v>
+      </c>
+      <c r="H14" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I14" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I14" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J14" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K14" s="12" t="str">
+        <v>7000</v>
+      </c>
+      <c r="K14" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="L14" s="10" t="str">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!M14)</f>
-        <v/>
-      </c>
-      <c r="M14" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M14" s="10">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!N14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="10" t="str">
+        <v>173197265</v>
+      </c>
+      <c r="N14" s="10">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!O14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O14" s="10">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!P14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
         <f>IF(Инвентаризация!C14="","",Инвентаризация!Q14)</f>
-        <v/>
+        <v>46242</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -44024,7 +44057,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -44040,14 +44073,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -44072,7 +44105,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>137800</v>
+        <v>144800</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -44088,7 +44121,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>137800</v>
+        <v>144800</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -44097,7 +44130,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -44114,7 +44147,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -44123,7 +44156,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -44132,7 +44165,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -44141,7 +44174,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44150,7 +44183,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44159,7 +44192,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="68">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>TEXTAR</t>
+  </si>
+  <si>
+    <t>ROADHOUSE</t>
   </si>
 </sst>
 </file>
@@ -1266,23 +1269,53 @@
       <c r="R14" s="10"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="8"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
+      <c r="A15" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="10">
+        <v>228220</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="10">
+        <v>173199833</v>
+      </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
-      <c r="Q15" s="8"/>
+      <c r="Q15" s="8">
+        <v>46242</v>
+      </c>
       <c r="R15" s="10"/>
     </row>
     <row r="16" spans="1:18">
@@ -11940,67 +11973,67 @@
     <row r="15" spans="1:16">
       <c r="A15" s="10" t="str">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!B15)</f>
-        <v/>
-      </c>
-      <c r="B15" s="10" t="str">
+        <v>ROADHOUSE</v>
+      </c>
+      <c r="B15" s="10">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!C15)</f>
-        <v/>
+        <v>228220</v>
       </c>
       <c r="C15" s="5" t="str">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!D15)</f>
-        <v/>
-      </c>
-      <c r="D15" s="11" t="str">
+        <v>Колодки тормозные задние</v>
+      </c>
+      <c r="D15" s="11">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!E15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!F15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!G15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="12" t="str">
+        <v>7000</v>
+      </c>
+      <c r="G15" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H15" s="13" t="str">
+        <v>7000</v>
+      </c>
+      <c r="H15" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I15" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I15" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J15" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K15" s="12" t="str">
+        <v>7000</v>
+      </c>
+      <c r="K15" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="L15" s="10" t="str">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!M15)</f>
-        <v/>
-      </c>
-      <c r="M15" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M15" s="10">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!N15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="10" t="str">
+        <v>173199833</v>
+      </c>
+      <c r="N15" s="10">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!O15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!P15)</f>
-        <v/>
-      </c>
-      <c r="P15" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
         <f>IF(Инвентаризация!C15="","",Инвентаризация!Q15)</f>
-        <v/>
+        <v>46242</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -44057,7 +44090,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -44073,14 +44106,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -44105,7 +44138,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>144800</v>
+        <v>151800</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -44121,7 +44154,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>144800</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -44130,7 +44163,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -44147,7 +44180,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -44156,7 +44189,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -44165,7 +44198,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -44174,7 +44207,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44183,7 +44216,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44192,7 +44225,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="70">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -226,6 +226,12 @@
   <si>
     <t>ROADHOUSE</t>
   </si>
+  <si>
+    <t>REMSA</t>
+  </si>
+  <si>
+    <t>014132</t>
+  </si>
 </sst>
 </file>
 
@@ -325,7 +331,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -366,6 +372,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -539,7 +554,7 @@
   <cols>
     <col min="1" max="1" width="15" style="9" customWidth="1"/>
     <col min="2" max="2" width="16.25" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16" style="17" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="7" width="18" customWidth="1"/>
@@ -557,7 +572,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -613,7 +628,7 @@
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -667,7 +682,7 @@
       <c r="B3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -721,7 +736,7 @@
       <c r="B4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="16" t="s">
         <v>50</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -771,7 +786,7 @@
       <c r="B5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="16" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -823,7 +838,7 @@
       <c r="B6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="16" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -873,7 +888,7 @@
       <c r="B7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -925,7 +940,7 @@
       <c r="B8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="16" t="s">
         <v>55</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -975,7 +990,7 @@
       <c r="B9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="16" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1025,7 +1040,7 @@
       <c r="B10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="16" t="s">
         <v>59</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1075,7 +1090,7 @@
       <c r="B11" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="16">
         <v>9116</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1125,7 +1140,7 @@
       <c r="B12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1175,7 +1190,7 @@
       <c r="B13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="16" t="s">
         <v>65</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1225,7 +1240,7 @@
       <c r="B14" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="16">
         <v>2176603</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -1275,7 +1290,7 @@
       <c r="B15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="16">
         <v>228220</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -1319,29 +1334,57 @@
       <c r="R15" s="10"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="8"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="A16" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
-      <c r="Q16" s="8"/>
+      <c r="Q16" s="8">
+        <v>46242</v>
+      </c>
       <c r="R16" s="10"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="8"/>
       <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
+      <c r="C17" s="16"/>
       <c r="D17" s="5"/>
       <c r="E17" s="6"/>
       <c r="F17" s="7"/>
@@ -1361,7 +1404,7 @@
     <row r="18" spans="1:18">
       <c r="A18" s="8"/>
       <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="5"/>
       <c r="E18" s="6"/>
       <c r="F18" s="7"/>
@@ -1381,7 +1424,7 @@
     <row r="19" spans="1:18">
       <c r="A19" s="8"/>
       <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="C19" s="16"/>
       <c r="D19" s="5"/>
       <c r="E19" s="6"/>
       <c r="F19" s="7"/>
@@ -1401,7 +1444,7 @@
     <row r="20" spans="1:18">
       <c r="A20" s="8"/>
       <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
+      <c r="C20" s="16"/>
       <c r="D20" s="5"/>
       <c r="E20" s="6"/>
       <c r="F20" s="7"/>
@@ -1421,7 +1464,7 @@
     <row r="21" spans="1:18">
       <c r="A21" s="8"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
+      <c r="C21" s="16"/>
       <c r="D21" s="5"/>
       <c r="E21" s="6"/>
       <c r="F21" s="7"/>
@@ -1441,7 +1484,7 @@
     <row r="22" spans="1:18">
       <c r="A22" s="8"/>
       <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="5"/>
       <c r="E22" s="6"/>
       <c r="F22" s="7"/>
@@ -1461,7 +1504,7 @@
     <row r="23" spans="1:18">
       <c r="A23" s="8"/>
       <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
+      <c r="C23" s="16"/>
       <c r="D23" s="5"/>
       <c r="E23" s="6"/>
       <c r="F23" s="7"/>
@@ -1481,7 +1524,7 @@
     <row r="24" spans="1:18">
       <c r="A24" s="8"/>
       <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
+      <c r="C24" s="16"/>
       <c r="D24" s="5"/>
       <c r="E24" s="6"/>
       <c r="F24" s="7"/>
@@ -1501,7 +1544,7 @@
     <row r="25" spans="1:18">
       <c r="A25" s="8"/>
       <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+      <c r="C25" s="16"/>
       <c r="D25" s="5"/>
       <c r="E25" s="6"/>
       <c r="F25" s="7"/>
@@ -1521,7 +1564,7 @@
     <row r="26" spans="1:18">
       <c r="A26" s="8"/>
       <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="C26" s="16"/>
       <c r="D26" s="5"/>
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
@@ -1541,7 +1584,7 @@
     <row r="27" spans="1:18">
       <c r="A27" s="8"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
+      <c r="C27" s="16"/>
       <c r="D27" s="5"/>
       <c r="E27" s="6"/>
       <c r="F27" s="7"/>
@@ -1561,7 +1604,7 @@
     <row r="28" spans="1:18">
       <c r="A28" s="8"/>
       <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="C28" s="16"/>
       <c r="D28" s="5"/>
       <c r="E28" s="6"/>
       <c r="F28" s="7"/>
@@ -1581,7 +1624,7 @@
     <row r="29" spans="1:18">
       <c r="A29" s="8"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="C29" s="16"/>
       <c r="D29" s="5"/>
       <c r="E29" s="6"/>
       <c r="F29" s="7"/>
@@ -1601,7 +1644,7 @@
     <row r="30" spans="1:18">
       <c r="A30" s="8"/>
       <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
+      <c r="C30" s="16"/>
       <c r="D30" s="5"/>
       <c r="E30" s="6"/>
       <c r="F30" s="7"/>
@@ -1621,7 +1664,7 @@
     <row r="31" spans="1:18">
       <c r="A31" s="8"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="C31" s="16"/>
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
       <c r="F31" s="7"/>
@@ -1641,7 +1684,7 @@
     <row r="32" spans="1:18">
       <c r="A32" s="8"/>
       <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="C32" s="16"/>
       <c r="D32" s="5"/>
       <c r="E32" s="6"/>
       <c r="F32" s="7"/>
@@ -1661,7 +1704,7 @@
     <row r="33" spans="1:18">
       <c r="A33" s="8"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="C33" s="16"/>
       <c r="D33" s="5"/>
       <c r="E33" s="6"/>
       <c r="F33" s="7"/>
@@ -1681,7 +1724,7 @@
     <row r="34" spans="1:18">
       <c r="A34" s="8"/>
       <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="C34" s="16"/>
       <c r="D34" s="5"/>
       <c r="E34" s="6"/>
       <c r="F34" s="7"/>
@@ -1701,7 +1744,7 @@
     <row r="35" spans="1:18">
       <c r="A35" s="8"/>
       <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="C35" s="16"/>
       <c r="D35" s="5"/>
       <c r="E35" s="6"/>
       <c r="F35" s="7"/>
@@ -1721,7 +1764,7 @@
     <row r="36" spans="1:18">
       <c r="A36" s="8"/>
       <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
+      <c r="C36" s="16"/>
       <c r="D36" s="5"/>
       <c r="E36" s="6"/>
       <c r="F36" s="7"/>
@@ -1741,7 +1784,7 @@
     <row r="37" spans="1:18">
       <c r="A37" s="8"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
+      <c r="C37" s="16"/>
       <c r="D37" s="5"/>
       <c r="E37" s="6"/>
       <c r="F37" s="7"/>
@@ -1761,7 +1804,7 @@
     <row r="38" spans="1:18">
       <c r="A38" s="8"/>
       <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
+      <c r="C38" s="16"/>
       <c r="D38" s="5"/>
       <c r="E38" s="6"/>
       <c r="F38" s="7"/>
@@ -1781,7 +1824,7 @@
     <row r="39" spans="1:18">
       <c r="A39" s="8"/>
       <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
+      <c r="C39" s="16"/>
       <c r="D39" s="5"/>
       <c r="E39" s="6"/>
       <c r="F39" s="7"/>
@@ -1801,7 +1844,7 @@
     <row r="40" spans="1:18">
       <c r="A40" s="8"/>
       <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
+      <c r="C40" s="16"/>
       <c r="D40" s="5"/>
       <c r="E40" s="6"/>
       <c r="F40" s="7"/>
@@ -1821,7 +1864,7 @@
     <row r="41" spans="1:18">
       <c r="A41" s="8"/>
       <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
+      <c r="C41" s="16"/>
       <c r="D41" s="5"/>
       <c r="E41" s="6"/>
       <c r="F41" s="7"/>
@@ -1841,7 +1884,7 @@
     <row r="42" spans="1:18">
       <c r="A42" s="8"/>
       <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
+      <c r="C42" s="16"/>
       <c r="D42" s="5"/>
       <c r="E42" s="6"/>
       <c r="F42" s="7"/>
@@ -1861,7 +1904,7 @@
     <row r="43" spans="1:18">
       <c r="A43" s="8"/>
       <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
+      <c r="C43" s="16"/>
       <c r="D43" s="5"/>
       <c r="E43" s="6"/>
       <c r="F43" s="7"/>
@@ -1881,7 +1924,7 @@
     <row r="44" spans="1:18">
       <c r="A44" s="8"/>
       <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
+      <c r="C44" s="16"/>
       <c r="D44" s="5"/>
       <c r="E44" s="6"/>
       <c r="F44" s="7"/>
@@ -1901,7 +1944,7 @@
     <row r="45" spans="1:18">
       <c r="A45" s="8"/>
       <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
+      <c r="C45" s="16"/>
       <c r="D45" s="5"/>
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
@@ -1921,7 +1964,7 @@
     <row r="46" spans="1:18">
       <c r="A46" s="8"/>
       <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
+      <c r="C46" s="16"/>
       <c r="D46" s="5"/>
       <c r="E46" s="6"/>
       <c r="F46" s="7"/>
@@ -1941,7 +1984,7 @@
     <row r="47" spans="1:18">
       <c r="A47" s="8"/>
       <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
+      <c r="C47" s="16"/>
       <c r="D47" s="5"/>
       <c r="E47" s="6"/>
       <c r="F47" s="7"/>
@@ -1961,7 +2004,7 @@
     <row r="48" spans="1:18">
       <c r="A48" s="8"/>
       <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
+      <c r="C48" s="16"/>
       <c r="D48" s="5"/>
       <c r="E48" s="6"/>
       <c r="F48" s="7"/>
@@ -1981,7 +2024,7 @@
     <row r="49" spans="1:18">
       <c r="A49" s="8"/>
       <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
+      <c r="C49" s="16"/>
       <c r="D49" s="5"/>
       <c r="E49" s="6"/>
       <c r="F49" s="7"/>
@@ -2001,7 +2044,7 @@
     <row r="50" spans="1:18">
       <c r="A50" s="8"/>
       <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
+      <c r="C50" s="16"/>
       <c r="D50" s="5"/>
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
@@ -2021,7 +2064,7 @@
     <row r="51" spans="1:18">
       <c r="A51" s="8"/>
       <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
+      <c r="C51" s="16"/>
       <c r="D51" s="5"/>
       <c r="E51" s="6"/>
       <c r="F51" s="7"/>
@@ -2041,7 +2084,7 @@
     <row r="52" spans="1:18">
       <c r="A52" s="8"/>
       <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
+      <c r="C52" s="16"/>
       <c r="D52" s="5"/>
       <c r="E52" s="6"/>
       <c r="F52" s="7"/>
@@ -2061,7 +2104,7 @@
     <row r="53" spans="1:18">
       <c r="A53" s="8"/>
       <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
+      <c r="C53" s="16"/>
       <c r="D53" s="5"/>
       <c r="E53" s="6"/>
       <c r="F53" s="7"/>
@@ -2081,7 +2124,7 @@
     <row r="54" spans="1:18">
       <c r="A54" s="8"/>
       <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
+      <c r="C54" s="16"/>
       <c r="D54" s="5"/>
       <c r="E54" s="6"/>
       <c r="F54" s="7"/>
@@ -2101,7 +2144,7 @@
     <row r="55" spans="1:18">
       <c r="A55" s="8"/>
       <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
+      <c r="C55" s="16"/>
       <c r="D55" s="5"/>
       <c r="E55" s="6"/>
       <c r="F55" s="7"/>
@@ -2121,7 +2164,7 @@
     <row r="56" spans="1:18">
       <c r="A56" s="8"/>
       <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
+      <c r="C56" s="16"/>
       <c r="D56" s="5"/>
       <c r="E56" s="6"/>
       <c r="F56" s="7"/>
@@ -2141,7 +2184,7 @@
     <row r="57" spans="1:18">
       <c r="A57" s="8"/>
       <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
+      <c r="C57" s="16"/>
       <c r="D57" s="5"/>
       <c r="E57" s="6"/>
       <c r="F57" s="7"/>
@@ -2161,7 +2204,7 @@
     <row r="58" spans="1:18">
       <c r="A58" s="8"/>
       <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
+      <c r="C58" s="16"/>
       <c r="D58" s="5"/>
       <c r="E58" s="6"/>
       <c r="F58" s="7"/>
@@ -2181,7 +2224,7 @@
     <row r="59" spans="1:18">
       <c r="A59" s="8"/>
       <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
+      <c r="C59" s="16"/>
       <c r="D59" s="5"/>
       <c r="E59" s="6"/>
       <c r="F59" s="7"/>
@@ -2201,7 +2244,7 @@
     <row r="60" spans="1:18">
       <c r="A60" s="8"/>
       <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
+      <c r="C60" s="16"/>
       <c r="D60" s="5"/>
       <c r="E60" s="6"/>
       <c r="F60" s="7"/>
@@ -2221,7 +2264,7 @@
     <row r="61" spans="1:18">
       <c r="A61" s="8"/>
       <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
+      <c r="C61" s="16"/>
       <c r="D61" s="5"/>
       <c r="E61" s="6"/>
       <c r="F61" s="7"/>
@@ -2241,7 +2284,7 @@
     <row r="62" spans="1:18">
       <c r="A62" s="8"/>
       <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
+      <c r="C62" s="16"/>
       <c r="D62" s="5"/>
       <c r="E62" s="6"/>
       <c r="F62" s="7"/>
@@ -2261,7 +2304,7 @@
     <row r="63" spans="1:18">
       <c r="A63" s="8"/>
       <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
+      <c r="C63" s="16"/>
       <c r="D63" s="5"/>
       <c r="E63" s="6"/>
       <c r="F63" s="7"/>
@@ -2281,7 +2324,7 @@
     <row r="64" spans="1:18">
       <c r="A64" s="8"/>
       <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
+      <c r="C64" s="16"/>
       <c r="D64" s="5"/>
       <c r="E64" s="6"/>
       <c r="F64" s="7"/>
@@ -2301,7 +2344,7 @@
     <row r="65" spans="1:18">
       <c r="A65" s="8"/>
       <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
+      <c r="C65" s="16"/>
       <c r="D65" s="5"/>
       <c r="E65" s="6"/>
       <c r="F65" s="7"/>
@@ -2321,7 +2364,7 @@
     <row r="66" spans="1:18">
       <c r="A66" s="8"/>
       <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
+      <c r="C66" s="16"/>
       <c r="D66" s="5"/>
       <c r="E66" s="6"/>
       <c r="F66" s="7"/>
@@ -2341,7 +2384,7 @@
     <row r="67" spans="1:18">
       <c r="A67" s="8"/>
       <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
+      <c r="C67" s="16"/>
       <c r="D67" s="5"/>
       <c r="E67" s="6"/>
       <c r="F67" s="7"/>
@@ -2361,7 +2404,7 @@
     <row r="68" spans="1:18">
       <c r="A68" s="8"/>
       <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
+      <c r="C68" s="16"/>
       <c r="D68" s="5"/>
       <c r="E68" s="6"/>
       <c r="F68" s="7"/>
@@ -2381,7 +2424,7 @@
     <row r="69" spans="1:18">
       <c r="A69" s="8"/>
       <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
+      <c r="C69" s="16"/>
       <c r="D69" s="5"/>
       <c r="E69" s="6"/>
       <c r="F69" s="7"/>
@@ -2401,7 +2444,7 @@
     <row r="70" spans="1:18">
       <c r="A70" s="8"/>
       <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
+      <c r="C70" s="16"/>
       <c r="D70" s="5"/>
       <c r="E70" s="6"/>
       <c r="F70" s="7"/>
@@ -2421,7 +2464,7 @@
     <row r="71" spans="1:18">
       <c r="A71" s="8"/>
       <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
+      <c r="C71" s="16"/>
       <c r="D71" s="5"/>
       <c r="E71" s="6"/>
       <c r="F71" s="7"/>
@@ -2441,7 +2484,7 @@
     <row r="72" spans="1:18">
       <c r="A72" s="8"/>
       <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
+      <c r="C72" s="16"/>
       <c r="D72" s="5"/>
       <c r="E72" s="6"/>
       <c r="F72" s="7"/>
@@ -2461,7 +2504,7 @@
     <row r="73" spans="1:18">
       <c r="A73" s="8"/>
       <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
+      <c r="C73" s="16"/>
       <c r="D73" s="5"/>
       <c r="E73" s="6"/>
       <c r="F73" s="7"/>
@@ -2481,7 +2524,7 @@
     <row r="74" spans="1:18">
       <c r="A74" s="8"/>
       <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
+      <c r="C74" s="16"/>
       <c r="D74" s="5"/>
       <c r="E74" s="6"/>
       <c r="F74" s="7"/>
@@ -2501,7 +2544,7 @@
     <row r="75" spans="1:18">
       <c r="A75" s="8"/>
       <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
+      <c r="C75" s="16"/>
       <c r="D75" s="5"/>
       <c r="E75" s="6"/>
       <c r="F75" s="7"/>
@@ -2521,7 +2564,7 @@
     <row r="76" spans="1:18">
       <c r="A76" s="8"/>
       <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
+      <c r="C76" s="16"/>
       <c r="D76" s="5"/>
       <c r="E76" s="6"/>
       <c r="F76" s="7"/>
@@ -2541,7 +2584,7 @@
     <row r="77" spans="1:18">
       <c r="A77" s="8"/>
       <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
+      <c r="C77" s="16"/>
       <c r="D77" s="5"/>
       <c r="E77" s="6"/>
       <c r="F77" s="7"/>
@@ -2561,7 +2604,7 @@
     <row r="78" spans="1:18">
       <c r="A78" s="8"/>
       <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
+      <c r="C78" s="16"/>
       <c r="D78" s="5"/>
       <c r="E78" s="6"/>
       <c r="F78" s="7"/>
@@ -2581,7 +2624,7 @@
     <row r="79" spans="1:18">
       <c r="A79" s="8"/>
       <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
+      <c r="C79" s="16"/>
       <c r="D79" s="5"/>
       <c r="E79" s="6"/>
       <c r="F79" s="7"/>
@@ -2601,7 +2644,7 @@
     <row r="80" spans="1:18">
       <c r="A80" s="8"/>
       <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
+      <c r="C80" s="16"/>
       <c r="D80" s="5"/>
       <c r="E80" s="6"/>
       <c r="F80" s="7"/>
@@ -2621,7 +2664,7 @@
     <row r="81" spans="1:18">
       <c r="A81" s="8"/>
       <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
+      <c r="C81" s="16"/>
       <c r="D81" s="5"/>
       <c r="E81" s="6"/>
       <c r="F81" s="7"/>
@@ -2641,7 +2684,7 @@
     <row r="82" spans="1:18">
       <c r="A82" s="8"/>
       <c r="B82" s="10"/>
-      <c r="C82" s="10"/>
+      <c r="C82" s="16"/>
       <c r="D82" s="5"/>
       <c r="E82" s="6"/>
       <c r="F82" s="7"/>
@@ -2661,7 +2704,7 @@
     <row r="83" spans="1:18">
       <c r="A83" s="8"/>
       <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
+      <c r="C83" s="16"/>
       <c r="D83" s="5"/>
       <c r="E83" s="6"/>
       <c r="F83" s="7"/>
@@ -2681,7 +2724,7 @@
     <row r="84" spans="1:18">
       <c r="A84" s="8"/>
       <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
+      <c r="C84" s="16"/>
       <c r="D84" s="5"/>
       <c r="E84" s="6"/>
       <c r="F84" s="7"/>
@@ -2701,7 +2744,7 @@
     <row r="85" spans="1:18">
       <c r="A85" s="8"/>
       <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
+      <c r="C85" s="16"/>
       <c r="D85" s="5"/>
       <c r="E85" s="6"/>
       <c r="F85" s="7"/>
@@ -2721,7 +2764,7 @@
     <row r="86" spans="1:18">
       <c r="A86" s="8"/>
       <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
+      <c r="C86" s="16"/>
       <c r="D86" s="5"/>
       <c r="E86" s="6"/>
       <c r="F86" s="7"/>
@@ -2741,7 +2784,7 @@
     <row r="87" spans="1:18">
       <c r="A87" s="8"/>
       <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
+      <c r="C87" s="16"/>
       <c r="D87" s="5"/>
       <c r="E87" s="6"/>
       <c r="F87" s="7"/>
@@ -2761,7 +2804,7 @@
     <row r="88" spans="1:18">
       <c r="A88" s="8"/>
       <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
+      <c r="C88" s="16"/>
       <c r="D88" s="5"/>
       <c r="E88" s="6"/>
       <c r="F88" s="7"/>
@@ -2781,7 +2824,7 @@
     <row r="89" spans="1:18">
       <c r="A89" s="8"/>
       <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
+      <c r="C89" s="16"/>
       <c r="D89" s="5"/>
       <c r="E89" s="6"/>
       <c r="F89" s="7"/>
@@ -2801,7 +2844,7 @@
     <row r="90" spans="1:18">
       <c r="A90" s="8"/>
       <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
+      <c r="C90" s="16"/>
       <c r="D90" s="5"/>
       <c r="E90" s="6"/>
       <c r="F90" s="7"/>
@@ -2821,7 +2864,7 @@
     <row r="91" spans="1:18">
       <c r="A91" s="8"/>
       <c r="B91" s="10"/>
-      <c r="C91" s="10"/>
+      <c r="C91" s="16"/>
       <c r="D91" s="5"/>
       <c r="E91" s="6"/>
       <c r="F91" s="7"/>
@@ -2841,7 +2884,7 @@
     <row r="92" spans="1:18">
       <c r="A92" s="8"/>
       <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
+      <c r="C92" s="16"/>
       <c r="D92" s="5"/>
       <c r="E92" s="6"/>
       <c r="F92" s="7"/>
@@ -2861,7 +2904,7 @@
     <row r="93" spans="1:18">
       <c r="A93" s="8"/>
       <c r="B93" s="10"/>
-      <c r="C93" s="10"/>
+      <c r="C93" s="16"/>
       <c r="D93" s="5"/>
       <c r="E93" s="6"/>
       <c r="F93" s="7"/>
@@ -2881,7 +2924,7 @@
     <row r="94" spans="1:18">
       <c r="A94" s="8"/>
       <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
+      <c r="C94" s="16"/>
       <c r="D94" s="5"/>
       <c r="E94" s="6"/>
       <c r="F94" s="7"/>
@@ -2901,7 +2944,7 @@
     <row r="95" spans="1:18">
       <c r="A95" s="8"/>
       <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
+      <c r="C95" s="16"/>
       <c r="D95" s="5"/>
       <c r="E95" s="6"/>
       <c r="F95" s="7"/>
@@ -2921,7 +2964,7 @@
     <row r="96" spans="1:18">
       <c r="A96" s="8"/>
       <c r="B96" s="10"/>
-      <c r="C96" s="10"/>
+      <c r="C96" s="16"/>
       <c r="D96" s="5"/>
       <c r="E96" s="6"/>
       <c r="F96" s="7"/>
@@ -2941,7 +2984,7 @@
     <row r="97" spans="1:18">
       <c r="A97" s="8"/>
       <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
+      <c r="C97" s="16"/>
       <c r="D97" s="5"/>
       <c r="E97" s="6"/>
       <c r="F97" s="7"/>
@@ -2961,7 +3004,7 @@
     <row r="98" spans="1:18">
       <c r="A98" s="8"/>
       <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
+      <c r="C98" s="16"/>
       <c r="D98" s="5"/>
       <c r="E98" s="6"/>
       <c r="F98" s="7"/>
@@ -2981,7 +3024,7 @@
     <row r="99" spans="1:18">
       <c r="A99" s="8"/>
       <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
+      <c r="C99" s="16"/>
       <c r="D99" s="5"/>
       <c r="E99" s="6"/>
       <c r="F99" s="7"/>
@@ -3001,7 +3044,7 @@
     <row r="100" spans="1:18">
       <c r="A100" s="8"/>
       <c r="B100" s="10"/>
-      <c r="C100" s="10"/>
+      <c r="C100" s="16"/>
       <c r="D100" s="5"/>
       <c r="E100" s="6"/>
       <c r="F100" s="7"/>
@@ -3021,7 +3064,7 @@
     <row r="101" spans="1:18">
       <c r="A101" s="8"/>
       <c r="B101" s="10"/>
-      <c r="C101" s="10"/>
+      <c r="C101" s="16"/>
       <c r="D101" s="5"/>
       <c r="E101" s="6"/>
       <c r="F101" s="7"/>
@@ -3041,7 +3084,7 @@
     <row r="102" spans="1:18">
       <c r="A102" s="8"/>
       <c r="B102" s="10"/>
-      <c r="C102" s="10"/>
+      <c r="C102" s="16"/>
       <c r="D102" s="5"/>
       <c r="E102" s="6"/>
       <c r="F102" s="7"/>
@@ -3061,7 +3104,7 @@
     <row r="103" spans="1:18">
       <c r="A103" s="8"/>
       <c r="B103" s="10"/>
-      <c r="C103" s="10"/>
+      <c r="C103" s="16"/>
       <c r="D103" s="5"/>
       <c r="E103" s="6"/>
       <c r="F103" s="7"/>
@@ -3081,7 +3124,7 @@
     <row r="104" spans="1:18">
       <c r="A104" s="8"/>
       <c r="B104" s="10"/>
-      <c r="C104" s="10"/>
+      <c r="C104" s="16"/>
       <c r="D104" s="5"/>
       <c r="E104" s="6"/>
       <c r="F104" s="7"/>
@@ -3101,7 +3144,7 @@
     <row r="105" spans="1:18">
       <c r="A105" s="8"/>
       <c r="B105" s="10"/>
-      <c r="C105" s="10"/>
+      <c r="C105" s="16"/>
       <c r="D105" s="5"/>
       <c r="E105" s="6"/>
       <c r="F105" s="7"/>
@@ -3121,7 +3164,7 @@
     <row r="106" spans="1:18">
       <c r="A106" s="8"/>
       <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
+      <c r="C106" s="16"/>
       <c r="D106" s="5"/>
       <c r="E106" s="6"/>
       <c r="F106" s="7"/>
@@ -3141,7 +3184,7 @@
     <row r="107" spans="1:18">
       <c r="A107" s="8"/>
       <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
+      <c r="C107" s="16"/>
       <c r="D107" s="5"/>
       <c r="E107" s="6"/>
       <c r="F107" s="7"/>
@@ -3161,7 +3204,7 @@
     <row r="108" spans="1:18">
       <c r="A108" s="8"/>
       <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
+      <c r="C108" s="16"/>
       <c r="D108" s="5"/>
       <c r="E108" s="6"/>
       <c r="F108" s="7"/>
@@ -3181,7 +3224,7 @@
     <row r="109" spans="1:18">
       <c r="A109" s="8"/>
       <c r="B109" s="10"/>
-      <c r="C109" s="10"/>
+      <c r="C109" s="16"/>
       <c r="D109" s="5"/>
       <c r="E109" s="6"/>
       <c r="F109" s="7"/>
@@ -3201,7 +3244,7 @@
     <row r="110" spans="1:18">
       <c r="A110" s="8"/>
       <c r="B110" s="10"/>
-      <c r="C110" s="10"/>
+      <c r="C110" s="16"/>
       <c r="D110" s="5"/>
       <c r="E110" s="6"/>
       <c r="F110" s="7"/>
@@ -3221,7 +3264,7 @@
     <row r="111" spans="1:18">
       <c r="A111" s="8"/>
       <c r="B111" s="10"/>
-      <c r="C111" s="10"/>
+      <c r="C111" s="16"/>
       <c r="D111" s="5"/>
       <c r="E111" s="6"/>
       <c r="F111" s="7"/>
@@ -3241,7 +3284,7 @@
     <row r="112" spans="1:18">
       <c r="A112" s="8"/>
       <c r="B112" s="10"/>
-      <c r="C112" s="10"/>
+      <c r="C112" s="16"/>
       <c r="D112" s="5"/>
       <c r="E112" s="6"/>
       <c r="F112" s="7"/>
@@ -3261,7 +3304,7 @@
     <row r="113" spans="1:18">
       <c r="A113" s="8"/>
       <c r="B113" s="10"/>
-      <c r="C113" s="10"/>
+      <c r="C113" s="16"/>
       <c r="D113" s="5"/>
       <c r="E113" s="6"/>
       <c r="F113" s="7"/>
@@ -3281,7 +3324,7 @@
     <row r="114" spans="1:18">
       <c r="A114" s="8"/>
       <c r="B114" s="10"/>
-      <c r="C114" s="10"/>
+      <c r="C114" s="16"/>
       <c r="D114" s="5"/>
       <c r="E114" s="6"/>
       <c r="F114" s="7"/>
@@ -3301,7 +3344,7 @@
     <row r="115" spans="1:18">
       <c r="A115" s="8"/>
       <c r="B115" s="10"/>
-      <c r="C115" s="10"/>
+      <c r="C115" s="16"/>
       <c r="D115" s="5"/>
       <c r="E115" s="6"/>
       <c r="F115" s="7"/>
@@ -3321,7 +3364,7 @@
     <row r="116" spans="1:18">
       <c r="A116" s="8"/>
       <c r="B116" s="10"/>
-      <c r="C116" s="10"/>
+      <c r="C116" s="16"/>
       <c r="D116" s="5"/>
       <c r="E116" s="6"/>
       <c r="F116" s="7"/>
@@ -3341,7 +3384,7 @@
     <row r="117" spans="1:18">
       <c r="A117" s="8"/>
       <c r="B117" s="10"/>
-      <c r="C117" s="10"/>
+      <c r="C117" s="16"/>
       <c r="D117" s="5"/>
       <c r="E117" s="6"/>
       <c r="F117" s="7"/>
@@ -3361,7 +3404,7 @@
     <row r="118" spans="1:18">
       <c r="A118" s="8"/>
       <c r="B118" s="10"/>
-      <c r="C118" s="10"/>
+      <c r="C118" s="16"/>
       <c r="D118" s="5"/>
       <c r="E118" s="6"/>
       <c r="F118" s="7"/>
@@ -3381,7 +3424,7 @@
     <row r="119" spans="1:18">
       <c r="A119" s="8"/>
       <c r="B119" s="10"/>
-      <c r="C119" s="10"/>
+      <c r="C119" s="16"/>
       <c r="D119" s="5"/>
       <c r="E119" s="6"/>
       <c r="F119" s="7"/>
@@ -3401,7 +3444,7 @@
     <row r="120" spans="1:18">
       <c r="A120" s="8"/>
       <c r="B120" s="10"/>
-      <c r="C120" s="10"/>
+      <c r="C120" s="16"/>
       <c r="D120" s="5"/>
       <c r="E120" s="6"/>
       <c r="F120" s="7"/>
@@ -3421,7 +3464,7 @@
     <row r="121" spans="1:18">
       <c r="A121" s="8"/>
       <c r="B121" s="10"/>
-      <c r="C121" s="10"/>
+      <c r="C121" s="16"/>
       <c r="D121" s="5"/>
       <c r="E121" s="6"/>
       <c r="F121" s="7"/>
@@ -3441,7 +3484,7 @@
     <row r="122" spans="1:18">
       <c r="A122" s="8"/>
       <c r="B122" s="10"/>
-      <c r="C122" s="10"/>
+      <c r="C122" s="16"/>
       <c r="D122" s="5"/>
       <c r="E122" s="6"/>
       <c r="F122" s="7"/>
@@ -3461,7 +3504,7 @@
     <row r="123" spans="1:18">
       <c r="A123" s="8"/>
       <c r="B123" s="10"/>
-      <c r="C123" s="10"/>
+      <c r="C123" s="16"/>
       <c r="D123" s="5"/>
       <c r="E123" s="6"/>
       <c r="F123" s="7"/>
@@ -3481,7 +3524,7 @@
     <row r="124" spans="1:18">
       <c r="A124" s="8"/>
       <c r="B124" s="10"/>
-      <c r="C124" s="10"/>
+      <c r="C124" s="16"/>
       <c r="D124" s="5"/>
       <c r="E124" s="6"/>
       <c r="F124" s="7"/>
@@ -3501,7 +3544,7 @@
     <row r="125" spans="1:18">
       <c r="A125" s="8"/>
       <c r="B125" s="10"/>
-      <c r="C125" s="10"/>
+      <c r="C125" s="16"/>
       <c r="D125" s="5"/>
       <c r="E125" s="6"/>
       <c r="F125" s="7"/>
@@ -3521,7 +3564,7 @@
     <row r="126" spans="1:18">
       <c r="A126" s="8"/>
       <c r="B126" s="10"/>
-      <c r="C126" s="10"/>
+      <c r="C126" s="16"/>
       <c r="D126" s="5"/>
       <c r="E126" s="6"/>
       <c r="F126" s="7"/>
@@ -3541,7 +3584,7 @@
     <row r="127" spans="1:18">
       <c r="A127" s="8"/>
       <c r="B127" s="10"/>
-      <c r="C127" s="10"/>
+      <c r="C127" s="16"/>
       <c r="D127" s="5"/>
       <c r="E127" s="6"/>
       <c r="F127" s="7"/>
@@ -3561,7 +3604,7 @@
     <row r="128" spans="1:18">
       <c r="A128" s="8"/>
       <c r="B128" s="10"/>
-      <c r="C128" s="10"/>
+      <c r="C128" s="16"/>
       <c r="D128" s="5"/>
       <c r="E128" s="6"/>
       <c r="F128" s="7"/>
@@ -3581,7 +3624,7 @@
     <row r="129" spans="1:18">
       <c r="A129" s="8"/>
       <c r="B129" s="10"/>
-      <c r="C129" s="10"/>
+      <c r="C129" s="16"/>
       <c r="D129" s="5"/>
       <c r="E129" s="6"/>
       <c r="F129" s="7"/>
@@ -3601,7 +3644,7 @@
     <row r="130" spans="1:18">
       <c r="A130" s="8"/>
       <c r="B130" s="10"/>
-      <c r="C130" s="10"/>
+      <c r="C130" s="16"/>
       <c r="D130" s="5"/>
       <c r="E130" s="6"/>
       <c r="F130" s="7"/>
@@ -3621,7 +3664,7 @@
     <row r="131" spans="1:18">
       <c r="A131" s="8"/>
       <c r="B131" s="10"/>
-      <c r="C131" s="10"/>
+      <c r="C131" s="16"/>
       <c r="D131" s="5"/>
       <c r="E131" s="6"/>
       <c r="F131" s="7"/>
@@ -3641,7 +3684,7 @@
     <row r="132" spans="1:18">
       <c r="A132" s="8"/>
       <c r="B132" s="10"/>
-      <c r="C132" s="10"/>
+      <c r="C132" s="16"/>
       <c r="D132" s="5"/>
       <c r="E132" s="6"/>
       <c r="F132" s="7"/>
@@ -3661,7 +3704,7 @@
     <row r="133" spans="1:18">
       <c r="A133" s="8"/>
       <c r="B133" s="10"/>
-      <c r="C133" s="10"/>
+      <c r="C133" s="16"/>
       <c r="D133" s="5"/>
       <c r="E133" s="6"/>
       <c r="F133" s="7"/>
@@ -3681,7 +3724,7 @@
     <row r="134" spans="1:18">
       <c r="A134" s="8"/>
       <c r="B134" s="10"/>
-      <c r="C134" s="10"/>
+      <c r="C134" s="16"/>
       <c r="D134" s="5"/>
       <c r="E134" s="6"/>
       <c r="F134" s="7"/>
@@ -3701,7 +3744,7 @@
     <row r="135" spans="1:18">
       <c r="A135" s="8"/>
       <c r="B135" s="10"/>
-      <c r="C135" s="10"/>
+      <c r="C135" s="16"/>
       <c r="D135" s="5"/>
       <c r="E135" s="6"/>
       <c r="F135" s="7"/>
@@ -3721,7 +3764,7 @@
     <row r="136" spans="1:18">
       <c r="A136" s="8"/>
       <c r="B136" s="10"/>
-      <c r="C136" s="10"/>
+      <c r="C136" s="16"/>
       <c r="D136" s="5"/>
       <c r="E136" s="6"/>
       <c r="F136" s="7"/>
@@ -3741,7 +3784,7 @@
     <row r="137" spans="1:18">
       <c r="A137" s="8"/>
       <c r="B137" s="10"/>
-      <c r="C137" s="10"/>
+      <c r="C137" s="16"/>
       <c r="D137" s="5"/>
       <c r="E137" s="6"/>
       <c r="F137" s="7"/>
@@ -3761,7 +3804,7 @@
     <row r="138" spans="1:18">
       <c r="A138" s="8"/>
       <c r="B138" s="10"/>
-      <c r="C138" s="10"/>
+      <c r="C138" s="16"/>
       <c r="D138" s="5"/>
       <c r="E138" s="6"/>
       <c r="F138" s="7"/>
@@ -3781,7 +3824,7 @@
     <row r="139" spans="1:18">
       <c r="A139" s="8"/>
       <c r="B139" s="10"/>
-      <c r="C139" s="10"/>
+      <c r="C139" s="16"/>
       <c r="D139" s="5"/>
       <c r="E139" s="6"/>
       <c r="F139" s="7"/>
@@ -3801,7 +3844,7 @@
     <row r="140" spans="1:18">
       <c r="A140" s="8"/>
       <c r="B140" s="10"/>
-      <c r="C140" s="10"/>
+      <c r="C140" s="16"/>
       <c r="D140" s="5"/>
       <c r="E140" s="6"/>
       <c r="F140" s="7"/>
@@ -3821,7 +3864,7 @@
     <row r="141" spans="1:18">
       <c r="A141" s="8"/>
       <c r="B141" s="10"/>
-      <c r="C141" s="10"/>
+      <c r="C141" s="16"/>
       <c r="D141" s="5"/>
       <c r="E141" s="6"/>
       <c r="F141" s="7"/>
@@ -3841,7 +3884,7 @@
     <row r="142" spans="1:18">
       <c r="A142" s="8"/>
       <c r="B142" s="10"/>
-      <c r="C142" s="10"/>
+      <c r="C142" s="16"/>
       <c r="D142" s="5"/>
       <c r="E142" s="6"/>
       <c r="F142" s="7"/>
@@ -3861,7 +3904,7 @@
     <row r="143" spans="1:18">
       <c r="A143" s="8"/>
       <c r="B143" s="10"/>
-      <c r="C143" s="10"/>
+      <c r="C143" s="16"/>
       <c r="D143" s="5"/>
       <c r="E143" s="6"/>
       <c r="F143" s="7"/>
@@ -3881,7 +3924,7 @@
     <row r="144" spans="1:18">
       <c r="A144" s="8"/>
       <c r="B144" s="10"/>
-      <c r="C144" s="10"/>
+      <c r="C144" s="16"/>
       <c r="D144" s="5"/>
       <c r="E144" s="6"/>
       <c r="F144" s="7"/>
@@ -3901,7 +3944,7 @@
     <row r="145" spans="1:18">
       <c r="A145" s="8"/>
       <c r="B145" s="10"/>
-      <c r="C145" s="10"/>
+      <c r="C145" s="16"/>
       <c r="D145" s="5"/>
       <c r="E145" s="6"/>
       <c r="F145" s="7"/>
@@ -3921,7 +3964,7 @@
     <row r="146" spans="1:18">
       <c r="A146" s="8"/>
       <c r="B146" s="10"/>
-      <c r="C146" s="10"/>
+      <c r="C146" s="16"/>
       <c r="D146" s="5"/>
       <c r="E146" s="6"/>
       <c r="F146" s="7"/>
@@ -3941,7 +3984,7 @@
     <row r="147" spans="1:18">
       <c r="A147" s="8"/>
       <c r="B147" s="10"/>
-      <c r="C147" s="10"/>
+      <c r="C147" s="16"/>
       <c r="D147" s="5"/>
       <c r="E147" s="6"/>
       <c r="F147" s="7"/>
@@ -3961,7 +4004,7 @@
     <row r="148" spans="1:18">
       <c r="A148" s="8"/>
       <c r="B148" s="10"/>
-      <c r="C148" s="10"/>
+      <c r="C148" s="16"/>
       <c r="D148" s="5"/>
       <c r="E148" s="6"/>
       <c r="F148" s="7"/>
@@ -3981,7 +4024,7 @@
     <row r="149" spans="1:18">
       <c r="A149" s="8"/>
       <c r="B149" s="10"/>
-      <c r="C149" s="10"/>
+      <c r="C149" s="16"/>
       <c r="D149" s="5"/>
       <c r="E149" s="6"/>
       <c r="F149" s="7"/>
@@ -4001,7 +4044,7 @@
     <row r="150" spans="1:18">
       <c r="A150" s="8"/>
       <c r="B150" s="10"/>
-      <c r="C150" s="10"/>
+      <c r="C150" s="16"/>
       <c r="D150" s="5"/>
       <c r="E150" s="6"/>
       <c r="F150" s="7"/>
@@ -4021,7 +4064,7 @@
     <row r="151" spans="1:18">
       <c r="A151" s="8"/>
       <c r="B151" s="10"/>
-      <c r="C151" s="10"/>
+      <c r="C151" s="16"/>
       <c r="D151" s="5"/>
       <c r="E151" s="6"/>
       <c r="F151" s="7"/>
@@ -4041,7 +4084,7 @@
     <row r="152" spans="1:18">
       <c r="A152" s="8"/>
       <c r="B152" s="10"/>
-      <c r="C152" s="10"/>
+      <c r="C152" s="16"/>
       <c r="D152" s="5"/>
       <c r="E152" s="6"/>
       <c r="F152" s="7"/>
@@ -4061,7 +4104,7 @@
     <row r="153" spans="1:18">
       <c r="A153" s="8"/>
       <c r="B153" s="10"/>
-      <c r="C153" s="10"/>
+      <c r="C153" s="16"/>
       <c r="D153" s="5"/>
       <c r="E153" s="6"/>
       <c r="F153" s="7"/>
@@ -4081,7 +4124,7 @@
     <row r="154" spans="1:18">
       <c r="A154" s="8"/>
       <c r="B154" s="10"/>
-      <c r="C154" s="10"/>
+      <c r="C154" s="16"/>
       <c r="D154" s="5"/>
       <c r="E154" s="6"/>
       <c r="F154" s="7"/>
@@ -4101,7 +4144,7 @@
     <row r="155" spans="1:18">
       <c r="A155" s="8"/>
       <c r="B155" s="10"/>
-      <c r="C155" s="10"/>
+      <c r="C155" s="16"/>
       <c r="D155" s="5"/>
       <c r="E155" s="6"/>
       <c r="F155" s="7"/>
@@ -4121,7 +4164,7 @@
     <row r="156" spans="1:18">
       <c r="A156" s="8"/>
       <c r="B156" s="10"/>
-      <c r="C156" s="10"/>
+      <c r="C156" s="16"/>
       <c r="D156" s="5"/>
       <c r="E156" s="6"/>
       <c r="F156" s="7"/>
@@ -4141,7 +4184,7 @@
     <row r="157" spans="1:18">
       <c r="A157" s="8"/>
       <c r="B157" s="10"/>
-      <c r="C157" s="10"/>
+      <c r="C157" s="16"/>
       <c r="D157" s="5"/>
       <c r="E157" s="6"/>
       <c r="F157" s="7"/>
@@ -4161,7 +4204,7 @@
     <row r="158" spans="1:18">
       <c r="A158" s="8"/>
       <c r="B158" s="10"/>
-      <c r="C158" s="10"/>
+      <c r="C158" s="16"/>
       <c r="D158" s="5"/>
       <c r="E158" s="6"/>
       <c r="F158" s="7"/>
@@ -4181,7 +4224,7 @@
     <row r="159" spans="1:18">
       <c r="A159" s="8"/>
       <c r="B159" s="10"/>
-      <c r="C159" s="10"/>
+      <c r="C159" s="16"/>
       <c r="D159" s="5"/>
       <c r="E159" s="6"/>
       <c r="F159" s="7"/>
@@ -4201,7 +4244,7 @@
     <row r="160" spans="1:18">
       <c r="A160" s="8"/>
       <c r="B160" s="10"/>
-      <c r="C160" s="10"/>
+      <c r="C160" s="16"/>
       <c r="D160" s="5"/>
       <c r="E160" s="6"/>
       <c r="F160" s="7"/>
@@ -4221,7 +4264,7 @@
     <row r="161" spans="1:18">
       <c r="A161" s="8"/>
       <c r="B161" s="10"/>
-      <c r="C161" s="10"/>
+      <c r="C161" s="16"/>
       <c r="D161" s="5"/>
       <c r="E161" s="6"/>
       <c r="F161" s="7"/>
@@ -4241,7 +4284,7 @@
     <row r="162" spans="1:18">
       <c r="A162" s="8"/>
       <c r="B162" s="10"/>
-      <c r="C162" s="10"/>
+      <c r="C162" s="16"/>
       <c r="D162" s="5"/>
       <c r="E162" s="6"/>
       <c r="F162" s="7"/>
@@ -4261,7 +4304,7 @@
     <row r="163" spans="1:18">
       <c r="A163" s="8"/>
       <c r="B163" s="10"/>
-      <c r="C163" s="10"/>
+      <c r="C163" s="16"/>
       <c r="D163" s="5"/>
       <c r="E163" s="6"/>
       <c r="F163" s="7"/>
@@ -4281,7 +4324,7 @@
     <row r="164" spans="1:18">
       <c r="A164" s="8"/>
       <c r="B164" s="10"/>
-      <c r="C164" s="10"/>
+      <c r="C164" s="16"/>
       <c r="D164" s="5"/>
       <c r="E164" s="6"/>
       <c r="F164" s="7"/>
@@ -4301,7 +4344,7 @@
     <row r="165" spans="1:18">
       <c r="A165" s="8"/>
       <c r="B165" s="10"/>
-      <c r="C165" s="10"/>
+      <c r="C165" s="16"/>
       <c r="D165" s="5"/>
       <c r="E165" s="6"/>
       <c r="F165" s="7"/>
@@ -4321,7 +4364,7 @@
     <row r="166" spans="1:18">
       <c r="A166" s="8"/>
       <c r="B166" s="10"/>
-      <c r="C166" s="10"/>
+      <c r="C166" s="16"/>
       <c r="D166" s="5"/>
       <c r="E166" s="6"/>
       <c r="F166" s="7"/>
@@ -4341,7 +4384,7 @@
     <row r="167" spans="1:18">
       <c r="A167" s="8"/>
       <c r="B167" s="10"/>
-      <c r="C167" s="10"/>
+      <c r="C167" s="16"/>
       <c r="D167" s="5"/>
       <c r="E167" s="6"/>
       <c r="F167" s="7"/>
@@ -4361,7 +4404,7 @@
     <row r="168" spans="1:18">
       <c r="A168" s="8"/>
       <c r="B168" s="10"/>
-      <c r="C168" s="10"/>
+      <c r="C168" s="16"/>
       <c r="D168" s="5"/>
       <c r="E168" s="6"/>
       <c r="F168" s="7"/>
@@ -4381,7 +4424,7 @@
     <row r="169" spans="1:18">
       <c r="A169" s="8"/>
       <c r="B169" s="10"/>
-      <c r="C169" s="10"/>
+      <c r="C169" s="16"/>
       <c r="D169" s="5"/>
       <c r="E169" s="6"/>
       <c r="F169" s="7"/>
@@ -4401,7 +4444,7 @@
     <row r="170" spans="1:18">
       <c r="A170" s="8"/>
       <c r="B170" s="10"/>
-      <c r="C170" s="10"/>
+      <c r="C170" s="16"/>
       <c r="D170" s="5"/>
       <c r="E170" s="6"/>
       <c r="F170" s="7"/>
@@ -4421,7 +4464,7 @@
     <row r="171" spans="1:18">
       <c r="A171" s="8"/>
       <c r="B171" s="10"/>
-      <c r="C171" s="10"/>
+      <c r="C171" s="16"/>
       <c r="D171" s="5"/>
       <c r="E171" s="6"/>
       <c r="F171" s="7"/>
@@ -4441,7 +4484,7 @@
     <row r="172" spans="1:18">
       <c r="A172" s="8"/>
       <c r="B172" s="10"/>
-      <c r="C172" s="10"/>
+      <c r="C172" s="16"/>
       <c r="D172" s="5"/>
       <c r="E172" s="6"/>
       <c r="F172" s="7"/>
@@ -4461,7 +4504,7 @@
     <row r="173" spans="1:18">
       <c r="A173" s="8"/>
       <c r="B173" s="10"/>
-      <c r="C173" s="10"/>
+      <c r="C173" s="16"/>
       <c r="D173" s="5"/>
       <c r="E173" s="6"/>
       <c r="F173" s="7"/>
@@ -4481,7 +4524,7 @@
     <row r="174" spans="1:18">
       <c r="A174" s="8"/>
       <c r="B174" s="10"/>
-      <c r="C174" s="10"/>
+      <c r="C174" s="16"/>
       <c r="D174" s="5"/>
       <c r="E174" s="6"/>
       <c r="F174" s="7"/>
@@ -4501,7 +4544,7 @@
     <row r="175" spans="1:18">
       <c r="A175" s="8"/>
       <c r="B175" s="10"/>
-      <c r="C175" s="10"/>
+      <c r="C175" s="16"/>
       <c r="D175" s="5"/>
       <c r="E175" s="6"/>
       <c r="F175" s="7"/>
@@ -4521,7 +4564,7 @@
     <row r="176" spans="1:18">
       <c r="A176" s="8"/>
       <c r="B176" s="10"/>
-      <c r="C176" s="10"/>
+      <c r="C176" s="16"/>
       <c r="D176" s="5"/>
       <c r="E176" s="6"/>
       <c r="F176" s="7"/>
@@ -4541,7 +4584,7 @@
     <row r="177" spans="1:18">
       <c r="A177" s="8"/>
       <c r="B177" s="10"/>
-      <c r="C177" s="10"/>
+      <c r="C177" s="16"/>
       <c r="D177" s="5"/>
       <c r="E177" s="6"/>
       <c r="F177" s="7"/>
@@ -4561,7 +4604,7 @@
     <row r="178" spans="1:18">
       <c r="A178" s="8"/>
       <c r="B178" s="10"/>
-      <c r="C178" s="10"/>
+      <c r="C178" s="16"/>
       <c r="D178" s="5"/>
       <c r="E178" s="6"/>
       <c r="F178" s="7"/>
@@ -4581,7 +4624,7 @@
     <row r="179" spans="1:18">
       <c r="A179" s="8"/>
       <c r="B179" s="10"/>
-      <c r="C179" s="10"/>
+      <c r="C179" s="16"/>
       <c r="D179" s="5"/>
       <c r="E179" s="6"/>
       <c r="F179" s="7"/>
@@ -4601,7 +4644,7 @@
     <row r="180" spans="1:18">
       <c r="A180" s="8"/>
       <c r="B180" s="10"/>
-      <c r="C180" s="10"/>
+      <c r="C180" s="16"/>
       <c r="D180" s="5"/>
       <c r="E180" s="6"/>
       <c r="F180" s="7"/>
@@ -4621,7 +4664,7 @@
     <row r="181" spans="1:18">
       <c r="A181" s="8"/>
       <c r="B181" s="10"/>
-      <c r="C181" s="10"/>
+      <c r="C181" s="16"/>
       <c r="D181" s="5"/>
       <c r="E181" s="6"/>
       <c r="F181" s="7"/>
@@ -4641,7 +4684,7 @@
     <row r="182" spans="1:18">
       <c r="A182" s="8"/>
       <c r="B182" s="10"/>
-      <c r="C182" s="10"/>
+      <c r="C182" s="16"/>
       <c r="D182" s="5"/>
       <c r="E182" s="6"/>
       <c r="F182" s="7"/>
@@ -4661,7 +4704,7 @@
     <row r="183" spans="1:18">
       <c r="A183" s="8"/>
       <c r="B183" s="10"/>
-      <c r="C183" s="10"/>
+      <c r="C183" s="16"/>
       <c r="D183" s="5"/>
       <c r="E183" s="6"/>
       <c r="F183" s="7"/>
@@ -4681,7 +4724,7 @@
     <row r="184" spans="1:18">
       <c r="A184" s="8"/>
       <c r="B184" s="10"/>
-      <c r="C184" s="10"/>
+      <c r="C184" s="16"/>
       <c r="D184" s="5"/>
       <c r="E184" s="6"/>
       <c r="F184" s="7"/>
@@ -4701,7 +4744,7 @@
     <row r="185" spans="1:18">
       <c r="A185" s="8"/>
       <c r="B185" s="10"/>
-      <c r="C185" s="10"/>
+      <c r="C185" s="16"/>
       <c r="D185" s="5"/>
       <c r="E185" s="6"/>
       <c r="F185" s="7"/>
@@ -4721,7 +4764,7 @@
     <row r="186" spans="1:18">
       <c r="A186" s="8"/>
       <c r="B186" s="10"/>
-      <c r="C186" s="10"/>
+      <c r="C186" s="16"/>
       <c r="D186" s="5"/>
       <c r="E186" s="6"/>
       <c r="F186" s="7"/>
@@ -4741,7 +4784,7 @@
     <row r="187" spans="1:18">
       <c r="A187" s="8"/>
       <c r="B187" s="10"/>
-      <c r="C187" s="10"/>
+      <c r="C187" s="16"/>
       <c r="D187" s="5"/>
       <c r="E187" s="6"/>
       <c r="F187" s="7"/>
@@ -4761,7 +4804,7 @@
     <row r="188" spans="1:18">
       <c r="A188" s="8"/>
       <c r="B188" s="10"/>
-      <c r="C188" s="10"/>
+      <c r="C188" s="16"/>
       <c r="D188" s="5"/>
       <c r="E188" s="6"/>
       <c r="F188" s="7"/>
@@ -4781,7 +4824,7 @@
     <row r="189" spans="1:18">
       <c r="A189" s="8"/>
       <c r="B189" s="10"/>
-      <c r="C189" s="10"/>
+      <c r="C189" s="16"/>
       <c r="D189" s="5"/>
       <c r="E189" s="6"/>
       <c r="F189" s="7"/>
@@ -4801,7 +4844,7 @@
     <row r="190" spans="1:18">
       <c r="A190" s="8"/>
       <c r="B190" s="10"/>
-      <c r="C190" s="10"/>
+      <c r="C190" s="16"/>
       <c r="D190" s="5"/>
       <c r="E190" s="6"/>
       <c r="F190" s="7"/>
@@ -4821,7 +4864,7 @@
     <row r="191" spans="1:18">
       <c r="A191" s="8"/>
       <c r="B191" s="10"/>
-      <c r="C191" s="10"/>
+      <c r="C191" s="16"/>
       <c r="D191" s="5"/>
       <c r="E191" s="6"/>
       <c r="F191" s="7"/>
@@ -4841,7 +4884,7 @@
     <row r="192" spans="1:18">
       <c r="A192" s="8"/>
       <c r="B192" s="10"/>
-      <c r="C192" s="10"/>
+      <c r="C192" s="16"/>
       <c r="D192" s="5"/>
       <c r="E192" s="6"/>
       <c r="F192" s="7"/>
@@ -4861,7 +4904,7 @@
     <row r="193" spans="1:18">
       <c r="A193" s="8"/>
       <c r="B193" s="10"/>
-      <c r="C193" s="10"/>
+      <c r="C193" s="16"/>
       <c r="D193" s="5"/>
       <c r="E193" s="6"/>
       <c r="F193" s="7"/>
@@ -4881,7 +4924,7 @@
     <row r="194" spans="1:18">
       <c r="A194" s="8"/>
       <c r="B194" s="10"/>
-      <c r="C194" s="10"/>
+      <c r="C194" s="16"/>
       <c r="D194" s="5"/>
       <c r="E194" s="6"/>
       <c r="F194" s="7"/>
@@ -4901,7 +4944,7 @@
     <row r="195" spans="1:18">
       <c r="A195" s="8"/>
       <c r="B195" s="10"/>
-      <c r="C195" s="10"/>
+      <c r="C195" s="16"/>
       <c r="D195" s="5"/>
       <c r="E195" s="6"/>
       <c r="F195" s="7"/>
@@ -4921,7 +4964,7 @@
     <row r="196" spans="1:18">
       <c r="A196" s="8"/>
       <c r="B196" s="10"/>
-      <c r="C196" s="10"/>
+      <c r="C196" s="16"/>
       <c r="D196" s="5"/>
       <c r="E196" s="6"/>
       <c r="F196" s="7"/>
@@ -4941,7 +4984,7 @@
     <row r="197" spans="1:18">
       <c r="A197" s="8"/>
       <c r="B197" s="10"/>
-      <c r="C197" s="10"/>
+      <c r="C197" s="16"/>
       <c r="D197" s="5"/>
       <c r="E197" s="6"/>
       <c r="F197" s="7"/>
@@ -4961,7 +5004,7 @@
     <row r="198" spans="1:18">
       <c r="A198" s="8"/>
       <c r="B198" s="10"/>
-      <c r="C198" s="10"/>
+      <c r="C198" s="16"/>
       <c r="D198" s="5"/>
       <c r="E198" s="6"/>
       <c r="F198" s="7"/>
@@ -4981,7 +5024,7 @@
     <row r="199" spans="1:18">
       <c r="A199" s="8"/>
       <c r="B199" s="10"/>
-      <c r="C199" s="10"/>
+      <c r="C199" s="16"/>
       <c r="D199" s="5"/>
       <c r="E199" s="6"/>
       <c r="F199" s="7"/>
@@ -5001,7 +5044,7 @@
     <row r="200" spans="1:18">
       <c r="A200" s="8"/>
       <c r="B200" s="10"/>
-      <c r="C200" s="10"/>
+      <c r="C200" s="16"/>
       <c r="D200" s="5"/>
       <c r="E200" s="6"/>
       <c r="F200" s="7"/>
@@ -5021,7 +5064,7 @@
     <row r="201" spans="1:18">
       <c r="A201" s="8"/>
       <c r="B201" s="10"/>
-      <c r="C201" s="10"/>
+      <c r="C201" s="16"/>
       <c r="D201" s="5"/>
       <c r="E201" s="6"/>
       <c r="F201" s="7"/>
@@ -5041,7 +5084,7 @@
     <row r="202" spans="1:18">
       <c r="A202" s="8"/>
       <c r="B202" s="10"/>
-      <c r="C202" s="10"/>
+      <c r="C202" s="16"/>
       <c r="D202" s="5"/>
       <c r="E202" s="6"/>
       <c r="F202" s="7"/>
@@ -5061,7 +5104,7 @@
     <row r="203" spans="1:18">
       <c r="A203" s="8"/>
       <c r="B203" s="10"/>
-      <c r="C203" s="10"/>
+      <c r="C203" s="16"/>
       <c r="D203" s="5"/>
       <c r="E203" s="6"/>
       <c r="F203" s="7"/>
@@ -5081,7 +5124,7 @@
     <row r="204" spans="1:18">
       <c r="A204" s="8"/>
       <c r="B204" s="10"/>
-      <c r="C204" s="10"/>
+      <c r="C204" s="16"/>
       <c r="D204" s="5"/>
       <c r="E204" s="6"/>
       <c r="F204" s="7"/>
@@ -5101,7 +5144,7 @@
     <row r="205" spans="1:18">
       <c r="A205" s="8"/>
       <c r="B205" s="10"/>
-      <c r="C205" s="10"/>
+      <c r="C205" s="16"/>
       <c r="D205" s="5"/>
       <c r="E205" s="6"/>
       <c r="F205" s="7"/>
@@ -5121,7 +5164,7 @@
     <row r="206" spans="1:18">
       <c r="A206" s="8"/>
       <c r="B206" s="10"/>
-      <c r="C206" s="10"/>
+      <c r="C206" s="16"/>
       <c r="D206" s="5"/>
       <c r="E206" s="6"/>
       <c r="F206" s="7"/>
@@ -5141,7 +5184,7 @@
     <row r="207" spans="1:18">
       <c r="A207" s="8"/>
       <c r="B207" s="10"/>
-      <c r="C207" s="10"/>
+      <c r="C207" s="16"/>
       <c r="D207" s="5"/>
       <c r="E207" s="6"/>
       <c r="F207" s="7"/>
@@ -5161,7 +5204,7 @@
     <row r="208" spans="1:18">
       <c r="A208" s="8"/>
       <c r="B208" s="10"/>
-      <c r="C208" s="10"/>
+      <c r="C208" s="16"/>
       <c r="D208" s="5"/>
       <c r="E208" s="6"/>
       <c r="F208" s="7"/>
@@ -5181,7 +5224,7 @@
     <row r="209" spans="1:18">
       <c r="A209" s="8"/>
       <c r="B209" s="10"/>
-      <c r="C209" s="10"/>
+      <c r="C209" s="16"/>
       <c r="D209" s="5"/>
       <c r="E209" s="6"/>
       <c r="F209" s="7"/>
@@ -5201,7 +5244,7 @@
     <row r="210" spans="1:18">
       <c r="A210" s="8"/>
       <c r="B210" s="10"/>
-      <c r="C210" s="10"/>
+      <c r="C210" s="16"/>
       <c r="D210" s="5"/>
       <c r="E210" s="6"/>
       <c r="F210" s="7"/>
@@ -5221,7 +5264,7 @@
     <row r="211" spans="1:18">
       <c r="A211" s="8"/>
       <c r="B211" s="10"/>
-      <c r="C211" s="10"/>
+      <c r="C211" s="16"/>
       <c r="D211" s="5"/>
       <c r="E211" s="6"/>
       <c r="F211" s="7"/>
@@ -5241,7 +5284,7 @@
     <row r="212" spans="1:18">
       <c r="A212" s="8"/>
       <c r="B212" s="10"/>
-      <c r="C212" s="10"/>
+      <c r="C212" s="16"/>
       <c r="D212" s="5"/>
       <c r="E212" s="6"/>
       <c r="F212" s="7"/>
@@ -5261,7 +5304,7 @@
     <row r="213" spans="1:18">
       <c r="A213" s="8"/>
       <c r="B213" s="10"/>
-      <c r="C213" s="10"/>
+      <c r="C213" s="16"/>
       <c r="D213" s="5"/>
       <c r="E213" s="6"/>
       <c r="F213" s="7"/>
@@ -5281,7 +5324,7 @@
     <row r="214" spans="1:18">
       <c r="A214" s="8"/>
       <c r="B214" s="10"/>
-      <c r="C214" s="10"/>
+      <c r="C214" s="16"/>
       <c r="D214" s="5"/>
       <c r="E214" s="6"/>
       <c r="F214" s="7"/>
@@ -5301,7 +5344,7 @@
     <row r="215" spans="1:18">
       <c r="A215" s="8"/>
       <c r="B215" s="10"/>
-      <c r="C215" s="10"/>
+      <c r="C215" s="16"/>
       <c r="D215" s="5"/>
       <c r="E215" s="6"/>
       <c r="F215" s="7"/>
@@ -5321,7 +5364,7 @@
     <row r="216" spans="1:18">
       <c r="A216" s="8"/>
       <c r="B216" s="10"/>
-      <c r="C216" s="10"/>
+      <c r="C216" s="16"/>
       <c r="D216" s="5"/>
       <c r="E216" s="6"/>
       <c r="F216" s="7"/>
@@ -5341,7 +5384,7 @@
     <row r="217" spans="1:18">
       <c r="A217" s="8"/>
       <c r="B217" s="10"/>
-      <c r="C217" s="10"/>
+      <c r="C217" s="16"/>
       <c r="D217" s="5"/>
       <c r="E217" s="6"/>
       <c r="F217" s="7"/>
@@ -5361,7 +5404,7 @@
     <row r="218" spans="1:18">
       <c r="A218" s="8"/>
       <c r="B218" s="10"/>
-      <c r="C218" s="10"/>
+      <c r="C218" s="16"/>
       <c r="D218" s="5"/>
       <c r="E218" s="6"/>
       <c r="F218" s="7"/>
@@ -5381,7 +5424,7 @@
     <row r="219" spans="1:18">
       <c r="A219" s="8"/>
       <c r="B219" s="10"/>
-      <c r="C219" s="10"/>
+      <c r="C219" s="16"/>
       <c r="D219" s="5"/>
       <c r="E219" s="6"/>
       <c r="F219" s="7"/>
@@ -5401,7 +5444,7 @@
     <row r="220" spans="1:18">
       <c r="A220" s="8"/>
       <c r="B220" s="10"/>
-      <c r="C220" s="10"/>
+      <c r="C220" s="16"/>
       <c r="D220" s="5"/>
       <c r="E220" s="6"/>
       <c r="F220" s="7"/>
@@ -5421,7 +5464,7 @@
     <row r="221" spans="1:18">
       <c r="A221" s="8"/>
       <c r="B221" s="10"/>
-      <c r="C221" s="10"/>
+      <c r="C221" s="16"/>
       <c r="D221" s="5"/>
       <c r="E221" s="6"/>
       <c r="F221" s="7"/>
@@ -5441,7 +5484,7 @@
     <row r="222" spans="1:18">
       <c r="A222" s="8"/>
       <c r="B222" s="10"/>
-      <c r="C222" s="10"/>
+      <c r="C222" s="16"/>
       <c r="D222" s="5"/>
       <c r="E222" s="6"/>
       <c r="F222" s="7"/>
@@ -5461,7 +5504,7 @@
     <row r="223" spans="1:18">
       <c r="A223" s="8"/>
       <c r="B223" s="10"/>
-      <c r="C223" s="10"/>
+      <c r="C223" s="16"/>
       <c r="D223" s="5"/>
       <c r="E223" s="6"/>
       <c r="F223" s="7"/>
@@ -5481,7 +5524,7 @@
     <row r="224" spans="1:18">
       <c r="A224" s="8"/>
       <c r="B224" s="10"/>
-      <c r="C224" s="10"/>
+      <c r="C224" s="16"/>
       <c r="D224" s="5"/>
       <c r="E224" s="6"/>
       <c r="F224" s="7"/>
@@ -5501,7 +5544,7 @@
     <row r="225" spans="1:18">
       <c r="A225" s="8"/>
       <c r="B225" s="10"/>
-      <c r="C225" s="10"/>
+      <c r="C225" s="16"/>
       <c r="D225" s="5"/>
       <c r="E225" s="6"/>
       <c r="F225" s="7"/>
@@ -5521,7 +5564,7 @@
     <row r="226" spans="1:18">
       <c r="A226" s="8"/>
       <c r="B226" s="10"/>
-      <c r="C226" s="10"/>
+      <c r="C226" s="16"/>
       <c r="D226" s="5"/>
       <c r="E226" s="6"/>
       <c r="F226" s="7"/>
@@ -5541,7 +5584,7 @@
     <row r="227" spans="1:18">
       <c r="A227" s="8"/>
       <c r="B227" s="10"/>
-      <c r="C227" s="10"/>
+      <c r="C227" s="16"/>
       <c r="D227" s="5"/>
       <c r="E227" s="6"/>
       <c r="F227" s="7"/>
@@ -5561,7 +5604,7 @@
     <row r="228" spans="1:18">
       <c r="A228" s="8"/>
       <c r="B228" s="10"/>
-      <c r="C228" s="10"/>
+      <c r="C228" s="16"/>
       <c r="D228" s="5"/>
       <c r="E228" s="6"/>
       <c r="F228" s="7"/>
@@ -5581,7 +5624,7 @@
     <row r="229" spans="1:18">
       <c r="A229" s="8"/>
       <c r="B229" s="10"/>
-      <c r="C229" s="10"/>
+      <c r="C229" s="16"/>
       <c r="D229" s="5"/>
       <c r="E229" s="6"/>
       <c r="F229" s="7"/>
@@ -5601,7 +5644,7 @@
     <row r="230" spans="1:18">
       <c r="A230" s="8"/>
       <c r="B230" s="10"/>
-      <c r="C230" s="10"/>
+      <c r="C230" s="16"/>
       <c r="D230" s="5"/>
       <c r="E230" s="6"/>
       <c r="F230" s="7"/>
@@ -5621,7 +5664,7 @@
     <row r="231" spans="1:18">
       <c r="A231" s="8"/>
       <c r="B231" s="10"/>
-      <c r="C231" s="10"/>
+      <c r="C231" s="16"/>
       <c r="D231" s="5"/>
       <c r="E231" s="6"/>
       <c r="F231" s="7"/>
@@ -5641,7 +5684,7 @@
     <row r="232" spans="1:18">
       <c r="A232" s="8"/>
       <c r="B232" s="10"/>
-      <c r="C232" s="10"/>
+      <c r="C232" s="16"/>
       <c r="D232" s="5"/>
       <c r="E232" s="6"/>
       <c r="F232" s="7"/>
@@ -5661,7 +5704,7 @@
     <row r="233" spans="1:18">
       <c r="A233" s="8"/>
       <c r="B233" s="10"/>
-      <c r="C233" s="10"/>
+      <c r="C233" s="16"/>
       <c r="D233" s="5"/>
       <c r="E233" s="6"/>
       <c r="F233" s="7"/>
@@ -5681,7 +5724,7 @@
     <row r="234" spans="1:18">
       <c r="A234" s="8"/>
       <c r="B234" s="10"/>
-      <c r="C234" s="10"/>
+      <c r="C234" s="16"/>
       <c r="D234" s="5"/>
       <c r="E234" s="6"/>
       <c r="F234" s="7"/>
@@ -5701,7 +5744,7 @@
     <row r="235" spans="1:18">
       <c r="A235" s="8"/>
       <c r="B235" s="10"/>
-      <c r="C235" s="10"/>
+      <c r="C235" s="16"/>
       <c r="D235" s="5"/>
       <c r="E235" s="6"/>
       <c r="F235" s="7"/>
@@ -5721,7 +5764,7 @@
     <row r="236" spans="1:18">
       <c r="A236" s="8"/>
       <c r="B236" s="10"/>
-      <c r="C236" s="10"/>
+      <c r="C236" s="16"/>
       <c r="D236" s="5"/>
       <c r="E236" s="6"/>
       <c r="F236" s="7"/>
@@ -5741,7 +5784,7 @@
     <row r="237" spans="1:18">
       <c r="A237" s="8"/>
       <c r="B237" s="10"/>
-      <c r="C237" s="10"/>
+      <c r="C237" s="16"/>
       <c r="D237" s="5"/>
       <c r="E237" s="6"/>
       <c r="F237" s="7"/>
@@ -5761,7 +5804,7 @@
     <row r="238" spans="1:18">
       <c r="A238" s="8"/>
       <c r="B238" s="10"/>
-      <c r="C238" s="10"/>
+      <c r="C238" s="16"/>
       <c r="D238" s="5"/>
       <c r="E238" s="6"/>
       <c r="F238" s="7"/>
@@ -5781,7 +5824,7 @@
     <row r="239" spans="1:18">
       <c r="A239" s="8"/>
       <c r="B239" s="10"/>
-      <c r="C239" s="10"/>
+      <c r="C239" s="16"/>
       <c r="D239" s="5"/>
       <c r="E239" s="6"/>
       <c r="F239" s="7"/>
@@ -5801,7 +5844,7 @@
     <row r="240" spans="1:18">
       <c r="A240" s="8"/>
       <c r="B240" s="10"/>
-      <c r="C240" s="10"/>
+      <c r="C240" s="16"/>
       <c r="D240" s="5"/>
       <c r="E240" s="6"/>
       <c r="F240" s="7"/>
@@ -5821,7 +5864,7 @@
     <row r="241" spans="1:18">
       <c r="A241" s="8"/>
       <c r="B241" s="10"/>
-      <c r="C241" s="10"/>
+      <c r="C241" s="16"/>
       <c r="D241" s="5"/>
       <c r="E241" s="6"/>
       <c r="F241" s="7"/>
@@ -5841,7 +5884,7 @@
     <row r="242" spans="1:18">
       <c r="A242" s="8"/>
       <c r="B242" s="10"/>
-      <c r="C242" s="10"/>
+      <c r="C242" s="16"/>
       <c r="D242" s="5"/>
       <c r="E242" s="6"/>
       <c r="F242" s="7"/>
@@ -5861,7 +5904,7 @@
     <row r="243" spans="1:18">
       <c r="A243" s="8"/>
       <c r="B243" s="10"/>
-      <c r="C243" s="10"/>
+      <c r="C243" s="16"/>
       <c r="D243" s="5"/>
       <c r="E243" s="6"/>
       <c r="F243" s="7"/>
@@ -5881,7 +5924,7 @@
     <row r="244" spans="1:18">
       <c r="A244" s="8"/>
       <c r="B244" s="10"/>
-      <c r="C244" s="10"/>
+      <c r="C244" s="16"/>
       <c r="D244" s="5"/>
       <c r="E244" s="6"/>
       <c r="F244" s="7"/>
@@ -5901,7 +5944,7 @@
     <row r="245" spans="1:18">
       <c r="A245" s="8"/>
       <c r="B245" s="10"/>
-      <c r="C245" s="10"/>
+      <c r="C245" s="16"/>
       <c r="D245" s="5"/>
       <c r="E245" s="6"/>
       <c r="F245" s="7"/>
@@ -5921,7 +5964,7 @@
     <row r="246" spans="1:18">
       <c r="A246" s="8"/>
       <c r="B246" s="10"/>
-      <c r="C246" s="10"/>
+      <c r="C246" s="16"/>
       <c r="D246" s="5"/>
       <c r="E246" s="6"/>
       <c r="F246" s="7"/>
@@ -5941,7 +5984,7 @@
     <row r="247" spans="1:18">
       <c r="A247" s="8"/>
       <c r="B247" s="10"/>
-      <c r="C247" s="10"/>
+      <c r="C247" s="16"/>
       <c r="D247" s="5"/>
       <c r="E247" s="6"/>
       <c r="F247" s="7"/>
@@ -5961,7 +6004,7 @@
     <row r="248" spans="1:18">
       <c r="A248" s="8"/>
       <c r="B248" s="10"/>
-      <c r="C248" s="10"/>
+      <c r="C248" s="16"/>
       <c r="D248" s="5"/>
       <c r="E248" s="6"/>
       <c r="F248" s="7"/>
@@ -5981,7 +6024,7 @@
     <row r="249" spans="1:18">
       <c r="A249" s="8"/>
       <c r="B249" s="10"/>
-      <c r="C249" s="10"/>
+      <c r="C249" s="16"/>
       <c r="D249" s="5"/>
       <c r="E249" s="6"/>
       <c r="F249" s="7"/>
@@ -6001,7 +6044,7 @@
     <row r="250" spans="1:18">
       <c r="A250" s="8"/>
       <c r="B250" s="10"/>
-      <c r="C250" s="10"/>
+      <c r="C250" s="16"/>
       <c r="D250" s="5"/>
       <c r="E250" s="6"/>
       <c r="F250" s="7"/>
@@ -6021,7 +6064,7 @@
     <row r="251" spans="1:18">
       <c r="A251" s="8"/>
       <c r="B251" s="10"/>
-      <c r="C251" s="10"/>
+      <c r="C251" s="16"/>
       <c r="D251" s="5"/>
       <c r="E251" s="6"/>
       <c r="F251" s="7"/>
@@ -6041,7 +6084,7 @@
     <row r="252" spans="1:18">
       <c r="A252" s="8"/>
       <c r="B252" s="10"/>
-      <c r="C252" s="10"/>
+      <c r="C252" s="16"/>
       <c r="D252" s="5"/>
       <c r="E252" s="6"/>
       <c r="F252" s="7"/>
@@ -6061,7 +6104,7 @@
     <row r="253" spans="1:18">
       <c r="A253" s="8"/>
       <c r="B253" s="10"/>
-      <c r="C253" s="10"/>
+      <c r="C253" s="16"/>
       <c r="D253" s="5"/>
       <c r="E253" s="6"/>
       <c r="F253" s="7"/>
@@ -6081,7 +6124,7 @@
     <row r="254" spans="1:18">
       <c r="A254" s="8"/>
       <c r="B254" s="10"/>
-      <c r="C254" s="10"/>
+      <c r="C254" s="16"/>
       <c r="D254" s="5"/>
       <c r="E254" s="6"/>
       <c r="F254" s="7"/>
@@ -6101,7 +6144,7 @@
     <row r="255" spans="1:18">
       <c r="A255" s="8"/>
       <c r="B255" s="10"/>
-      <c r="C255" s="10"/>
+      <c r="C255" s="16"/>
       <c r="D255" s="5"/>
       <c r="E255" s="6"/>
       <c r="F255" s="7"/>
@@ -6121,7 +6164,7 @@
     <row r="256" spans="1:18">
       <c r="A256" s="8"/>
       <c r="B256" s="10"/>
-      <c r="C256" s="10"/>
+      <c r="C256" s="16"/>
       <c r="D256" s="5"/>
       <c r="E256" s="6"/>
       <c r="F256" s="7"/>
@@ -6141,7 +6184,7 @@
     <row r="257" spans="1:18">
       <c r="A257" s="8"/>
       <c r="B257" s="10"/>
-      <c r="C257" s="10"/>
+      <c r="C257" s="16"/>
       <c r="D257" s="5"/>
       <c r="E257" s="6"/>
       <c r="F257" s="7"/>
@@ -6161,7 +6204,7 @@
     <row r="258" spans="1:18">
       <c r="A258" s="8"/>
       <c r="B258" s="10"/>
-      <c r="C258" s="10"/>
+      <c r="C258" s="16"/>
       <c r="D258" s="5"/>
       <c r="E258" s="6"/>
       <c r="F258" s="7"/>
@@ -6181,7 +6224,7 @@
     <row r="259" spans="1:18">
       <c r="A259" s="8"/>
       <c r="B259" s="10"/>
-      <c r="C259" s="10"/>
+      <c r="C259" s="16"/>
       <c r="D259" s="5"/>
       <c r="E259" s="6"/>
       <c r="F259" s="7"/>
@@ -6201,7 +6244,7 @@
     <row r="260" spans="1:18">
       <c r="A260" s="8"/>
       <c r="B260" s="10"/>
-      <c r="C260" s="10"/>
+      <c r="C260" s="16"/>
       <c r="D260" s="5"/>
       <c r="E260" s="6"/>
       <c r="F260" s="7"/>
@@ -6221,7 +6264,7 @@
     <row r="261" spans="1:18">
       <c r="A261" s="8"/>
       <c r="B261" s="10"/>
-      <c r="C261" s="10"/>
+      <c r="C261" s="16"/>
       <c r="D261" s="5"/>
       <c r="E261" s="6"/>
       <c r="F261" s="7"/>
@@ -6241,7 +6284,7 @@
     <row r="262" spans="1:18">
       <c r="A262" s="8"/>
       <c r="B262" s="10"/>
-      <c r="C262" s="10"/>
+      <c r="C262" s="16"/>
       <c r="D262" s="5"/>
       <c r="E262" s="6"/>
       <c r="F262" s="7"/>
@@ -6261,7 +6304,7 @@
     <row r="263" spans="1:18">
       <c r="A263" s="8"/>
       <c r="B263" s="10"/>
-      <c r="C263" s="10"/>
+      <c r="C263" s="16"/>
       <c r="D263" s="5"/>
       <c r="E263" s="6"/>
       <c r="F263" s="7"/>
@@ -6281,7 +6324,7 @@
     <row r="264" spans="1:18">
       <c r="A264" s="8"/>
       <c r="B264" s="10"/>
-      <c r="C264" s="10"/>
+      <c r="C264" s="16"/>
       <c r="D264" s="5"/>
       <c r="E264" s="6"/>
       <c r="F264" s="7"/>
@@ -6301,7 +6344,7 @@
     <row r="265" spans="1:18">
       <c r="A265" s="8"/>
       <c r="B265" s="10"/>
-      <c r="C265" s="10"/>
+      <c r="C265" s="16"/>
       <c r="D265" s="5"/>
       <c r="E265" s="6"/>
       <c r="F265" s="7"/>
@@ -6321,7 +6364,7 @@
     <row r="266" spans="1:18">
       <c r="A266" s="8"/>
       <c r="B266" s="10"/>
-      <c r="C266" s="10"/>
+      <c r="C266" s="16"/>
       <c r="D266" s="5"/>
       <c r="E266" s="6"/>
       <c r="F266" s="7"/>
@@ -6341,7 +6384,7 @@
     <row r="267" spans="1:18">
       <c r="A267" s="8"/>
       <c r="B267" s="10"/>
-      <c r="C267" s="10"/>
+      <c r="C267" s="16"/>
       <c r="D267" s="5"/>
       <c r="E267" s="6"/>
       <c r="F267" s="7"/>
@@ -6361,7 +6404,7 @@
     <row r="268" spans="1:18">
       <c r="A268" s="8"/>
       <c r="B268" s="10"/>
-      <c r="C268" s="10"/>
+      <c r="C268" s="16"/>
       <c r="D268" s="5"/>
       <c r="E268" s="6"/>
       <c r="F268" s="7"/>
@@ -6381,7 +6424,7 @@
     <row r="269" spans="1:18">
       <c r="A269" s="8"/>
       <c r="B269" s="10"/>
-      <c r="C269" s="10"/>
+      <c r="C269" s="16"/>
       <c r="D269" s="5"/>
       <c r="E269" s="6"/>
       <c r="F269" s="7"/>
@@ -6401,7 +6444,7 @@
     <row r="270" spans="1:18">
       <c r="A270" s="8"/>
       <c r="B270" s="10"/>
-      <c r="C270" s="10"/>
+      <c r="C270" s="16"/>
       <c r="D270" s="5"/>
       <c r="E270" s="6"/>
       <c r="F270" s="7"/>
@@ -6421,7 +6464,7 @@
     <row r="271" spans="1:18">
       <c r="A271" s="8"/>
       <c r="B271" s="10"/>
-      <c r="C271" s="10"/>
+      <c r="C271" s="16"/>
       <c r="D271" s="5"/>
       <c r="E271" s="6"/>
       <c r="F271" s="7"/>
@@ -6441,7 +6484,7 @@
     <row r="272" spans="1:18">
       <c r="A272" s="8"/>
       <c r="B272" s="10"/>
-      <c r="C272" s="10"/>
+      <c r="C272" s="16"/>
       <c r="D272" s="5"/>
       <c r="E272" s="6"/>
       <c r="F272" s="7"/>
@@ -6461,7 +6504,7 @@
     <row r="273" spans="1:18">
       <c r="A273" s="8"/>
       <c r="B273" s="10"/>
-      <c r="C273" s="10"/>
+      <c r="C273" s="16"/>
       <c r="D273" s="5"/>
       <c r="E273" s="6"/>
       <c r="F273" s="7"/>
@@ -6481,7 +6524,7 @@
     <row r="274" spans="1:18">
       <c r="A274" s="8"/>
       <c r="B274" s="10"/>
-      <c r="C274" s="10"/>
+      <c r="C274" s="16"/>
       <c r="D274" s="5"/>
       <c r="E274" s="6"/>
       <c r="F274" s="7"/>
@@ -6501,7 +6544,7 @@
     <row r="275" spans="1:18">
       <c r="A275" s="8"/>
       <c r="B275" s="10"/>
-      <c r="C275" s="10"/>
+      <c r="C275" s="16"/>
       <c r="D275" s="5"/>
       <c r="E275" s="6"/>
       <c r="F275" s="7"/>
@@ -6521,7 +6564,7 @@
     <row r="276" spans="1:18">
       <c r="A276" s="8"/>
       <c r="B276" s="10"/>
-      <c r="C276" s="10"/>
+      <c r="C276" s="16"/>
       <c r="D276" s="5"/>
       <c r="E276" s="6"/>
       <c r="F276" s="7"/>
@@ -6541,7 +6584,7 @@
     <row r="277" spans="1:18">
       <c r="A277" s="8"/>
       <c r="B277" s="10"/>
-      <c r="C277" s="10"/>
+      <c r="C277" s="16"/>
       <c r="D277" s="5"/>
       <c r="E277" s="6"/>
       <c r="F277" s="7"/>
@@ -6561,7 +6604,7 @@
     <row r="278" spans="1:18">
       <c r="A278" s="8"/>
       <c r="B278" s="10"/>
-      <c r="C278" s="10"/>
+      <c r="C278" s="16"/>
       <c r="D278" s="5"/>
       <c r="E278" s="6"/>
       <c r="F278" s="7"/>
@@ -6581,7 +6624,7 @@
     <row r="279" spans="1:18">
       <c r="A279" s="8"/>
       <c r="B279" s="10"/>
-      <c r="C279" s="10"/>
+      <c r="C279" s="16"/>
       <c r="D279" s="5"/>
       <c r="E279" s="6"/>
       <c r="F279" s="7"/>
@@ -6601,7 +6644,7 @@
     <row r="280" spans="1:18">
       <c r="A280" s="8"/>
       <c r="B280" s="10"/>
-      <c r="C280" s="10"/>
+      <c r="C280" s="16"/>
       <c r="D280" s="5"/>
       <c r="E280" s="6"/>
       <c r="F280" s="7"/>
@@ -6621,7 +6664,7 @@
     <row r="281" spans="1:18">
       <c r="A281" s="8"/>
       <c r="B281" s="10"/>
-      <c r="C281" s="10"/>
+      <c r="C281" s="16"/>
       <c r="D281" s="5"/>
       <c r="E281" s="6"/>
       <c r="F281" s="7"/>
@@ -6641,7 +6684,7 @@
     <row r="282" spans="1:18">
       <c r="A282" s="8"/>
       <c r="B282" s="10"/>
-      <c r="C282" s="10"/>
+      <c r="C282" s="16"/>
       <c r="D282" s="5"/>
       <c r="E282" s="6"/>
       <c r="F282" s="7"/>
@@ -6661,7 +6704,7 @@
     <row r="283" spans="1:18">
       <c r="A283" s="8"/>
       <c r="B283" s="10"/>
-      <c r="C283" s="10"/>
+      <c r="C283" s="16"/>
       <c r="D283" s="5"/>
       <c r="E283" s="6"/>
       <c r="F283" s="7"/>
@@ -6681,7 +6724,7 @@
     <row r="284" spans="1:18">
       <c r="A284" s="8"/>
       <c r="B284" s="10"/>
-      <c r="C284" s="10"/>
+      <c r="C284" s="16"/>
       <c r="D284" s="5"/>
       <c r="E284" s="6"/>
       <c r="F284" s="7"/>
@@ -6701,7 +6744,7 @@
     <row r="285" spans="1:18">
       <c r="A285" s="8"/>
       <c r="B285" s="10"/>
-      <c r="C285" s="10"/>
+      <c r="C285" s="16"/>
       <c r="D285" s="5"/>
       <c r="E285" s="6"/>
       <c r="F285" s="7"/>
@@ -6721,7 +6764,7 @@
     <row r="286" spans="1:18">
       <c r="A286" s="8"/>
       <c r="B286" s="10"/>
-      <c r="C286" s="10"/>
+      <c r="C286" s="16"/>
       <c r="D286" s="5"/>
       <c r="E286" s="6"/>
       <c r="F286" s="7"/>
@@ -6741,7 +6784,7 @@
     <row r="287" spans="1:18">
       <c r="A287" s="8"/>
       <c r="B287" s="10"/>
-      <c r="C287" s="10"/>
+      <c r="C287" s="16"/>
       <c r="D287" s="5"/>
       <c r="E287" s="6"/>
       <c r="F287" s="7"/>
@@ -6761,7 +6804,7 @@
     <row r="288" spans="1:18">
       <c r="A288" s="8"/>
       <c r="B288" s="10"/>
-      <c r="C288" s="10"/>
+      <c r="C288" s="16"/>
       <c r="D288" s="5"/>
       <c r="E288" s="6"/>
       <c r="F288" s="7"/>
@@ -6781,7 +6824,7 @@
     <row r="289" spans="1:18">
       <c r="A289" s="8"/>
       <c r="B289" s="10"/>
-      <c r="C289" s="10"/>
+      <c r="C289" s="16"/>
       <c r="D289" s="5"/>
       <c r="E289" s="6"/>
       <c r="F289" s="7"/>
@@ -6801,7 +6844,7 @@
     <row r="290" spans="1:18">
       <c r="A290" s="8"/>
       <c r="B290" s="10"/>
-      <c r="C290" s="10"/>
+      <c r="C290" s="16"/>
       <c r="D290" s="5"/>
       <c r="E290" s="6"/>
       <c r="F290" s="7"/>
@@ -6821,7 +6864,7 @@
     <row r="291" spans="1:18">
       <c r="A291" s="8"/>
       <c r="B291" s="10"/>
-      <c r="C291" s="10"/>
+      <c r="C291" s="16"/>
       <c r="D291" s="5"/>
       <c r="E291" s="6"/>
       <c r="F291" s="7"/>
@@ -6841,7 +6884,7 @@
     <row r="292" spans="1:18">
       <c r="A292" s="8"/>
       <c r="B292" s="10"/>
-      <c r="C292" s="10"/>
+      <c r="C292" s="16"/>
       <c r="D292" s="5"/>
       <c r="E292" s="6"/>
       <c r="F292" s="7"/>
@@ -6861,7 +6904,7 @@
     <row r="293" spans="1:18">
       <c r="A293" s="8"/>
       <c r="B293" s="10"/>
-      <c r="C293" s="10"/>
+      <c r="C293" s="16"/>
       <c r="D293" s="5"/>
       <c r="E293" s="6"/>
       <c r="F293" s="7"/>
@@ -6881,7 +6924,7 @@
     <row r="294" spans="1:18">
       <c r="A294" s="8"/>
       <c r="B294" s="10"/>
-      <c r="C294" s="10"/>
+      <c r="C294" s="16"/>
       <c r="D294" s="5"/>
       <c r="E294" s="6"/>
       <c r="F294" s="7"/>
@@ -6901,7 +6944,7 @@
     <row r="295" spans="1:18">
       <c r="A295" s="8"/>
       <c r="B295" s="10"/>
-      <c r="C295" s="10"/>
+      <c r="C295" s="16"/>
       <c r="D295" s="5"/>
       <c r="E295" s="6"/>
       <c r="F295" s="7"/>
@@ -6921,7 +6964,7 @@
     <row r="296" spans="1:18">
       <c r="A296" s="8"/>
       <c r="B296" s="10"/>
-      <c r="C296" s="10"/>
+      <c r="C296" s="16"/>
       <c r="D296" s="5"/>
       <c r="E296" s="6"/>
       <c r="F296" s="7"/>
@@ -6941,7 +6984,7 @@
     <row r="297" spans="1:18">
       <c r="A297" s="8"/>
       <c r="B297" s="10"/>
-      <c r="C297" s="10"/>
+      <c r="C297" s="16"/>
       <c r="D297" s="5"/>
       <c r="E297" s="6"/>
       <c r="F297" s="7"/>
@@ -6961,7 +7004,7 @@
     <row r="298" spans="1:18">
       <c r="A298" s="8"/>
       <c r="B298" s="10"/>
-      <c r="C298" s="10"/>
+      <c r="C298" s="16"/>
       <c r="D298" s="5"/>
       <c r="E298" s="6"/>
       <c r="F298" s="7"/>
@@ -6981,7 +7024,7 @@
     <row r="299" spans="1:18">
       <c r="A299" s="8"/>
       <c r="B299" s="10"/>
-      <c r="C299" s="10"/>
+      <c r="C299" s="16"/>
       <c r="D299" s="5"/>
       <c r="E299" s="6"/>
       <c r="F299" s="7"/>
@@ -7001,7 +7044,7 @@
     <row r="300" spans="1:18">
       <c r="A300" s="8"/>
       <c r="B300" s="10"/>
-      <c r="C300" s="10"/>
+      <c r="C300" s="16"/>
       <c r="D300" s="5"/>
       <c r="E300" s="6"/>
       <c r="F300" s="7"/>
@@ -7021,7 +7064,7 @@
     <row r="301" spans="1:18">
       <c r="A301" s="8"/>
       <c r="B301" s="10"/>
-      <c r="C301" s="10"/>
+      <c r="C301" s="16"/>
       <c r="D301" s="5"/>
       <c r="E301" s="6"/>
       <c r="F301" s="7"/>
@@ -7041,7 +7084,7 @@
     <row r="302" spans="1:18">
       <c r="A302" s="8"/>
       <c r="B302" s="10"/>
-      <c r="C302" s="10"/>
+      <c r="C302" s="16"/>
       <c r="D302" s="5"/>
       <c r="E302" s="6"/>
       <c r="F302" s="7"/>
@@ -7061,7 +7104,7 @@
     <row r="303" spans="1:18">
       <c r="A303" s="8"/>
       <c r="B303" s="10"/>
-      <c r="C303" s="10"/>
+      <c r="C303" s="16"/>
       <c r="D303" s="5"/>
       <c r="E303" s="6"/>
       <c r="F303" s="7"/>
@@ -7081,7 +7124,7 @@
     <row r="304" spans="1:18">
       <c r="A304" s="8"/>
       <c r="B304" s="10"/>
-      <c r="C304" s="10"/>
+      <c r="C304" s="16"/>
       <c r="D304" s="5"/>
       <c r="E304" s="6"/>
       <c r="F304" s="7"/>
@@ -7101,7 +7144,7 @@
     <row r="305" spans="1:18">
       <c r="A305" s="8"/>
       <c r="B305" s="10"/>
-      <c r="C305" s="10"/>
+      <c r="C305" s="16"/>
       <c r="D305" s="5"/>
       <c r="E305" s="6"/>
       <c r="F305" s="7"/>
@@ -7121,7 +7164,7 @@
     <row r="306" spans="1:18">
       <c r="A306" s="8"/>
       <c r="B306" s="10"/>
-      <c r="C306" s="10"/>
+      <c r="C306" s="16"/>
       <c r="D306" s="5"/>
       <c r="E306" s="6"/>
       <c r="F306" s="7"/>
@@ -7141,7 +7184,7 @@
     <row r="307" spans="1:18">
       <c r="A307" s="8"/>
       <c r="B307" s="10"/>
-      <c r="C307" s="10"/>
+      <c r="C307" s="16"/>
       <c r="D307" s="5"/>
       <c r="E307" s="6"/>
       <c r="F307" s="7"/>
@@ -7161,7 +7204,7 @@
     <row r="308" spans="1:18">
       <c r="A308" s="8"/>
       <c r="B308" s="10"/>
-      <c r="C308" s="10"/>
+      <c r="C308" s="16"/>
       <c r="D308" s="5"/>
       <c r="E308" s="6"/>
       <c r="F308" s="7"/>
@@ -7181,7 +7224,7 @@
     <row r="309" spans="1:18">
       <c r="A309" s="8"/>
       <c r="B309" s="10"/>
-      <c r="C309" s="10"/>
+      <c r="C309" s="16"/>
       <c r="D309" s="5"/>
       <c r="E309" s="6"/>
       <c r="F309" s="7"/>
@@ -7201,7 +7244,7 @@
     <row r="310" spans="1:18">
       <c r="A310" s="8"/>
       <c r="B310" s="10"/>
-      <c r="C310" s="10"/>
+      <c r="C310" s="16"/>
       <c r="D310" s="5"/>
       <c r="E310" s="6"/>
       <c r="F310" s="7"/>
@@ -7221,7 +7264,7 @@
     <row r="311" spans="1:18">
       <c r="A311" s="8"/>
       <c r="B311" s="10"/>
-      <c r="C311" s="10"/>
+      <c r="C311" s="16"/>
       <c r="D311" s="5"/>
       <c r="E311" s="6"/>
       <c r="F311" s="7"/>
@@ -7241,7 +7284,7 @@
     <row r="312" spans="1:18">
       <c r="A312" s="8"/>
       <c r="B312" s="10"/>
-      <c r="C312" s="10"/>
+      <c r="C312" s="16"/>
       <c r="D312" s="5"/>
       <c r="E312" s="6"/>
       <c r="F312" s="7"/>
@@ -7261,7 +7304,7 @@
     <row r="313" spans="1:18">
       <c r="A313" s="8"/>
       <c r="B313" s="10"/>
-      <c r="C313" s="10"/>
+      <c r="C313" s="16"/>
       <c r="D313" s="5"/>
       <c r="E313" s="6"/>
       <c r="F313" s="7"/>
@@ -7281,7 +7324,7 @@
     <row r="314" spans="1:18">
       <c r="A314" s="8"/>
       <c r="B314" s="10"/>
-      <c r="C314" s="10"/>
+      <c r="C314" s="16"/>
       <c r="D314" s="5"/>
       <c r="E314" s="6"/>
       <c r="F314" s="7"/>
@@ -7301,7 +7344,7 @@
     <row r="315" spans="1:18">
       <c r="A315" s="8"/>
       <c r="B315" s="10"/>
-      <c r="C315" s="10"/>
+      <c r="C315" s="16"/>
       <c r="D315" s="5"/>
       <c r="E315" s="6"/>
       <c r="F315" s="7"/>
@@ -7321,7 +7364,7 @@
     <row r="316" spans="1:18">
       <c r="A316" s="8"/>
       <c r="B316" s="10"/>
-      <c r="C316" s="10"/>
+      <c r="C316" s="16"/>
       <c r="D316" s="5"/>
       <c r="E316" s="6"/>
       <c r="F316" s="7"/>
@@ -7341,7 +7384,7 @@
     <row r="317" spans="1:18">
       <c r="A317" s="8"/>
       <c r="B317" s="10"/>
-      <c r="C317" s="10"/>
+      <c r="C317" s="16"/>
       <c r="D317" s="5"/>
       <c r="E317" s="6"/>
       <c r="F317" s="7"/>
@@ -7361,7 +7404,7 @@
     <row r="318" spans="1:18">
       <c r="A318" s="8"/>
       <c r="B318" s="10"/>
-      <c r="C318" s="10"/>
+      <c r="C318" s="16"/>
       <c r="D318" s="5"/>
       <c r="E318" s="6"/>
       <c r="F318" s="7"/>
@@ -7381,7 +7424,7 @@
     <row r="319" spans="1:18">
       <c r="A319" s="8"/>
       <c r="B319" s="10"/>
-      <c r="C319" s="10"/>
+      <c r="C319" s="16"/>
       <c r="D319" s="5"/>
       <c r="E319" s="6"/>
       <c r="F319" s="7"/>
@@ -7401,7 +7444,7 @@
     <row r="320" spans="1:18">
       <c r="A320" s="8"/>
       <c r="B320" s="10"/>
-      <c r="C320" s="10"/>
+      <c r="C320" s="16"/>
       <c r="D320" s="5"/>
       <c r="E320" s="6"/>
       <c r="F320" s="7"/>
@@ -7421,7 +7464,7 @@
     <row r="321" spans="1:18">
       <c r="A321" s="8"/>
       <c r="B321" s="10"/>
-      <c r="C321" s="10"/>
+      <c r="C321" s="16"/>
       <c r="D321" s="5"/>
       <c r="E321" s="6"/>
       <c r="F321" s="7"/>
@@ -7441,7 +7484,7 @@
     <row r="322" spans="1:18">
       <c r="A322" s="8"/>
       <c r="B322" s="10"/>
-      <c r="C322" s="10"/>
+      <c r="C322" s="16"/>
       <c r="D322" s="5"/>
       <c r="E322" s="6"/>
       <c r="F322" s="7"/>
@@ -7461,7 +7504,7 @@
     <row r="323" spans="1:18">
       <c r="A323" s="8"/>
       <c r="B323" s="10"/>
-      <c r="C323" s="10"/>
+      <c r="C323" s="16"/>
       <c r="D323" s="5"/>
       <c r="E323" s="6"/>
       <c r="F323" s="7"/>
@@ -7481,7 +7524,7 @@
     <row r="324" spans="1:18">
       <c r="A324" s="8"/>
       <c r="B324" s="10"/>
-      <c r="C324" s="10"/>
+      <c r="C324" s="16"/>
       <c r="D324" s="5"/>
       <c r="E324" s="6"/>
       <c r="F324" s="7"/>
@@ -7501,7 +7544,7 @@
     <row r="325" spans="1:18">
       <c r="A325" s="8"/>
       <c r="B325" s="10"/>
-      <c r="C325" s="10"/>
+      <c r="C325" s="16"/>
       <c r="D325" s="5"/>
       <c r="E325" s="6"/>
       <c r="F325" s="7"/>
@@ -7521,7 +7564,7 @@
     <row r="326" spans="1:18">
       <c r="A326" s="8"/>
       <c r="B326" s="10"/>
-      <c r="C326" s="10"/>
+      <c r="C326" s="16"/>
       <c r="D326" s="5"/>
       <c r="E326" s="6"/>
       <c r="F326" s="7"/>
@@ -7541,7 +7584,7 @@
     <row r="327" spans="1:18">
       <c r="A327" s="8"/>
       <c r="B327" s="10"/>
-      <c r="C327" s="10"/>
+      <c r="C327" s="16"/>
       <c r="D327" s="5"/>
       <c r="E327" s="6"/>
       <c r="F327" s="7"/>
@@ -7561,7 +7604,7 @@
     <row r="328" spans="1:18">
       <c r="A328" s="8"/>
       <c r="B328" s="10"/>
-      <c r="C328" s="10"/>
+      <c r="C328" s="16"/>
       <c r="D328" s="5"/>
       <c r="E328" s="6"/>
       <c r="F328" s="7"/>
@@ -7581,7 +7624,7 @@
     <row r="329" spans="1:18">
       <c r="A329" s="8"/>
       <c r="B329" s="10"/>
-      <c r="C329" s="10"/>
+      <c r="C329" s="16"/>
       <c r="D329" s="5"/>
       <c r="E329" s="6"/>
       <c r="F329" s="7"/>
@@ -7601,7 +7644,7 @@
     <row r="330" spans="1:18">
       <c r="A330" s="8"/>
       <c r="B330" s="10"/>
-      <c r="C330" s="10"/>
+      <c r="C330" s="16"/>
       <c r="D330" s="5"/>
       <c r="E330" s="6"/>
       <c r="F330" s="7"/>
@@ -7621,7 +7664,7 @@
     <row r="331" spans="1:18">
       <c r="A331" s="8"/>
       <c r="B331" s="10"/>
-      <c r="C331" s="10"/>
+      <c r="C331" s="16"/>
       <c r="D331" s="5"/>
       <c r="E331" s="6"/>
       <c r="F331" s="7"/>
@@ -7641,7 +7684,7 @@
     <row r="332" spans="1:18">
       <c r="A332" s="8"/>
       <c r="B332" s="10"/>
-      <c r="C332" s="10"/>
+      <c r="C332" s="16"/>
       <c r="D332" s="5"/>
       <c r="E332" s="6"/>
       <c r="F332" s="7"/>
@@ -7661,7 +7704,7 @@
     <row r="333" spans="1:18">
       <c r="A333" s="8"/>
       <c r="B333" s="10"/>
-      <c r="C333" s="10"/>
+      <c r="C333" s="16"/>
       <c r="D333" s="5"/>
       <c r="E333" s="6"/>
       <c r="F333" s="7"/>
@@ -7681,7 +7724,7 @@
     <row r="334" spans="1:18">
       <c r="A334" s="8"/>
       <c r="B334" s="10"/>
-      <c r="C334" s="10"/>
+      <c r="C334" s="16"/>
       <c r="D334" s="5"/>
       <c r="E334" s="6"/>
       <c r="F334" s="7"/>
@@ -7701,7 +7744,7 @@
     <row r="335" spans="1:18">
       <c r="A335" s="8"/>
       <c r="B335" s="10"/>
-      <c r="C335" s="10"/>
+      <c r="C335" s="16"/>
       <c r="D335" s="5"/>
       <c r="E335" s="6"/>
       <c r="F335" s="7"/>
@@ -7721,7 +7764,7 @@
     <row r="336" spans="1:18">
       <c r="A336" s="8"/>
       <c r="B336" s="10"/>
-      <c r="C336" s="10"/>
+      <c r="C336" s="16"/>
       <c r="D336" s="5"/>
       <c r="E336" s="6"/>
       <c r="F336" s="7"/>
@@ -7741,7 +7784,7 @@
     <row r="337" spans="1:18">
       <c r="A337" s="8"/>
       <c r="B337" s="10"/>
-      <c r="C337" s="10"/>
+      <c r="C337" s="16"/>
       <c r="D337" s="5"/>
       <c r="E337" s="6"/>
       <c r="F337" s="7"/>
@@ -7761,7 +7804,7 @@
     <row r="338" spans="1:18">
       <c r="A338" s="8"/>
       <c r="B338" s="10"/>
-      <c r="C338" s="10"/>
+      <c r="C338" s="16"/>
       <c r="D338" s="5"/>
       <c r="E338" s="6"/>
       <c r="F338" s="7"/>
@@ -7781,7 +7824,7 @@
     <row r="339" spans="1:18">
       <c r="A339" s="8"/>
       <c r="B339" s="10"/>
-      <c r="C339" s="10"/>
+      <c r="C339" s="16"/>
       <c r="D339" s="5"/>
       <c r="E339" s="6"/>
       <c r="F339" s="7"/>
@@ -7801,7 +7844,7 @@
     <row r="340" spans="1:18">
       <c r="A340" s="8"/>
       <c r="B340" s="10"/>
-      <c r="C340" s="10"/>
+      <c r="C340" s="16"/>
       <c r="D340" s="5"/>
       <c r="E340" s="6"/>
       <c r="F340" s="7"/>
@@ -7821,7 +7864,7 @@
     <row r="341" spans="1:18">
       <c r="A341" s="8"/>
       <c r="B341" s="10"/>
-      <c r="C341" s="10"/>
+      <c r="C341" s="16"/>
       <c r="D341" s="5"/>
       <c r="E341" s="6"/>
       <c r="F341" s="7"/>
@@ -7841,7 +7884,7 @@
     <row r="342" spans="1:18">
       <c r="A342" s="8"/>
       <c r="B342" s="10"/>
-      <c r="C342" s="10"/>
+      <c r="C342" s="16"/>
       <c r="D342" s="5"/>
       <c r="E342" s="6"/>
       <c r="F342" s="7"/>
@@ -7861,7 +7904,7 @@
     <row r="343" spans="1:18">
       <c r="A343" s="8"/>
       <c r="B343" s="10"/>
-      <c r="C343" s="10"/>
+      <c r="C343" s="16"/>
       <c r="D343" s="5"/>
       <c r="E343" s="6"/>
       <c r="F343" s="7"/>
@@ -7881,7 +7924,7 @@
     <row r="344" spans="1:18">
       <c r="A344" s="8"/>
       <c r="B344" s="10"/>
-      <c r="C344" s="10"/>
+      <c r="C344" s="16"/>
       <c r="D344" s="5"/>
       <c r="E344" s="6"/>
       <c r="F344" s="7"/>
@@ -7901,7 +7944,7 @@
     <row r="345" spans="1:18">
       <c r="A345" s="8"/>
       <c r="B345" s="10"/>
-      <c r="C345" s="10"/>
+      <c r="C345" s="16"/>
       <c r="D345" s="5"/>
       <c r="E345" s="6"/>
       <c r="F345" s="7"/>
@@ -7921,7 +7964,7 @@
     <row r="346" spans="1:18">
       <c r="A346" s="8"/>
       <c r="B346" s="10"/>
-      <c r="C346" s="10"/>
+      <c r="C346" s="16"/>
       <c r="D346" s="5"/>
       <c r="E346" s="6"/>
       <c r="F346" s="7"/>
@@ -7941,7 +7984,7 @@
     <row r="347" spans="1:18">
       <c r="A347" s="8"/>
       <c r="B347" s="10"/>
-      <c r="C347" s="10"/>
+      <c r="C347" s="16"/>
       <c r="D347" s="5"/>
       <c r="E347" s="6"/>
       <c r="F347" s="7"/>
@@ -7961,7 +8004,7 @@
     <row r="348" spans="1:18">
       <c r="A348" s="8"/>
       <c r="B348" s="10"/>
-      <c r="C348" s="10"/>
+      <c r="C348" s="16"/>
       <c r="D348" s="5"/>
       <c r="E348" s="6"/>
       <c r="F348" s="7"/>
@@ -7981,7 +8024,7 @@
     <row r="349" spans="1:18">
       <c r="A349" s="8"/>
       <c r="B349" s="10"/>
-      <c r="C349" s="10"/>
+      <c r="C349" s="16"/>
       <c r="D349" s="5"/>
       <c r="E349" s="6"/>
       <c r="F349" s="7"/>
@@ -8001,7 +8044,7 @@
     <row r="350" spans="1:18">
       <c r="A350" s="8"/>
       <c r="B350" s="10"/>
-      <c r="C350" s="10"/>
+      <c r="C350" s="16"/>
       <c r="D350" s="5"/>
       <c r="E350" s="6"/>
       <c r="F350" s="7"/>
@@ -8021,7 +8064,7 @@
     <row r="351" spans="1:18">
       <c r="A351" s="8"/>
       <c r="B351" s="10"/>
-      <c r="C351" s="10"/>
+      <c r="C351" s="16"/>
       <c r="D351" s="5"/>
       <c r="E351" s="6"/>
       <c r="F351" s="7"/>
@@ -8041,7 +8084,7 @@
     <row r="352" spans="1:18">
       <c r="A352" s="8"/>
       <c r="B352" s="10"/>
-      <c r="C352" s="10"/>
+      <c r="C352" s="16"/>
       <c r="D352" s="5"/>
       <c r="E352" s="6"/>
       <c r="F352" s="7"/>
@@ -8061,7 +8104,7 @@
     <row r="353" spans="1:18">
       <c r="A353" s="8"/>
       <c r="B353" s="10"/>
-      <c r="C353" s="10"/>
+      <c r="C353" s="16"/>
       <c r="D353" s="5"/>
       <c r="E353" s="6"/>
       <c r="F353" s="7"/>
@@ -8081,7 +8124,7 @@
     <row r="354" spans="1:18">
       <c r="A354" s="8"/>
       <c r="B354" s="10"/>
-      <c r="C354" s="10"/>
+      <c r="C354" s="16"/>
       <c r="D354" s="5"/>
       <c r="E354" s="6"/>
       <c r="F354" s="7"/>
@@ -8101,7 +8144,7 @@
     <row r="355" spans="1:18">
       <c r="A355" s="8"/>
       <c r="B355" s="10"/>
-      <c r="C355" s="10"/>
+      <c r="C355" s="16"/>
       <c r="D355" s="5"/>
       <c r="E355" s="6"/>
       <c r="F355" s="7"/>
@@ -8121,7 +8164,7 @@
     <row r="356" spans="1:18">
       <c r="A356" s="8"/>
       <c r="B356" s="10"/>
-      <c r="C356" s="10"/>
+      <c r="C356" s="16"/>
       <c r="D356" s="5"/>
       <c r="E356" s="6"/>
       <c r="F356" s="7"/>
@@ -8141,7 +8184,7 @@
     <row r="357" spans="1:18">
       <c r="A357" s="8"/>
       <c r="B357" s="10"/>
-      <c r="C357" s="10"/>
+      <c r="C357" s="16"/>
       <c r="D357" s="5"/>
       <c r="E357" s="6"/>
       <c r="F357" s="7"/>
@@ -8161,7 +8204,7 @@
     <row r="358" spans="1:18">
       <c r="A358" s="8"/>
       <c r="B358" s="10"/>
-      <c r="C358" s="10"/>
+      <c r="C358" s="16"/>
       <c r="D358" s="5"/>
       <c r="E358" s="6"/>
       <c r="F358" s="7"/>
@@ -8181,7 +8224,7 @@
     <row r="359" spans="1:18">
       <c r="A359" s="8"/>
       <c r="B359" s="10"/>
-      <c r="C359" s="10"/>
+      <c r="C359" s="16"/>
       <c r="D359" s="5"/>
       <c r="E359" s="6"/>
       <c r="F359" s="7"/>
@@ -8201,7 +8244,7 @@
     <row r="360" spans="1:18">
       <c r="A360" s="8"/>
       <c r="B360" s="10"/>
-      <c r="C360" s="10"/>
+      <c r="C360" s="16"/>
       <c r="D360" s="5"/>
       <c r="E360" s="6"/>
       <c r="F360" s="7"/>
@@ -8221,7 +8264,7 @@
     <row r="361" spans="1:18">
       <c r="A361" s="8"/>
       <c r="B361" s="10"/>
-      <c r="C361" s="10"/>
+      <c r="C361" s="16"/>
       <c r="D361" s="5"/>
       <c r="E361" s="6"/>
       <c r="F361" s="7"/>
@@ -8241,7 +8284,7 @@
     <row r="362" spans="1:18">
       <c r="A362" s="8"/>
       <c r="B362" s="10"/>
-      <c r="C362" s="10"/>
+      <c r="C362" s="16"/>
       <c r="D362" s="5"/>
       <c r="E362" s="6"/>
       <c r="F362" s="7"/>
@@ -8261,7 +8304,7 @@
     <row r="363" spans="1:18">
       <c r="A363" s="8"/>
       <c r="B363" s="10"/>
-      <c r="C363" s="10"/>
+      <c r="C363" s="16"/>
       <c r="D363" s="5"/>
       <c r="E363" s="6"/>
       <c r="F363" s="7"/>
@@ -8281,7 +8324,7 @@
     <row r="364" spans="1:18">
       <c r="A364" s="8"/>
       <c r="B364" s="10"/>
-      <c r="C364" s="10"/>
+      <c r="C364" s="16"/>
       <c r="D364" s="5"/>
       <c r="E364" s="6"/>
       <c r="F364" s="7"/>
@@ -8301,7 +8344,7 @@
     <row r="365" spans="1:18">
       <c r="A365" s="8"/>
       <c r="B365" s="10"/>
-      <c r="C365" s="10"/>
+      <c r="C365" s="16"/>
       <c r="D365" s="5"/>
       <c r="E365" s="6"/>
       <c r="F365" s="7"/>
@@ -8321,7 +8364,7 @@
     <row r="366" spans="1:18">
       <c r="A366" s="8"/>
       <c r="B366" s="10"/>
-      <c r="C366" s="10"/>
+      <c r="C366" s="16"/>
       <c r="D366" s="5"/>
       <c r="E366" s="6"/>
       <c r="F366" s="7"/>
@@ -8341,7 +8384,7 @@
     <row r="367" spans="1:18">
       <c r="A367" s="8"/>
       <c r="B367" s="10"/>
-      <c r="C367" s="10"/>
+      <c r="C367" s="16"/>
       <c r="D367" s="5"/>
       <c r="E367" s="6"/>
       <c r="F367" s="7"/>
@@ -8361,7 +8404,7 @@
     <row r="368" spans="1:18">
       <c r="A368" s="8"/>
       <c r="B368" s="10"/>
-      <c r="C368" s="10"/>
+      <c r="C368" s="16"/>
       <c r="D368" s="5"/>
       <c r="E368" s="6"/>
       <c r="F368" s="7"/>
@@ -8381,7 +8424,7 @@
     <row r="369" spans="1:18">
       <c r="A369" s="8"/>
       <c r="B369" s="10"/>
-      <c r="C369" s="10"/>
+      <c r="C369" s="16"/>
       <c r="D369" s="5"/>
       <c r="E369" s="6"/>
       <c r="F369" s="7"/>
@@ -8401,7 +8444,7 @@
     <row r="370" spans="1:18">
       <c r="A370" s="8"/>
       <c r="B370" s="10"/>
-      <c r="C370" s="10"/>
+      <c r="C370" s="16"/>
       <c r="D370" s="5"/>
       <c r="E370" s="6"/>
       <c r="F370" s="7"/>
@@ -8421,7 +8464,7 @@
     <row r="371" spans="1:18">
       <c r="A371" s="8"/>
       <c r="B371" s="10"/>
-      <c r="C371" s="10"/>
+      <c r="C371" s="16"/>
       <c r="D371" s="5"/>
       <c r="E371" s="6"/>
       <c r="F371" s="7"/>
@@ -8441,7 +8484,7 @@
     <row r="372" spans="1:18">
       <c r="A372" s="8"/>
       <c r="B372" s="10"/>
-      <c r="C372" s="10"/>
+      <c r="C372" s="16"/>
       <c r="D372" s="5"/>
       <c r="E372" s="6"/>
       <c r="F372" s="7"/>
@@ -8461,7 +8504,7 @@
     <row r="373" spans="1:18">
       <c r="A373" s="8"/>
       <c r="B373" s="10"/>
-      <c r="C373" s="10"/>
+      <c r="C373" s="16"/>
       <c r="D373" s="5"/>
       <c r="E373" s="6"/>
       <c r="F373" s="7"/>
@@ -8481,7 +8524,7 @@
     <row r="374" spans="1:18">
       <c r="A374" s="8"/>
       <c r="B374" s="10"/>
-      <c r="C374" s="10"/>
+      <c r="C374" s="16"/>
       <c r="D374" s="5"/>
       <c r="E374" s="6"/>
       <c r="F374" s="7"/>
@@ -8501,7 +8544,7 @@
     <row r="375" spans="1:18">
       <c r="A375" s="8"/>
       <c r="B375" s="10"/>
-      <c r="C375" s="10"/>
+      <c r="C375" s="16"/>
       <c r="D375" s="5"/>
       <c r="E375" s="6"/>
       <c r="F375" s="7"/>
@@ -8521,7 +8564,7 @@
     <row r="376" spans="1:18">
       <c r="A376" s="8"/>
       <c r="B376" s="10"/>
-      <c r="C376" s="10"/>
+      <c r="C376" s="16"/>
       <c r="D376" s="5"/>
       <c r="E376" s="6"/>
       <c r="F376" s="7"/>
@@ -8541,7 +8584,7 @@
     <row r="377" spans="1:18">
       <c r="A377" s="8"/>
       <c r="B377" s="10"/>
-      <c r="C377" s="10"/>
+      <c r="C377" s="16"/>
       <c r="D377" s="5"/>
       <c r="E377" s="6"/>
       <c r="F377" s="7"/>
@@ -8561,7 +8604,7 @@
     <row r="378" spans="1:18">
       <c r="A378" s="8"/>
       <c r="B378" s="10"/>
-      <c r="C378" s="10"/>
+      <c r="C378" s="16"/>
       <c r="D378" s="5"/>
       <c r="E378" s="6"/>
       <c r="F378" s="7"/>
@@ -8581,7 +8624,7 @@
     <row r="379" spans="1:18">
       <c r="A379" s="8"/>
       <c r="B379" s="10"/>
-      <c r="C379" s="10"/>
+      <c r="C379" s="16"/>
       <c r="D379" s="5"/>
       <c r="E379" s="6"/>
       <c r="F379" s="7"/>
@@ -8601,7 +8644,7 @@
     <row r="380" spans="1:18">
       <c r="A380" s="8"/>
       <c r="B380" s="10"/>
-      <c r="C380" s="10"/>
+      <c r="C380" s="16"/>
       <c r="D380" s="5"/>
       <c r="E380" s="6"/>
       <c r="F380" s="7"/>
@@ -8621,7 +8664,7 @@
     <row r="381" spans="1:18">
       <c r="A381" s="8"/>
       <c r="B381" s="10"/>
-      <c r="C381" s="10"/>
+      <c r="C381" s="16"/>
       <c r="D381" s="5"/>
       <c r="E381" s="6"/>
       <c r="F381" s="7"/>
@@ -8641,7 +8684,7 @@
     <row r="382" spans="1:18">
       <c r="A382" s="8"/>
       <c r="B382" s="10"/>
-      <c r="C382" s="10"/>
+      <c r="C382" s="16"/>
       <c r="D382" s="5"/>
       <c r="E382" s="6"/>
       <c r="F382" s="7"/>
@@ -8661,7 +8704,7 @@
     <row r="383" spans="1:18">
       <c r="A383" s="8"/>
       <c r="B383" s="10"/>
-      <c r="C383" s="10"/>
+      <c r="C383" s="16"/>
       <c r="D383" s="5"/>
       <c r="E383" s="6"/>
       <c r="F383" s="7"/>
@@ -8681,7 +8724,7 @@
     <row r="384" spans="1:18">
       <c r="A384" s="8"/>
       <c r="B384" s="10"/>
-      <c r="C384" s="10"/>
+      <c r="C384" s="16"/>
       <c r="D384" s="5"/>
       <c r="E384" s="6"/>
       <c r="F384" s="7"/>
@@ -8701,7 +8744,7 @@
     <row r="385" spans="1:18">
       <c r="A385" s="8"/>
       <c r="B385" s="10"/>
-      <c r="C385" s="10"/>
+      <c r="C385" s="16"/>
       <c r="D385" s="5"/>
       <c r="E385" s="6"/>
       <c r="F385" s="7"/>
@@ -8721,7 +8764,7 @@
     <row r="386" spans="1:18">
       <c r="A386" s="8"/>
       <c r="B386" s="10"/>
-      <c r="C386" s="10"/>
+      <c r="C386" s="16"/>
       <c r="D386" s="5"/>
       <c r="E386" s="6"/>
       <c r="F386" s="7"/>
@@ -8741,7 +8784,7 @@
     <row r="387" spans="1:18">
       <c r="A387" s="8"/>
       <c r="B387" s="10"/>
-      <c r="C387" s="10"/>
+      <c r="C387" s="16"/>
       <c r="D387" s="5"/>
       <c r="E387" s="6"/>
       <c r="F387" s="7"/>
@@ -8761,7 +8804,7 @@
     <row r="388" spans="1:18">
       <c r="A388" s="8"/>
       <c r="B388" s="10"/>
-      <c r="C388" s="10"/>
+      <c r="C388" s="16"/>
       <c r="D388" s="5"/>
       <c r="E388" s="6"/>
       <c r="F388" s="7"/>
@@ -8781,7 +8824,7 @@
     <row r="389" spans="1:18">
       <c r="A389" s="8"/>
       <c r="B389" s="10"/>
-      <c r="C389" s="10"/>
+      <c r="C389" s="16"/>
       <c r="D389" s="5"/>
       <c r="E389" s="6"/>
       <c r="F389" s="7"/>
@@ -8801,7 +8844,7 @@
     <row r="390" spans="1:18">
       <c r="A390" s="8"/>
       <c r="B390" s="10"/>
-      <c r="C390" s="10"/>
+      <c r="C390" s="16"/>
       <c r="D390" s="5"/>
       <c r="E390" s="6"/>
       <c r="F390" s="7"/>
@@ -8821,7 +8864,7 @@
     <row r="391" spans="1:18">
       <c r="A391" s="8"/>
       <c r="B391" s="10"/>
-      <c r="C391" s="10"/>
+      <c r="C391" s="16"/>
       <c r="D391" s="5"/>
       <c r="E391" s="6"/>
       <c r="F391" s="7"/>
@@ -8841,7 +8884,7 @@
     <row r="392" spans="1:18">
       <c r="A392" s="8"/>
       <c r="B392" s="10"/>
-      <c r="C392" s="10"/>
+      <c r="C392" s="16"/>
       <c r="D392" s="5"/>
       <c r="E392" s="6"/>
       <c r="F392" s="7"/>
@@ -8861,7 +8904,7 @@
     <row r="393" spans="1:18">
       <c r="A393" s="8"/>
       <c r="B393" s="10"/>
-      <c r="C393" s="10"/>
+      <c r="C393" s="16"/>
       <c r="D393" s="5"/>
       <c r="E393" s="6"/>
       <c r="F393" s="7"/>
@@ -8881,7 +8924,7 @@
     <row r="394" spans="1:18">
       <c r="A394" s="8"/>
       <c r="B394" s="10"/>
-      <c r="C394" s="10"/>
+      <c r="C394" s="16"/>
       <c r="D394" s="5"/>
       <c r="E394" s="6"/>
       <c r="F394" s="7"/>
@@ -8901,7 +8944,7 @@
     <row r="395" spans="1:18">
       <c r="A395" s="8"/>
       <c r="B395" s="10"/>
-      <c r="C395" s="10"/>
+      <c r="C395" s="16"/>
       <c r="D395" s="5"/>
       <c r="E395" s="6"/>
       <c r="F395" s="7"/>
@@ -8921,7 +8964,7 @@
     <row r="396" spans="1:18">
       <c r="A396" s="8"/>
       <c r="B396" s="10"/>
-      <c r="C396" s="10"/>
+      <c r="C396" s="16"/>
       <c r="D396" s="5"/>
       <c r="E396" s="6"/>
       <c r="F396" s="7"/>
@@ -8941,7 +8984,7 @@
     <row r="397" spans="1:18">
       <c r="A397" s="8"/>
       <c r="B397" s="10"/>
-      <c r="C397" s="10"/>
+      <c r="C397" s="16"/>
       <c r="D397" s="5"/>
       <c r="E397" s="6"/>
       <c r="F397" s="7"/>
@@ -8961,7 +9004,7 @@
     <row r="398" spans="1:18">
       <c r="A398" s="8"/>
       <c r="B398" s="10"/>
-      <c r="C398" s="10"/>
+      <c r="C398" s="16"/>
       <c r="D398" s="5"/>
       <c r="E398" s="6"/>
       <c r="F398" s="7"/>
@@ -8981,7 +9024,7 @@
     <row r="399" spans="1:18">
       <c r="A399" s="8"/>
       <c r="B399" s="10"/>
-      <c r="C399" s="10"/>
+      <c r="C399" s="16"/>
       <c r="D399" s="5"/>
       <c r="E399" s="6"/>
       <c r="F399" s="7"/>
@@ -9001,7 +9044,7 @@
     <row r="400" spans="1:18">
       <c r="A400" s="8"/>
       <c r="B400" s="10"/>
-      <c r="C400" s="10"/>
+      <c r="C400" s="16"/>
       <c r="D400" s="5"/>
       <c r="E400" s="6"/>
       <c r="F400" s="7"/>
@@ -9021,7 +9064,7 @@
     <row r="401" spans="1:18">
       <c r="A401" s="8"/>
       <c r="B401" s="10"/>
-      <c r="C401" s="10"/>
+      <c r="C401" s="16"/>
       <c r="D401" s="5"/>
       <c r="E401" s="6"/>
       <c r="F401" s="7"/>
@@ -9041,7 +9084,7 @@
     <row r="402" spans="1:18">
       <c r="A402" s="8"/>
       <c r="B402" s="10"/>
-      <c r="C402" s="10"/>
+      <c r="C402" s="16"/>
       <c r="D402" s="5"/>
       <c r="E402" s="6"/>
       <c r="F402" s="7"/>
@@ -9061,7 +9104,7 @@
     <row r="403" spans="1:18">
       <c r="A403" s="8"/>
       <c r="B403" s="10"/>
-      <c r="C403" s="10"/>
+      <c r="C403" s="16"/>
       <c r="D403" s="5"/>
       <c r="E403" s="6"/>
       <c r="F403" s="7"/>
@@ -9081,7 +9124,7 @@
     <row r="404" spans="1:18">
       <c r="A404" s="8"/>
       <c r="B404" s="10"/>
-      <c r="C404" s="10"/>
+      <c r="C404" s="16"/>
       <c r="D404" s="5"/>
       <c r="E404" s="6"/>
       <c r="F404" s="7"/>
@@ -9101,7 +9144,7 @@
     <row r="405" spans="1:18">
       <c r="A405" s="8"/>
       <c r="B405" s="10"/>
-      <c r="C405" s="10"/>
+      <c r="C405" s="16"/>
       <c r="D405" s="5"/>
       <c r="E405" s="6"/>
       <c r="F405" s="7"/>
@@ -9121,7 +9164,7 @@
     <row r="406" spans="1:18">
       <c r="A406" s="8"/>
       <c r="B406" s="10"/>
-      <c r="C406" s="10"/>
+      <c r="C406" s="16"/>
       <c r="D406" s="5"/>
       <c r="E406" s="6"/>
       <c r="F406" s="7"/>
@@ -9141,7 +9184,7 @@
     <row r="407" spans="1:18">
       <c r="A407" s="8"/>
       <c r="B407" s="10"/>
-      <c r="C407" s="10"/>
+      <c r="C407" s="16"/>
       <c r="D407" s="5"/>
       <c r="E407" s="6"/>
       <c r="F407" s="7"/>
@@ -9161,7 +9204,7 @@
     <row r="408" spans="1:18">
       <c r="A408" s="8"/>
       <c r="B408" s="10"/>
-      <c r="C408" s="10"/>
+      <c r="C408" s="16"/>
       <c r="D408" s="5"/>
       <c r="E408" s="6"/>
       <c r="F408" s="7"/>
@@ -9181,7 +9224,7 @@
     <row r="409" spans="1:18">
       <c r="A409" s="8"/>
       <c r="B409" s="10"/>
-      <c r="C409" s="10"/>
+      <c r="C409" s="16"/>
       <c r="D409" s="5"/>
       <c r="E409" s="6"/>
       <c r="F409" s="7"/>
@@ -9201,7 +9244,7 @@
     <row r="410" spans="1:18">
       <c r="A410" s="8"/>
       <c r="B410" s="10"/>
-      <c r="C410" s="10"/>
+      <c r="C410" s="16"/>
       <c r="D410" s="5"/>
       <c r="E410" s="6"/>
       <c r="F410" s="7"/>
@@ -9221,7 +9264,7 @@
     <row r="411" spans="1:18">
       <c r="A411" s="8"/>
       <c r="B411" s="10"/>
-      <c r="C411" s="10"/>
+      <c r="C411" s="16"/>
       <c r="D411" s="5"/>
       <c r="E411" s="6"/>
       <c r="F411" s="7"/>
@@ -9241,7 +9284,7 @@
     <row r="412" spans="1:18">
       <c r="A412" s="8"/>
       <c r="B412" s="10"/>
-      <c r="C412" s="10"/>
+      <c r="C412" s="16"/>
       <c r="D412" s="5"/>
       <c r="E412" s="6"/>
       <c r="F412" s="7"/>
@@ -9261,7 +9304,7 @@
     <row r="413" spans="1:18">
       <c r="A413" s="8"/>
       <c r="B413" s="10"/>
-      <c r="C413" s="10"/>
+      <c r="C413" s="16"/>
       <c r="D413" s="5"/>
       <c r="E413" s="6"/>
       <c r="F413" s="7"/>
@@ -9281,7 +9324,7 @@
     <row r="414" spans="1:18">
       <c r="A414" s="8"/>
       <c r="B414" s="10"/>
-      <c r="C414" s="10"/>
+      <c r="C414" s="16"/>
       <c r="D414" s="5"/>
       <c r="E414" s="6"/>
       <c r="F414" s="7"/>
@@ -9301,7 +9344,7 @@
     <row r="415" spans="1:18">
       <c r="A415" s="8"/>
       <c r="B415" s="10"/>
-      <c r="C415" s="10"/>
+      <c r="C415" s="16"/>
       <c r="D415" s="5"/>
       <c r="E415" s="6"/>
       <c r="F415" s="7"/>
@@ -9321,7 +9364,7 @@
     <row r="416" spans="1:18">
       <c r="A416" s="8"/>
       <c r="B416" s="10"/>
-      <c r="C416" s="10"/>
+      <c r="C416" s="16"/>
       <c r="D416" s="5"/>
       <c r="E416" s="6"/>
       <c r="F416" s="7"/>
@@ -9341,7 +9384,7 @@
     <row r="417" spans="1:18">
       <c r="A417" s="8"/>
       <c r="B417" s="10"/>
-      <c r="C417" s="10"/>
+      <c r="C417" s="16"/>
       <c r="D417" s="5"/>
       <c r="E417" s="6"/>
       <c r="F417" s="7"/>
@@ -9361,7 +9404,7 @@
     <row r="418" spans="1:18">
       <c r="A418" s="8"/>
       <c r="B418" s="10"/>
-      <c r="C418" s="10"/>
+      <c r="C418" s="16"/>
       <c r="D418" s="5"/>
       <c r="E418" s="6"/>
       <c r="F418" s="7"/>
@@ -9381,7 +9424,7 @@
     <row r="419" spans="1:18">
       <c r="A419" s="8"/>
       <c r="B419" s="10"/>
-      <c r="C419" s="10"/>
+      <c r="C419" s="16"/>
       <c r="D419" s="5"/>
       <c r="E419" s="6"/>
       <c r="F419" s="7"/>
@@ -9401,7 +9444,7 @@
     <row r="420" spans="1:18">
       <c r="A420" s="8"/>
       <c r="B420" s="10"/>
-      <c r="C420" s="10"/>
+      <c r="C420" s="16"/>
       <c r="D420" s="5"/>
       <c r="E420" s="6"/>
       <c r="F420" s="7"/>
@@ -9421,7 +9464,7 @@
     <row r="421" spans="1:18">
       <c r="A421" s="8"/>
       <c r="B421" s="10"/>
-      <c r="C421" s="10"/>
+      <c r="C421" s="16"/>
       <c r="D421" s="5"/>
       <c r="E421" s="6"/>
       <c r="F421" s="7"/>
@@ -9441,7 +9484,7 @@
     <row r="422" spans="1:18">
       <c r="A422" s="8"/>
       <c r="B422" s="10"/>
-      <c r="C422" s="10"/>
+      <c r="C422" s="16"/>
       <c r="D422" s="5"/>
       <c r="E422" s="6"/>
       <c r="F422" s="7"/>
@@ -9461,7 +9504,7 @@
     <row r="423" spans="1:18">
       <c r="A423" s="8"/>
       <c r="B423" s="10"/>
-      <c r="C423" s="10"/>
+      <c r="C423" s="16"/>
       <c r="D423" s="5"/>
       <c r="E423" s="6"/>
       <c r="F423" s="7"/>
@@ -9481,7 +9524,7 @@
     <row r="424" spans="1:18">
       <c r="A424" s="8"/>
       <c r="B424" s="10"/>
-      <c r="C424" s="10"/>
+      <c r="C424" s="16"/>
       <c r="D424" s="5"/>
       <c r="E424" s="6"/>
       <c r="F424" s="7"/>
@@ -9501,7 +9544,7 @@
     <row r="425" spans="1:18">
       <c r="A425" s="8"/>
       <c r="B425" s="10"/>
-      <c r="C425" s="10"/>
+      <c r="C425" s="16"/>
       <c r="D425" s="5"/>
       <c r="E425" s="6"/>
       <c r="F425" s="7"/>
@@ -9521,7 +9564,7 @@
     <row r="426" spans="1:18">
       <c r="A426" s="8"/>
       <c r="B426" s="10"/>
-      <c r="C426" s="10"/>
+      <c r="C426" s="16"/>
       <c r="D426" s="5"/>
       <c r="E426" s="6"/>
       <c r="F426" s="7"/>
@@ -9541,7 +9584,7 @@
     <row r="427" spans="1:18">
       <c r="A427" s="8"/>
       <c r="B427" s="10"/>
-      <c r="C427" s="10"/>
+      <c r="C427" s="16"/>
       <c r="D427" s="5"/>
       <c r="E427" s="6"/>
       <c r="F427" s="7"/>
@@ -9561,7 +9604,7 @@
     <row r="428" spans="1:18">
       <c r="A428" s="8"/>
       <c r="B428" s="10"/>
-      <c r="C428" s="10"/>
+      <c r="C428" s="16"/>
       <c r="D428" s="5"/>
       <c r="E428" s="6"/>
       <c r="F428" s="7"/>
@@ -9581,7 +9624,7 @@
     <row r="429" spans="1:18">
       <c r="A429" s="8"/>
       <c r="B429" s="10"/>
-      <c r="C429" s="10"/>
+      <c r="C429" s="16"/>
       <c r="D429" s="5"/>
       <c r="E429" s="6"/>
       <c r="F429" s="7"/>
@@ -9601,7 +9644,7 @@
     <row r="430" spans="1:18">
       <c r="A430" s="8"/>
       <c r="B430" s="10"/>
-      <c r="C430" s="10"/>
+      <c r="C430" s="16"/>
       <c r="D430" s="5"/>
       <c r="E430" s="6"/>
       <c r="F430" s="7"/>
@@ -9621,7 +9664,7 @@
     <row r="431" spans="1:18">
       <c r="A431" s="8"/>
       <c r="B431" s="10"/>
-      <c r="C431" s="10"/>
+      <c r="C431" s="16"/>
       <c r="D431" s="5"/>
       <c r="E431" s="6"/>
       <c r="F431" s="7"/>
@@ -9641,7 +9684,7 @@
     <row r="432" spans="1:18">
       <c r="A432" s="8"/>
       <c r="B432" s="10"/>
-      <c r="C432" s="10"/>
+      <c r="C432" s="16"/>
       <c r="D432" s="5"/>
       <c r="E432" s="6"/>
       <c r="F432" s="7"/>
@@ -9661,7 +9704,7 @@
     <row r="433" spans="1:18">
       <c r="A433" s="8"/>
       <c r="B433" s="10"/>
-      <c r="C433" s="10"/>
+      <c r="C433" s="16"/>
       <c r="D433" s="5"/>
       <c r="E433" s="6"/>
       <c r="F433" s="7"/>
@@ -9681,7 +9724,7 @@
     <row r="434" spans="1:18">
       <c r="A434" s="8"/>
       <c r="B434" s="10"/>
-      <c r="C434" s="10"/>
+      <c r="C434" s="16"/>
       <c r="D434" s="5"/>
       <c r="E434" s="6"/>
       <c r="F434" s="7"/>
@@ -9701,7 +9744,7 @@
     <row r="435" spans="1:18">
       <c r="A435" s="8"/>
       <c r="B435" s="10"/>
-      <c r="C435" s="10"/>
+      <c r="C435" s="16"/>
       <c r="D435" s="5"/>
       <c r="E435" s="6"/>
       <c r="F435" s="7"/>
@@ -9721,7 +9764,7 @@
     <row r="436" spans="1:18">
       <c r="A436" s="8"/>
       <c r="B436" s="10"/>
-      <c r="C436" s="10"/>
+      <c r="C436" s="16"/>
       <c r="D436" s="5"/>
       <c r="E436" s="6"/>
       <c r="F436" s="7"/>
@@ -9741,7 +9784,7 @@
     <row r="437" spans="1:18">
       <c r="A437" s="8"/>
       <c r="B437" s="10"/>
-      <c r="C437" s="10"/>
+      <c r="C437" s="16"/>
       <c r="D437" s="5"/>
       <c r="E437" s="6"/>
       <c r="F437" s="7"/>
@@ -9761,7 +9804,7 @@
     <row r="438" spans="1:18">
       <c r="A438" s="8"/>
       <c r="B438" s="10"/>
-      <c r="C438" s="10"/>
+      <c r="C438" s="16"/>
       <c r="D438" s="5"/>
       <c r="E438" s="6"/>
       <c r="F438" s="7"/>
@@ -9781,7 +9824,7 @@
     <row r="439" spans="1:18">
       <c r="A439" s="8"/>
       <c r="B439" s="10"/>
-      <c r="C439" s="10"/>
+      <c r="C439" s="16"/>
       <c r="D439" s="5"/>
       <c r="E439" s="6"/>
       <c r="F439" s="7"/>
@@ -9801,7 +9844,7 @@
     <row r="440" spans="1:18">
       <c r="A440" s="8"/>
       <c r="B440" s="10"/>
-      <c r="C440" s="10"/>
+      <c r="C440" s="16"/>
       <c r="D440" s="5"/>
       <c r="E440" s="6"/>
       <c r="F440" s="7"/>
@@ -9821,7 +9864,7 @@
     <row r="441" spans="1:18">
       <c r="A441" s="8"/>
       <c r="B441" s="10"/>
-      <c r="C441" s="10"/>
+      <c r="C441" s="16"/>
       <c r="D441" s="5"/>
       <c r="E441" s="6"/>
       <c r="F441" s="7"/>
@@ -9841,7 +9884,7 @@
     <row r="442" spans="1:18">
       <c r="A442" s="8"/>
       <c r="B442" s="10"/>
-      <c r="C442" s="10"/>
+      <c r="C442" s="16"/>
       <c r="D442" s="5"/>
       <c r="E442" s="6"/>
       <c r="F442" s="7"/>
@@ -9861,7 +9904,7 @@
     <row r="443" spans="1:18">
       <c r="A443" s="8"/>
       <c r="B443" s="10"/>
-      <c r="C443" s="10"/>
+      <c r="C443" s="16"/>
       <c r="D443" s="5"/>
       <c r="E443" s="6"/>
       <c r="F443" s="7"/>
@@ -9881,7 +9924,7 @@
     <row r="444" spans="1:18">
       <c r="A444" s="8"/>
       <c r="B444" s="10"/>
-      <c r="C444" s="10"/>
+      <c r="C444" s="16"/>
       <c r="D444" s="5"/>
       <c r="E444" s="6"/>
       <c r="F444" s="7"/>
@@ -9901,7 +9944,7 @@
     <row r="445" spans="1:18">
       <c r="A445" s="8"/>
       <c r="B445" s="10"/>
-      <c r="C445" s="10"/>
+      <c r="C445" s="16"/>
       <c r="D445" s="5"/>
       <c r="E445" s="6"/>
       <c r="F445" s="7"/>
@@ -9921,7 +9964,7 @@
     <row r="446" spans="1:18">
       <c r="A446" s="8"/>
       <c r="B446" s="10"/>
-      <c r="C446" s="10"/>
+      <c r="C446" s="16"/>
       <c r="D446" s="5"/>
       <c r="E446" s="6"/>
       <c r="F446" s="7"/>
@@ -9941,7 +9984,7 @@
     <row r="447" spans="1:18">
       <c r="A447" s="8"/>
       <c r="B447" s="10"/>
-      <c r="C447" s="10"/>
+      <c r="C447" s="16"/>
       <c r="D447" s="5"/>
       <c r="E447" s="6"/>
       <c r="F447" s="7"/>
@@ -9961,7 +10004,7 @@
     <row r="448" spans="1:18">
       <c r="A448" s="8"/>
       <c r="B448" s="10"/>
-      <c r="C448" s="10"/>
+      <c r="C448" s="16"/>
       <c r="D448" s="5"/>
       <c r="E448" s="6"/>
       <c r="F448" s="7"/>
@@ -9981,7 +10024,7 @@
     <row r="449" spans="1:18">
       <c r="A449" s="8"/>
       <c r="B449" s="10"/>
-      <c r="C449" s="10"/>
+      <c r="C449" s="16"/>
       <c r="D449" s="5"/>
       <c r="E449" s="6"/>
       <c r="F449" s="7"/>
@@ -10001,7 +10044,7 @@
     <row r="450" spans="1:18">
       <c r="A450" s="8"/>
       <c r="B450" s="10"/>
-      <c r="C450" s="10"/>
+      <c r="C450" s="16"/>
       <c r="D450" s="5"/>
       <c r="E450" s="6"/>
       <c r="F450" s="7"/>
@@ -10021,7 +10064,7 @@
     <row r="451" spans="1:18">
       <c r="A451" s="8"/>
       <c r="B451" s="10"/>
-      <c r="C451" s="10"/>
+      <c r="C451" s="16"/>
       <c r="D451" s="5"/>
       <c r="E451" s="6"/>
       <c r="F451" s="7"/>
@@ -10041,7 +10084,7 @@
     <row r="452" spans="1:18">
       <c r="A452" s="8"/>
       <c r="B452" s="10"/>
-      <c r="C452" s="10"/>
+      <c r="C452" s="16"/>
       <c r="D452" s="5"/>
       <c r="E452" s="6"/>
       <c r="F452" s="7"/>
@@ -10061,7 +10104,7 @@
     <row r="453" spans="1:18">
       <c r="A453" s="8"/>
       <c r="B453" s="10"/>
-      <c r="C453" s="10"/>
+      <c r="C453" s="16"/>
       <c r="D453" s="5"/>
       <c r="E453" s="6"/>
       <c r="F453" s="7"/>
@@ -10081,7 +10124,7 @@
     <row r="454" spans="1:18">
       <c r="A454" s="8"/>
       <c r="B454" s="10"/>
-      <c r="C454" s="10"/>
+      <c r="C454" s="16"/>
       <c r="D454" s="5"/>
       <c r="E454" s="6"/>
       <c r="F454" s="7"/>
@@ -10101,7 +10144,7 @@
     <row r="455" spans="1:18">
       <c r="A455" s="8"/>
       <c r="B455" s="10"/>
-      <c r="C455" s="10"/>
+      <c r="C455" s="16"/>
       <c r="D455" s="5"/>
       <c r="E455" s="6"/>
       <c r="F455" s="7"/>
@@ -10121,7 +10164,7 @@
     <row r="456" spans="1:18">
       <c r="A456" s="8"/>
       <c r="B456" s="10"/>
-      <c r="C456" s="10"/>
+      <c r="C456" s="16"/>
       <c r="D456" s="5"/>
       <c r="E456" s="6"/>
       <c r="F456" s="7"/>
@@ -10141,7 +10184,7 @@
     <row r="457" spans="1:18">
       <c r="A457" s="8"/>
       <c r="B457" s="10"/>
-      <c r="C457" s="10"/>
+      <c r="C457" s="16"/>
       <c r="D457" s="5"/>
       <c r="E457" s="6"/>
       <c r="F457" s="7"/>
@@ -10161,7 +10204,7 @@
     <row r="458" spans="1:18">
       <c r="A458" s="8"/>
       <c r="B458" s="10"/>
-      <c r="C458" s="10"/>
+      <c r="C458" s="16"/>
       <c r="D458" s="5"/>
       <c r="E458" s="6"/>
       <c r="F458" s="7"/>
@@ -10181,7 +10224,7 @@
     <row r="459" spans="1:18">
       <c r="A459" s="8"/>
       <c r="B459" s="10"/>
-      <c r="C459" s="10"/>
+      <c r="C459" s="16"/>
       <c r="D459" s="5"/>
       <c r="E459" s="6"/>
       <c r="F459" s="7"/>
@@ -10201,7 +10244,7 @@
     <row r="460" spans="1:18">
       <c r="A460" s="8"/>
       <c r="B460" s="10"/>
-      <c r="C460" s="10"/>
+      <c r="C460" s="16"/>
       <c r="D460" s="5"/>
       <c r="E460" s="6"/>
       <c r="F460" s="7"/>
@@ -10221,7 +10264,7 @@
     <row r="461" spans="1:18">
       <c r="A461" s="8"/>
       <c r="B461" s="10"/>
-      <c r="C461" s="10"/>
+      <c r="C461" s="16"/>
       <c r="D461" s="5"/>
       <c r="E461" s="6"/>
       <c r="F461" s="7"/>
@@ -10241,7 +10284,7 @@
     <row r="462" spans="1:18">
       <c r="A462" s="8"/>
       <c r="B462" s="10"/>
-      <c r="C462" s="10"/>
+      <c r="C462" s="16"/>
       <c r="D462" s="5"/>
       <c r="E462" s="6"/>
       <c r="F462" s="7"/>
@@ -10261,7 +10304,7 @@
     <row r="463" spans="1:18">
       <c r="A463" s="8"/>
       <c r="B463" s="10"/>
-      <c r="C463" s="10"/>
+      <c r="C463" s="16"/>
       <c r="D463" s="5"/>
       <c r="E463" s="6"/>
       <c r="F463" s="7"/>
@@ -10281,7 +10324,7 @@
     <row r="464" spans="1:18">
       <c r="A464" s="8"/>
       <c r="B464" s="10"/>
-      <c r="C464" s="10"/>
+      <c r="C464" s="16"/>
       <c r="D464" s="5"/>
       <c r="E464" s="6"/>
       <c r="F464" s="7"/>
@@ -10301,7 +10344,7 @@
     <row r="465" spans="1:18">
       <c r="A465" s="8"/>
       <c r="B465" s="10"/>
-      <c r="C465" s="10"/>
+      <c r="C465" s="16"/>
       <c r="D465" s="5"/>
       <c r="E465" s="6"/>
       <c r="F465" s="7"/>
@@ -10321,7 +10364,7 @@
     <row r="466" spans="1:18">
       <c r="A466" s="8"/>
       <c r="B466" s="10"/>
-      <c r="C466" s="10"/>
+      <c r="C466" s="16"/>
       <c r="D466" s="5"/>
       <c r="E466" s="6"/>
       <c r="F466" s="7"/>
@@ -10341,7 +10384,7 @@
     <row r="467" spans="1:18">
       <c r="A467" s="8"/>
       <c r="B467" s="10"/>
-      <c r="C467" s="10"/>
+      <c r="C467" s="16"/>
       <c r="D467" s="5"/>
       <c r="E467" s="6"/>
       <c r="F467" s="7"/>
@@ -10361,7 +10404,7 @@
     <row r="468" spans="1:18">
       <c r="A468" s="8"/>
       <c r="B468" s="10"/>
-      <c r="C468" s="10"/>
+      <c r="C468" s="16"/>
       <c r="D468" s="5"/>
       <c r="E468" s="6"/>
       <c r="F468" s="7"/>
@@ -10381,7 +10424,7 @@
     <row r="469" spans="1:18">
       <c r="A469" s="8"/>
       <c r="B469" s="10"/>
-      <c r="C469" s="10"/>
+      <c r="C469" s="16"/>
       <c r="D469" s="5"/>
       <c r="E469" s="6"/>
       <c r="F469" s="7"/>
@@ -10401,7 +10444,7 @@
     <row r="470" spans="1:18">
       <c r="A470" s="8"/>
       <c r="B470" s="10"/>
-      <c r="C470" s="10"/>
+      <c r="C470" s="16"/>
       <c r="D470" s="5"/>
       <c r="E470" s="6"/>
       <c r="F470" s="7"/>
@@ -10421,7 +10464,7 @@
     <row r="471" spans="1:18">
       <c r="A471" s="8"/>
       <c r="B471" s="10"/>
-      <c r="C471" s="10"/>
+      <c r="C471" s="16"/>
       <c r="D471" s="5"/>
       <c r="E471" s="6"/>
       <c r="F471" s="7"/>
@@ -10441,7 +10484,7 @@
     <row r="472" spans="1:18">
       <c r="A472" s="8"/>
       <c r="B472" s="10"/>
-      <c r="C472" s="10"/>
+      <c r="C472" s="16"/>
       <c r="D472" s="5"/>
       <c r="E472" s="6"/>
       <c r="F472" s="7"/>
@@ -10461,7 +10504,7 @@
     <row r="473" spans="1:18">
       <c r="A473" s="8"/>
       <c r="B473" s="10"/>
-      <c r="C473" s="10"/>
+      <c r="C473" s="16"/>
       <c r="D473" s="5"/>
       <c r="E473" s="6"/>
       <c r="F473" s="7"/>
@@ -10481,7 +10524,7 @@
     <row r="474" spans="1:18">
       <c r="A474" s="8"/>
       <c r="B474" s="10"/>
-      <c r="C474" s="10"/>
+      <c r="C474" s="16"/>
       <c r="D474" s="5"/>
       <c r="E474" s="6"/>
       <c r="F474" s="7"/>
@@ -10501,7 +10544,7 @@
     <row r="475" spans="1:18">
       <c r="A475" s="8"/>
       <c r="B475" s="10"/>
-      <c r="C475" s="10"/>
+      <c r="C475" s="16"/>
       <c r="D475" s="5"/>
       <c r="E475" s="6"/>
       <c r="F475" s="7"/>
@@ -10521,7 +10564,7 @@
     <row r="476" spans="1:18">
       <c r="A476" s="8"/>
       <c r="B476" s="10"/>
-      <c r="C476" s="10"/>
+      <c r="C476" s="16"/>
       <c r="D476" s="5"/>
       <c r="E476" s="6"/>
       <c r="F476" s="7"/>
@@ -10541,7 +10584,7 @@
     <row r="477" spans="1:18">
       <c r="A477" s="8"/>
       <c r="B477" s="10"/>
-      <c r="C477" s="10"/>
+      <c r="C477" s="16"/>
       <c r="D477" s="5"/>
       <c r="E477" s="6"/>
       <c r="F477" s="7"/>
@@ -10561,7 +10604,7 @@
     <row r="478" spans="1:18">
       <c r="A478" s="8"/>
       <c r="B478" s="10"/>
-      <c r="C478" s="10"/>
+      <c r="C478" s="16"/>
       <c r="D478" s="5"/>
       <c r="E478" s="6"/>
       <c r="F478" s="7"/>
@@ -10581,7 +10624,7 @@
     <row r="479" spans="1:18">
       <c r="A479" s="8"/>
       <c r="B479" s="10"/>
-      <c r="C479" s="10"/>
+      <c r="C479" s="16"/>
       <c r="D479" s="5"/>
       <c r="E479" s="6"/>
       <c r="F479" s="7"/>
@@ -10601,7 +10644,7 @@
     <row r="480" spans="1:18">
       <c r="A480" s="8"/>
       <c r="B480" s="10"/>
-      <c r="C480" s="10"/>
+      <c r="C480" s="16"/>
       <c r="D480" s="5"/>
       <c r="E480" s="6"/>
       <c r="F480" s="7"/>
@@ -10621,7 +10664,7 @@
     <row r="481" spans="1:18">
       <c r="A481" s="8"/>
       <c r="B481" s="10"/>
-      <c r="C481" s="10"/>
+      <c r="C481" s="16"/>
       <c r="D481" s="5"/>
       <c r="E481" s="6"/>
       <c r="F481" s="7"/>
@@ -10641,7 +10684,7 @@
     <row r="482" spans="1:18">
       <c r="A482" s="8"/>
       <c r="B482" s="10"/>
-      <c r="C482" s="10"/>
+      <c r="C482" s="16"/>
       <c r="D482" s="5"/>
       <c r="E482" s="6"/>
       <c r="F482" s="7"/>
@@ -10661,7 +10704,7 @@
     <row r="483" spans="1:18">
       <c r="A483" s="8"/>
       <c r="B483" s="10"/>
-      <c r="C483" s="10"/>
+      <c r="C483" s="16"/>
       <c r="D483" s="5"/>
       <c r="E483" s="6"/>
       <c r="F483" s="7"/>
@@ -10681,7 +10724,7 @@
     <row r="484" spans="1:18">
       <c r="A484" s="8"/>
       <c r="B484" s="10"/>
-      <c r="C484" s="10"/>
+      <c r="C484" s="16"/>
       <c r="D484" s="5"/>
       <c r="E484" s="6"/>
       <c r="F484" s="7"/>
@@ -10701,7 +10744,7 @@
     <row r="485" spans="1:18">
       <c r="A485" s="8"/>
       <c r="B485" s="10"/>
-      <c r="C485" s="10"/>
+      <c r="C485" s="16"/>
       <c r="D485" s="5"/>
       <c r="E485" s="6"/>
       <c r="F485" s="7"/>
@@ -10721,7 +10764,7 @@
     <row r="486" spans="1:18">
       <c r="A486" s="8"/>
       <c r="B486" s="10"/>
-      <c r="C486" s="10"/>
+      <c r="C486" s="16"/>
       <c r="D486" s="5"/>
       <c r="E486" s="6"/>
       <c r="F486" s="7"/>
@@ -10741,7 +10784,7 @@
     <row r="487" spans="1:18">
       <c r="A487" s="8"/>
       <c r="B487" s="10"/>
-      <c r="C487" s="10"/>
+      <c r="C487" s="16"/>
       <c r="D487" s="5"/>
       <c r="E487" s="6"/>
       <c r="F487" s="7"/>
@@ -10761,7 +10804,7 @@
     <row r="488" spans="1:18">
       <c r="A488" s="8"/>
       <c r="B488" s="10"/>
-      <c r="C488" s="10"/>
+      <c r="C488" s="16"/>
       <c r="D488" s="5"/>
       <c r="E488" s="6"/>
       <c r="F488" s="7"/>
@@ -10781,7 +10824,7 @@
     <row r="489" spans="1:18">
       <c r="A489" s="8"/>
       <c r="B489" s="10"/>
-      <c r="C489" s="10"/>
+      <c r="C489" s="16"/>
       <c r="D489" s="5"/>
       <c r="E489" s="6"/>
       <c r="F489" s="7"/>
@@ -10801,7 +10844,7 @@
     <row r="490" spans="1:18">
       <c r="A490" s="8"/>
       <c r="B490" s="10"/>
-      <c r="C490" s="10"/>
+      <c r="C490" s="16"/>
       <c r="D490" s="5"/>
       <c r="E490" s="6"/>
       <c r="F490" s="7"/>
@@ -10821,7 +10864,7 @@
     <row r="491" spans="1:18">
       <c r="A491" s="8"/>
       <c r="B491" s="10"/>
-      <c r="C491" s="10"/>
+      <c r="C491" s="16"/>
       <c r="D491" s="5"/>
       <c r="E491" s="6"/>
       <c r="F491" s="7"/>
@@ -10841,7 +10884,7 @@
     <row r="492" spans="1:18">
       <c r="A492" s="8"/>
       <c r="B492" s="10"/>
-      <c r="C492" s="10"/>
+      <c r="C492" s="16"/>
       <c r="D492" s="5"/>
       <c r="E492" s="6"/>
       <c r="F492" s="7"/>
@@ -10861,7 +10904,7 @@
     <row r="493" spans="1:18">
       <c r="A493" s="8"/>
       <c r="B493" s="10"/>
-      <c r="C493" s="10"/>
+      <c r="C493" s="16"/>
       <c r="D493" s="5"/>
       <c r="E493" s="6"/>
       <c r="F493" s="7"/>
@@ -10881,7 +10924,7 @@
     <row r="494" spans="1:18">
       <c r="A494" s="8"/>
       <c r="B494" s="10"/>
-      <c r="C494" s="10"/>
+      <c r="C494" s="16"/>
       <c r="D494" s="5"/>
       <c r="E494" s="6"/>
       <c r="F494" s="7"/>
@@ -10901,7 +10944,7 @@
     <row r="495" spans="1:18">
       <c r="A495" s="8"/>
       <c r="B495" s="10"/>
-      <c r="C495" s="10"/>
+      <c r="C495" s="16"/>
       <c r="D495" s="5"/>
       <c r="E495" s="6"/>
       <c r="F495" s="7"/>
@@ -10921,7 +10964,7 @@
     <row r="496" spans="1:18">
       <c r="A496" s="8"/>
       <c r="B496" s="10"/>
-      <c r="C496" s="10"/>
+      <c r="C496" s="16"/>
       <c r="D496" s="5"/>
       <c r="E496" s="6"/>
       <c r="F496" s="7"/>
@@ -10941,7 +10984,7 @@
     <row r="497" spans="1:18">
       <c r="A497" s="8"/>
       <c r="B497" s="10"/>
-      <c r="C497" s="10"/>
+      <c r="C497" s="16"/>
       <c r="D497" s="5"/>
       <c r="E497" s="6"/>
       <c r="F497" s="7"/>
@@ -10961,7 +11004,7 @@
     <row r="498" spans="1:18">
       <c r="A498" s="8"/>
       <c r="B498" s="10"/>
-      <c r="C498" s="10"/>
+      <c r="C498" s="16"/>
       <c r="D498" s="5"/>
       <c r="E498" s="6"/>
       <c r="F498" s="7"/>
@@ -10981,7 +11024,7 @@
     <row r="499" spans="1:18">
       <c r="A499" s="8"/>
       <c r="B499" s="10"/>
-      <c r="C499" s="10"/>
+      <c r="C499" s="16"/>
       <c r="D499" s="5"/>
       <c r="E499" s="6"/>
       <c r="F499" s="7"/>
@@ -11001,7 +11044,7 @@
     <row r="500" spans="1:18">
       <c r="A500" s="8"/>
       <c r="B500" s="10"/>
-      <c r="C500" s="10"/>
+      <c r="C500" s="16"/>
       <c r="D500" s="5"/>
       <c r="E500" s="6"/>
       <c r="F500" s="7"/>
@@ -12039,67 +12082,67 @@
     <row r="16" spans="1:16">
       <c r="A16" s="10" t="str">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!B16)</f>
-        <v/>
+        <v>REMSA</v>
       </c>
       <c r="B16" s="10" t="str">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!C16)</f>
-        <v/>
+        <v>014132</v>
       </c>
       <c r="C16" s="5" t="str">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!D16)</f>
-        <v/>
-      </c>
-      <c r="D16" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D16" s="11">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!E16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!F16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!G16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="12" t="str">
+        <v>6000</v>
+      </c>
+      <c r="G16" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H16" s="13" t="str">
+        <v>6000</v>
+      </c>
+      <c r="H16" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I16" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I16" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J16" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K16" s="12" t="str">
+        <v>6000</v>
+      </c>
+      <c r="K16" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!M16)</f>
-        <v/>
-      </c>
-      <c r="M16" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M16" s="10">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!N16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!O16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!P16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
         <f>IF(Инвентаризация!C16="","",Инвентаризация!Q16)</f>
-        <v/>
+        <v>46242</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -44090,7 +44133,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -44106,14 +44149,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -44138,7 +44181,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>151800</v>
+        <v>157800</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -44154,7 +44197,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>151800</v>
+        <v>157800</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -44163,7 +44206,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -44180,7 +44223,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -44189,7 +44232,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -44198,7 +44241,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -44207,7 +44250,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44216,7 +44259,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44225,7 +44268,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/stock_v1.0.xlsx
+++ b/stock_v1.0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="72">
   <si>
     <t>Дата добавления</t>
   </si>
@@ -232,6 +232,12 @@
   <si>
     <t>014132</t>
   </si>
+  <si>
+    <t>HP1045</t>
+  </si>
+  <si>
+    <t>HSB</t>
+  </si>
 </sst>
 </file>
 
@@ -370,9 +376,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -381,6 +384,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -554,7 +560,7 @@
   <cols>
     <col min="1" max="1" width="15" style="9" customWidth="1"/>
     <col min="2" max="2" width="16.25" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16" style="17" customWidth="1"/>
+    <col min="3" max="3" width="16" style="16" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="7" width="18" customWidth="1"/>
@@ -572,7 +578,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -628,7 +634,7 @@
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -682,7 +688,7 @@
       <c r="B3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -736,7 +742,7 @@
       <c r="B4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -786,7 +792,7 @@
       <c r="B5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -838,7 +844,7 @@
       <c r="B6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -888,7 +894,7 @@
       <c r="B7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>54</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -940,7 +946,7 @@
       <c r="B8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -990,7 +996,7 @@
       <c r="B9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1040,7 +1046,7 @@
       <c r="B10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>59</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1090,7 +1096,7 @@
       <c r="B11" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="15">
         <v>9116</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1140,7 +1146,7 @@
       <c r="B12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1190,7 +1196,7 @@
       <c r="B13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>65</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1240,7 +1246,7 @@
       <c r="B14" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="15">
         <v>2176603</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -1290,7 +1296,7 @@
       <c r="B15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="15">
         <v>228220</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -1340,7 +1346,7 @@
       <c r="B16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -1382,29 +1388,59 @@
       <c r="R16" s="10"/>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="8"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="A17" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>4000</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="10">
+        <v>173207490</v>
+      </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
-      <c r="Q17" s="8"/>
+      <c r="Q17" s="8">
+        <v>46242</v>
+      </c>
       <c r="R17" s="10"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="8"/>
       <c r="B18" s="10"/>
-      <c r="C18" s="16"/>
+      <c r="C18" s="15"/>
       <c r="D18" s="5"/>
       <c r="E18" s="6"/>
       <c r="F18" s="7"/>
@@ -1424,7 +1460,7 @@
     <row r="19" spans="1:18">
       <c r="A19" s="8"/>
       <c r="B19" s="10"/>
-      <c r="C19" s="16"/>
+      <c r="C19" s="15"/>
       <c r="D19" s="5"/>
       <c r="E19" s="6"/>
       <c r="F19" s="7"/>
@@ -1444,7 +1480,7 @@
     <row r="20" spans="1:18">
       <c r="A20" s="8"/>
       <c r="B20" s="10"/>
-      <c r="C20" s="16"/>
+      <c r="C20" s="15"/>
       <c r="D20" s="5"/>
       <c r="E20" s="6"/>
       <c r="F20" s="7"/>
@@ -1464,7 +1500,7 @@
     <row r="21" spans="1:18">
       <c r="A21" s="8"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="16"/>
+      <c r="C21" s="15"/>
       <c r="D21" s="5"/>
       <c r="E21" s="6"/>
       <c r="F21" s="7"/>
@@ -1484,7 +1520,7 @@
     <row r="22" spans="1:18">
       <c r="A22" s="8"/>
       <c r="B22" s="10"/>
-      <c r="C22" s="16"/>
+      <c r="C22" s="15"/>
       <c r="D22" s="5"/>
       <c r="E22" s="6"/>
       <c r="F22" s="7"/>
@@ -1504,7 +1540,7 @@
     <row r="23" spans="1:18">
       <c r="A23" s="8"/>
       <c r="B23" s="10"/>
-      <c r="C23" s="16"/>
+      <c r="C23" s="15"/>
       <c r="D23" s="5"/>
       <c r="E23" s="6"/>
       <c r="F23" s="7"/>
@@ -1524,7 +1560,7 @@
     <row r="24" spans="1:18">
       <c r="A24" s="8"/>
       <c r="B24" s="10"/>
-      <c r="C24" s="16"/>
+      <c r="C24" s="15"/>
       <c r="D24" s="5"/>
       <c r="E24" s="6"/>
       <c r="F24" s="7"/>
@@ -1544,7 +1580,7 @@
     <row r="25" spans="1:18">
       <c r="A25" s="8"/>
       <c r="B25" s="10"/>
-      <c r="C25" s="16"/>
+      <c r="C25" s="15"/>
       <c r="D25" s="5"/>
       <c r="E25" s="6"/>
       <c r="F25" s="7"/>
@@ -1564,7 +1600,7 @@
     <row r="26" spans="1:18">
       <c r="A26" s="8"/>
       <c r="B26" s="10"/>
-      <c r="C26" s="16"/>
+      <c r="C26" s="15"/>
       <c r="D26" s="5"/>
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
@@ -1584,7 +1620,7 @@
     <row r="27" spans="1:18">
       <c r="A27" s="8"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="16"/>
+      <c r="C27" s="15"/>
       <c r="D27" s="5"/>
       <c r="E27" s="6"/>
       <c r="F27" s="7"/>
@@ -1604,7 +1640,7 @@
     <row r="28" spans="1:18">
       <c r="A28" s="8"/>
       <c r="B28" s="10"/>
-      <c r="C28" s="16"/>
+      <c r="C28" s="15"/>
       <c r="D28" s="5"/>
       <c r="E28" s="6"/>
       <c r="F28" s="7"/>
@@ -1624,7 +1660,7 @@
     <row r="29" spans="1:18">
       <c r="A29" s="8"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="16"/>
+      <c r="C29" s="15"/>
       <c r="D29" s="5"/>
       <c r="E29" s="6"/>
       <c r="F29" s="7"/>
@@ -1644,7 +1680,7 @@
     <row r="30" spans="1:18">
       <c r="A30" s="8"/>
       <c r="B30" s="10"/>
-      <c r="C30" s="16"/>
+      <c r="C30" s="15"/>
       <c r="D30" s="5"/>
       <c r="E30" s="6"/>
       <c r="F30" s="7"/>
@@ -1664,7 +1700,7 @@
     <row r="31" spans="1:18">
       <c r="A31" s="8"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="16"/>
+      <c r="C31" s="15"/>
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
       <c r="F31" s="7"/>
@@ -1684,7 +1720,7 @@
     <row r="32" spans="1:18">
       <c r="A32" s="8"/>
       <c r="B32" s="10"/>
-      <c r="C32" s="16"/>
+      <c r="C32" s="15"/>
       <c r="D32" s="5"/>
       <c r="E32" s="6"/>
       <c r="F32" s="7"/>
@@ -1704,7 +1740,7 @@
     <row r="33" spans="1:18">
       <c r="A33" s="8"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="16"/>
+      <c r="C33" s="15"/>
       <c r="D33" s="5"/>
       <c r="E33" s="6"/>
       <c r="F33" s="7"/>
@@ -1724,7 +1760,7 @@
     <row r="34" spans="1:18">
       <c r="A34" s="8"/>
       <c r="B34" s="10"/>
-      <c r="C34" s="16"/>
+      <c r="C34" s="15"/>
       <c r="D34" s="5"/>
       <c r="E34" s="6"/>
       <c r="F34" s="7"/>
@@ -1744,7 +1780,7 @@
     <row r="35" spans="1:18">
       <c r="A35" s="8"/>
       <c r="B35" s="10"/>
-      <c r="C35" s="16"/>
+      <c r="C35" s="15"/>
       <c r="D35" s="5"/>
       <c r="E35" s="6"/>
       <c r="F35" s="7"/>
@@ -1764,7 +1800,7 @@
     <row r="36" spans="1:18">
       <c r="A36" s="8"/>
       <c r="B36" s="10"/>
-      <c r="C36" s="16"/>
+      <c r="C36" s="15"/>
       <c r="D36" s="5"/>
       <c r="E36" s="6"/>
       <c r="F36" s="7"/>
@@ -1784,7 +1820,7 @@
     <row r="37" spans="1:18">
       <c r="A37" s="8"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="16"/>
+      <c r="C37" s="15"/>
       <c r="D37" s="5"/>
       <c r="E37" s="6"/>
       <c r="F37" s="7"/>
@@ -1804,7 +1840,7 @@
     <row r="38" spans="1:18">
       <c r="A38" s="8"/>
       <c r="B38" s="10"/>
-      <c r="C38" s="16"/>
+      <c r="C38" s="15"/>
       <c r="D38" s="5"/>
       <c r="E38" s="6"/>
       <c r="F38" s="7"/>
@@ -1824,7 +1860,7 @@
     <row r="39" spans="1:18">
       <c r="A39" s="8"/>
       <c r="B39" s="10"/>
-      <c r="C39" s="16"/>
+      <c r="C39" s="15"/>
       <c r="D39" s="5"/>
       <c r="E39" s="6"/>
       <c r="F39" s="7"/>
@@ -1844,7 +1880,7 @@
     <row r="40" spans="1:18">
       <c r="A40" s="8"/>
       <c r="B40" s="10"/>
-      <c r="C40" s="16"/>
+      <c r="C40" s="15"/>
       <c r="D40" s="5"/>
       <c r="E40" s="6"/>
       <c r="F40" s="7"/>
@@ -1864,7 +1900,7 @@
     <row r="41" spans="1:18">
       <c r="A41" s="8"/>
       <c r="B41" s="10"/>
-      <c r="C41" s="16"/>
+      <c r="C41" s="15"/>
       <c r="D41" s="5"/>
       <c r="E41" s="6"/>
       <c r="F41" s="7"/>
@@ -1884,7 +1920,7 @@
     <row r="42" spans="1:18">
       <c r="A42" s="8"/>
       <c r="B42" s="10"/>
-      <c r="C42" s="16"/>
+      <c r="C42" s="15"/>
       <c r="D42" s="5"/>
       <c r="E42" s="6"/>
       <c r="F42" s="7"/>
@@ -1904,7 +1940,7 @@
     <row r="43" spans="1:18">
       <c r="A43" s="8"/>
       <c r="B43" s="10"/>
-      <c r="C43" s="16"/>
+      <c r="C43" s="15"/>
       <c r="D43" s="5"/>
       <c r="E43" s="6"/>
       <c r="F43" s="7"/>
@@ -1924,7 +1960,7 @@
     <row r="44" spans="1:18">
       <c r="A44" s="8"/>
       <c r="B44" s="10"/>
-      <c r="C44" s="16"/>
+      <c r="C44" s="15"/>
       <c r="D44" s="5"/>
       <c r="E44" s="6"/>
       <c r="F44" s="7"/>
@@ -1944,7 +1980,7 @@
     <row r="45" spans="1:18">
       <c r="A45" s="8"/>
       <c r="B45" s="10"/>
-      <c r="C45" s="16"/>
+      <c r="C45" s="15"/>
       <c r="D45" s="5"/>
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
@@ -1964,7 +2000,7 @@
     <row r="46" spans="1:18">
       <c r="A46" s="8"/>
       <c r="B46" s="10"/>
-      <c r="C46" s="16"/>
+      <c r="C46" s="15"/>
       <c r="D46" s="5"/>
       <c r="E46" s="6"/>
       <c r="F46" s="7"/>
@@ -1984,7 +2020,7 @@
     <row r="47" spans="1:18">
       <c r="A47" s="8"/>
       <c r="B47" s="10"/>
-      <c r="C47" s="16"/>
+      <c r="C47" s="15"/>
       <c r="D47" s="5"/>
       <c r="E47" s="6"/>
       <c r="F47" s="7"/>
@@ -2004,7 +2040,7 @@
     <row r="48" spans="1:18">
       <c r="A48" s="8"/>
       <c r="B48" s="10"/>
-      <c r="C48" s="16"/>
+      <c r="C48" s="15"/>
       <c r="D48" s="5"/>
       <c r="E48" s="6"/>
       <c r="F48" s="7"/>
@@ -2024,7 +2060,7 @@
     <row r="49" spans="1:18">
       <c r="A49" s="8"/>
       <c r="B49" s="10"/>
-      <c r="C49" s="16"/>
+      <c r="C49" s="15"/>
       <c r="D49" s="5"/>
       <c r="E49" s="6"/>
       <c r="F49" s="7"/>
@@ -2044,7 +2080,7 @@
     <row r="50" spans="1:18">
       <c r="A50" s="8"/>
       <c r="B50" s="10"/>
-      <c r="C50" s="16"/>
+      <c r="C50" s="15"/>
       <c r="D50" s="5"/>
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
@@ -2064,7 +2100,7 @@
     <row r="51" spans="1:18">
       <c r="A51" s="8"/>
       <c r="B51" s="10"/>
-      <c r="C51" s="16"/>
+      <c r="C51" s="15"/>
       <c r="D51" s="5"/>
       <c r="E51" s="6"/>
       <c r="F51" s="7"/>
@@ -2084,7 +2120,7 @@
     <row r="52" spans="1:18">
       <c r="A52" s="8"/>
       <c r="B52" s="10"/>
-      <c r="C52" s="16"/>
+      <c r="C52" s="15"/>
       <c r="D52" s="5"/>
       <c r="E52" s="6"/>
       <c r="F52" s="7"/>
@@ -2104,7 +2140,7 @@
     <row r="53" spans="1:18">
       <c r="A53" s="8"/>
       <c r="B53" s="10"/>
-      <c r="C53" s="16"/>
+      <c r="C53" s="15"/>
       <c r="D53" s="5"/>
       <c r="E53" s="6"/>
       <c r="F53" s="7"/>
@@ -2124,7 +2160,7 @@
     <row r="54" spans="1:18">
       <c r="A54" s="8"/>
       <c r="B54" s="10"/>
-      <c r="C54" s="16"/>
+      <c r="C54" s="15"/>
       <c r="D54" s="5"/>
       <c r="E54" s="6"/>
       <c r="F54" s="7"/>
@@ -2144,7 +2180,7 @@
     <row r="55" spans="1:18">
       <c r="A55" s="8"/>
       <c r="B55" s="10"/>
-      <c r="C55" s="16"/>
+      <c r="C55" s="15"/>
       <c r="D55" s="5"/>
       <c r="E55" s="6"/>
       <c r="F55" s="7"/>
@@ -2164,7 +2200,7 @@
     <row r="56" spans="1:18">
       <c r="A56" s="8"/>
       <c r="B56" s="10"/>
-      <c r="C56" s="16"/>
+      <c r="C56" s="15"/>
       <c r="D56" s="5"/>
       <c r="E56" s="6"/>
       <c r="F56" s="7"/>
@@ -2184,7 +2220,7 @@
     <row r="57" spans="1:18">
       <c r="A57" s="8"/>
       <c r="B57" s="10"/>
-      <c r="C57" s="16"/>
+      <c r="C57" s="15"/>
       <c r="D57" s="5"/>
       <c r="E57" s="6"/>
       <c r="F57" s="7"/>
@@ -2204,7 +2240,7 @@
     <row r="58" spans="1:18">
       <c r="A58" s="8"/>
       <c r="B58" s="10"/>
-      <c r="C58" s="16"/>
+      <c r="C58" s="15"/>
       <c r="D58" s="5"/>
       <c r="E58" s="6"/>
       <c r="F58" s="7"/>
@@ -2224,7 +2260,7 @@
     <row r="59" spans="1:18">
       <c r="A59" s="8"/>
       <c r="B59" s="10"/>
-      <c r="C59" s="16"/>
+      <c r="C59" s="15"/>
       <c r="D59" s="5"/>
       <c r="E59" s="6"/>
       <c r="F59" s="7"/>
@@ -2244,7 +2280,7 @@
     <row r="60" spans="1:18">
       <c r="A60" s="8"/>
       <c r="B60" s="10"/>
-      <c r="C60" s="16"/>
+      <c r="C60" s="15"/>
       <c r="D60" s="5"/>
       <c r="E60" s="6"/>
       <c r="F60" s="7"/>
@@ -2264,7 +2300,7 @@
     <row r="61" spans="1:18">
       <c r="A61" s="8"/>
       <c r="B61" s="10"/>
-      <c r="C61" s="16"/>
+      <c r="C61" s="15"/>
       <c r="D61" s="5"/>
       <c r="E61" s="6"/>
       <c r="F61" s="7"/>
@@ -2284,7 +2320,7 @@
     <row r="62" spans="1:18">
       <c r="A62" s="8"/>
       <c r="B62" s="10"/>
-      <c r="C62" s="16"/>
+      <c r="C62" s="15"/>
       <c r="D62" s="5"/>
       <c r="E62" s="6"/>
       <c r="F62" s="7"/>
@@ -2304,7 +2340,7 @@
     <row r="63" spans="1:18">
       <c r="A63" s="8"/>
       <c r="B63" s="10"/>
-      <c r="C63" s="16"/>
+      <c r="C63" s="15"/>
       <c r="D63" s="5"/>
       <c r="E63" s="6"/>
       <c r="F63" s="7"/>
@@ -2324,7 +2360,7 @@
     <row r="64" spans="1:18">
       <c r="A64" s="8"/>
       <c r="B64" s="10"/>
-      <c r="C64" s="16"/>
+      <c r="C64" s="15"/>
       <c r="D64" s="5"/>
       <c r="E64" s="6"/>
       <c r="F64" s="7"/>
@@ -2344,7 +2380,7 @@
     <row r="65" spans="1:18">
       <c r="A65" s="8"/>
       <c r="B65" s="10"/>
-      <c r="C65" s="16"/>
+      <c r="C65" s="15"/>
       <c r="D65" s="5"/>
       <c r="E65" s="6"/>
       <c r="F65" s="7"/>
@@ -2364,7 +2400,7 @@
     <row r="66" spans="1:18">
       <c r="A66" s="8"/>
       <c r="B66" s="10"/>
-      <c r="C66" s="16"/>
+      <c r="C66" s="15"/>
       <c r="D66" s="5"/>
       <c r="E66" s="6"/>
       <c r="F66" s="7"/>
@@ -2384,7 +2420,7 @@
     <row r="67" spans="1:18">
       <c r="A67" s="8"/>
       <c r="B67" s="10"/>
-      <c r="C67" s="16"/>
+      <c r="C67" s="15"/>
       <c r="D67" s="5"/>
       <c r="E67" s="6"/>
       <c r="F67" s="7"/>
@@ -2404,7 +2440,7 @@
     <row r="68" spans="1:18">
       <c r="A68" s="8"/>
       <c r="B68" s="10"/>
-      <c r="C68" s="16"/>
+      <c r="C68" s="15"/>
       <c r="D68" s="5"/>
       <c r="E68" s="6"/>
       <c r="F68" s="7"/>
@@ -2424,7 +2460,7 @@
     <row r="69" spans="1:18">
       <c r="A69" s="8"/>
       <c r="B69" s="10"/>
-      <c r="C69" s="16"/>
+      <c r="C69" s="15"/>
       <c r="D69" s="5"/>
       <c r="E69" s="6"/>
       <c r="F69" s="7"/>
@@ -2444,7 +2480,7 @@
     <row r="70" spans="1:18">
       <c r="A70" s="8"/>
       <c r="B70" s="10"/>
-      <c r="C70" s="16"/>
+      <c r="C70" s="15"/>
       <c r="D70" s="5"/>
       <c r="E70" s="6"/>
       <c r="F70" s="7"/>
@@ -2464,7 +2500,7 @@
     <row r="71" spans="1:18">
       <c r="A71" s="8"/>
       <c r="B71" s="10"/>
-      <c r="C71" s="16"/>
+      <c r="C71" s="15"/>
       <c r="D71" s="5"/>
       <c r="E71" s="6"/>
       <c r="F71" s="7"/>
@@ -2484,7 +2520,7 @@
     <row r="72" spans="1:18">
       <c r="A72" s="8"/>
       <c r="B72" s="10"/>
-      <c r="C72" s="16"/>
+      <c r="C72" s="15"/>
       <c r="D72" s="5"/>
       <c r="E72" s="6"/>
       <c r="F72" s="7"/>
@@ -2504,7 +2540,7 @@
     <row r="73" spans="1:18">
       <c r="A73" s="8"/>
       <c r="B73" s="10"/>
-      <c r="C73" s="16"/>
+      <c r="C73" s="15"/>
       <c r="D73" s="5"/>
       <c r="E73" s="6"/>
       <c r="F73" s="7"/>
@@ -2524,7 +2560,7 @@
     <row r="74" spans="1:18">
       <c r="A74" s="8"/>
       <c r="B74" s="10"/>
-      <c r="C74" s="16"/>
+      <c r="C74" s="15"/>
       <c r="D74" s="5"/>
       <c r="E74" s="6"/>
       <c r="F74" s="7"/>
@@ -2544,7 +2580,7 @@
     <row r="75" spans="1:18">
       <c r="A75" s="8"/>
       <c r="B75" s="10"/>
-      <c r="C75" s="16"/>
+      <c r="C75" s="15"/>
       <c r="D75" s="5"/>
       <c r="E75" s="6"/>
       <c r="F75" s="7"/>
@@ -2564,7 +2600,7 @@
     <row r="76" spans="1:18">
       <c r="A76" s="8"/>
       <c r="B76" s="10"/>
-      <c r="C76" s="16"/>
+      <c r="C76" s="15"/>
       <c r="D76" s="5"/>
       <c r="E76" s="6"/>
       <c r="F76" s="7"/>
@@ -2584,7 +2620,7 @@
     <row r="77" spans="1:18">
       <c r="A77" s="8"/>
       <c r="B77" s="10"/>
-      <c r="C77" s="16"/>
+      <c r="C77" s="15"/>
       <c r="D77" s="5"/>
       <c r="E77" s="6"/>
       <c r="F77" s="7"/>
@@ -2604,7 +2640,7 @@
     <row r="78" spans="1:18">
       <c r="A78" s="8"/>
       <c r="B78" s="10"/>
-      <c r="C78" s="16"/>
+      <c r="C78" s="15"/>
       <c r="D78" s="5"/>
       <c r="E78" s="6"/>
       <c r="F78" s="7"/>
@@ -2624,7 +2660,7 @@
     <row r="79" spans="1:18">
       <c r="A79" s="8"/>
       <c r="B79" s="10"/>
-      <c r="C79" s="16"/>
+      <c r="C79" s="15"/>
       <c r="D79" s="5"/>
       <c r="E79" s="6"/>
       <c r="F79" s="7"/>
@@ -2644,7 +2680,7 @@
     <row r="80" spans="1:18">
       <c r="A80" s="8"/>
       <c r="B80" s="10"/>
-      <c r="C80" s="16"/>
+      <c r="C80" s="15"/>
       <c r="D80" s="5"/>
       <c r="E80" s="6"/>
       <c r="F80" s="7"/>
@@ -2664,7 +2700,7 @@
     <row r="81" spans="1:18">
       <c r="A81" s="8"/>
       <c r="B81" s="10"/>
-      <c r="C81" s="16"/>
+      <c r="C81" s="15"/>
       <c r="D81" s="5"/>
       <c r="E81" s="6"/>
       <c r="F81" s="7"/>
@@ -2684,7 +2720,7 @@
     <row r="82" spans="1:18">
       <c r="A82" s="8"/>
       <c r="B82" s="10"/>
-      <c r="C82" s="16"/>
+      <c r="C82" s="15"/>
       <c r="D82" s="5"/>
       <c r="E82" s="6"/>
       <c r="F82" s="7"/>
@@ -2704,7 +2740,7 @@
     <row r="83" spans="1:18">
       <c r="A83" s="8"/>
       <c r="B83" s="10"/>
-      <c r="C83" s="16"/>
+      <c r="C83" s="15"/>
       <c r="D83" s="5"/>
       <c r="E83" s="6"/>
       <c r="F83" s="7"/>
@@ -2724,7 +2760,7 @@
     <row r="84" spans="1:18">
       <c r="A84" s="8"/>
       <c r="B84" s="10"/>
-      <c r="C84" s="16"/>
+      <c r="C84" s="15"/>
       <c r="D84" s="5"/>
       <c r="E84" s="6"/>
       <c r="F84" s="7"/>
@@ -2744,7 +2780,7 @@
     <row r="85" spans="1:18">
       <c r="A85" s="8"/>
       <c r="B85" s="10"/>
-      <c r="C85" s="16"/>
+      <c r="C85" s="15"/>
       <c r="D85" s="5"/>
       <c r="E85" s="6"/>
       <c r="F85" s="7"/>
@@ -2764,7 +2800,7 @@
     <row r="86" spans="1:18">
       <c r="A86" s="8"/>
       <c r="B86" s="10"/>
-      <c r="C86" s="16"/>
+      <c r="C86" s="15"/>
       <c r="D86" s="5"/>
       <c r="E86" s="6"/>
       <c r="F86" s="7"/>
@@ -2784,7 +2820,7 @@
     <row r="87" spans="1:18">
       <c r="A87" s="8"/>
       <c r="B87" s="10"/>
-      <c r="C87" s="16"/>
+      <c r="C87" s="15"/>
       <c r="D87" s="5"/>
       <c r="E87" s="6"/>
       <c r="F87" s="7"/>
@@ -2804,7 +2840,7 @@
     <row r="88" spans="1:18">
       <c r="A88" s="8"/>
       <c r="B88" s="10"/>
-      <c r="C88" s="16"/>
+      <c r="C88" s="15"/>
       <c r="D88" s="5"/>
       <c r="E88" s="6"/>
       <c r="F88" s="7"/>
@@ -2824,7 +2860,7 @@
     <row r="89" spans="1:18">
       <c r="A89" s="8"/>
       <c r="B89" s="10"/>
-      <c r="C89" s="16"/>
+      <c r="C89" s="15"/>
       <c r="D89" s="5"/>
       <c r="E89" s="6"/>
       <c r="F89" s="7"/>
@@ -2844,7 +2880,7 @@
     <row r="90" spans="1:18">
       <c r="A90" s="8"/>
       <c r="B90" s="10"/>
-      <c r="C90" s="16"/>
+      <c r="C90" s="15"/>
       <c r="D90" s="5"/>
       <c r="E90" s="6"/>
       <c r="F90" s="7"/>
@@ -2864,7 +2900,7 @@
     <row r="91" spans="1:18">
       <c r="A91" s="8"/>
       <c r="B91" s="10"/>
-      <c r="C91" s="16"/>
+      <c r="C91" s="15"/>
       <c r="D91" s="5"/>
       <c r="E91" s="6"/>
       <c r="F91" s="7"/>
@@ -2884,7 +2920,7 @@
     <row r="92" spans="1:18">
       <c r="A92" s="8"/>
       <c r="B92" s="10"/>
-      <c r="C92" s="16"/>
+      <c r="C92" s="15"/>
       <c r="D92" s="5"/>
       <c r="E92" s="6"/>
       <c r="F92" s="7"/>
@@ -2904,7 +2940,7 @@
     <row r="93" spans="1:18">
       <c r="A93" s="8"/>
       <c r="B93" s="10"/>
-      <c r="C93" s="16"/>
+      <c r="C93" s="15"/>
       <c r="D93" s="5"/>
       <c r="E93" s="6"/>
       <c r="F93" s="7"/>
@@ -2924,7 +2960,7 @@
     <row r="94" spans="1:18">
       <c r="A94" s="8"/>
       <c r="B94" s="10"/>
-      <c r="C94" s="16"/>
+      <c r="C94" s="15"/>
       <c r="D94" s="5"/>
       <c r="E94" s="6"/>
       <c r="F94" s="7"/>
@@ -2944,7 +2980,7 @@
     <row r="95" spans="1:18">
       <c r="A95" s="8"/>
       <c r="B95" s="10"/>
-      <c r="C95" s="16"/>
+      <c r="C95" s="15"/>
       <c r="D95" s="5"/>
       <c r="E95" s="6"/>
       <c r="F95" s="7"/>
@@ -2964,7 +3000,7 @@
     <row r="96" spans="1:18">
       <c r="A96" s="8"/>
       <c r="B96" s="10"/>
-      <c r="C96" s="16"/>
+      <c r="C96" s="15"/>
       <c r="D96" s="5"/>
       <c r="E96" s="6"/>
       <c r="F96" s="7"/>
@@ -2984,7 +3020,7 @@
     <row r="97" spans="1:18">
       <c r="A97" s="8"/>
       <c r="B97" s="10"/>
-      <c r="C97" s="16"/>
+      <c r="C97" s="15"/>
       <c r="D97" s="5"/>
       <c r="E97" s="6"/>
       <c r="F97" s="7"/>
@@ -3004,7 +3040,7 @@
     <row r="98" spans="1:18">
       <c r="A98" s="8"/>
       <c r="B98" s="10"/>
-      <c r="C98" s="16"/>
+      <c r="C98" s="15"/>
       <c r="D98" s="5"/>
       <c r="E98" s="6"/>
       <c r="F98" s="7"/>
@@ -3024,7 +3060,7 @@
     <row r="99" spans="1:18">
       <c r="A99" s="8"/>
       <c r="B99" s="10"/>
-      <c r="C99" s="16"/>
+      <c r="C99" s="15"/>
       <c r="D99" s="5"/>
       <c r="E99" s="6"/>
       <c r="F99" s="7"/>
@@ -3044,7 +3080,7 @@
     <row r="100" spans="1:18">
       <c r="A100" s="8"/>
       <c r="B100" s="10"/>
-      <c r="C100" s="16"/>
+      <c r="C100" s="15"/>
       <c r="D100" s="5"/>
       <c r="E100" s="6"/>
       <c r="F100" s="7"/>
@@ -3064,7 +3100,7 @@
     <row r="101" spans="1:18">
       <c r="A101" s="8"/>
       <c r="B101" s="10"/>
-      <c r="C101" s="16"/>
+      <c r="C101" s="15"/>
       <c r="D101" s="5"/>
       <c r="E101" s="6"/>
       <c r="F101" s="7"/>
@@ -3084,7 +3120,7 @@
     <row r="102" spans="1:18">
       <c r="A102" s="8"/>
       <c r="B102" s="10"/>
-      <c r="C102" s="16"/>
+      <c r="C102" s="15"/>
       <c r="D102" s="5"/>
       <c r="E102" s="6"/>
       <c r="F102" s="7"/>
@@ -3104,7 +3140,7 @@
     <row r="103" spans="1:18">
       <c r="A103" s="8"/>
       <c r="B103" s="10"/>
-      <c r="C103" s="16"/>
+      <c r="C103" s="15"/>
       <c r="D103" s="5"/>
       <c r="E103" s="6"/>
       <c r="F103" s="7"/>
@@ -3124,7 +3160,7 @@
     <row r="104" spans="1:18">
       <c r="A104" s="8"/>
       <c r="B104" s="10"/>
-      <c r="C104" s="16"/>
+      <c r="C104" s="15"/>
       <c r="D104" s="5"/>
       <c r="E104" s="6"/>
       <c r="F104" s="7"/>
@@ -3144,7 +3180,7 @@
     <row r="105" spans="1:18">
       <c r="A105" s="8"/>
       <c r="B105" s="10"/>
-      <c r="C105" s="16"/>
+      <c r="C105" s="15"/>
       <c r="D105" s="5"/>
       <c r="E105" s="6"/>
       <c r="F105" s="7"/>
@@ -3164,7 +3200,7 @@
     <row r="106" spans="1:18">
       <c r="A106" s="8"/>
       <c r="B106" s="10"/>
-      <c r="C106" s="16"/>
+      <c r="C106" s="15"/>
       <c r="D106" s="5"/>
       <c r="E106" s="6"/>
       <c r="F106" s="7"/>
@@ -3184,7 +3220,7 @@
     <row r="107" spans="1:18">
       <c r="A107" s="8"/>
       <c r="B107" s="10"/>
-      <c r="C107" s="16"/>
+      <c r="C107" s="15"/>
       <c r="D107" s="5"/>
       <c r="E107" s="6"/>
       <c r="F107" s="7"/>
@@ -3204,7 +3240,7 @@
     <row r="108" spans="1:18">
       <c r="A108" s="8"/>
       <c r="B108" s="10"/>
-      <c r="C108" s="16"/>
+      <c r="C108" s="15"/>
       <c r="D108" s="5"/>
       <c r="E108" s="6"/>
       <c r="F108" s="7"/>
@@ -3224,7 +3260,7 @@
     <row r="109" spans="1:18">
       <c r="A109" s="8"/>
       <c r="B109" s="10"/>
-      <c r="C109" s="16"/>
+      <c r="C109" s="15"/>
       <c r="D109" s="5"/>
       <c r="E109" s="6"/>
       <c r="F109" s="7"/>
@@ -3244,7 +3280,7 @@
     <row r="110" spans="1:18">
       <c r="A110" s="8"/>
       <c r="B110" s="10"/>
-      <c r="C110" s="16"/>
+      <c r="C110" s="15"/>
       <c r="D110" s="5"/>
       <c r="E110" s="6"/>
       <c r="F110" s="7"/>
@@ -3264,7 +3300,7 @@
     <row r="111" spans="1:18">
       <c r="A111" s="8"/>
       <c r="B111" s="10"/>
-      <c r="C111" s="16"/>
+      <c r="C111" s="15"/>
       <c r="D111" s="5"/>
       <c r="E111" s="6"/>
       <c r="F111" s="7"/>
@@ -3284,7 +3320,7 @@
     <row r="112" spans="1:18">
       <c r="A112" s="8"/>
       <c r="B112" s="10"/>
-      <c r="C112" s="16"/>
+      <c r="C112" s="15"/>
       <c r="D112" s="5"/>
       <c r="E112" s="6"/>
       <c r="F112" s="7"/>
@@ -3304,7 +3340,7 @@
     <row r="113" spans="1:18">
       <c r="A113" s="8"/>
       <c r="B113" s="10"/>
-      <c r="C113" s="16"/>
+      <c r="C113" s="15"/>
       <c r="D113" s="5"/>
       <c r="E113" s="6"/>
       <c r="F113" s="7"/>
@@ -3324,7 +3360,7 @@
     <row r="114" spans="1:18">
       <c r="A114" s="8"/>
       <c r="B114" s="10"/>
-      <c r="C114" s="16"/>
+      <c r="C114" s="15"/>
       <c r="D114" s="5"/>
       <c r="E114" s="6"/>
       <c r="F114" s="7"/>
@@ -3344,7 +3380,7 @@
     <row r="115" spans="1:18">
       <c r="A115" s="8"/>
       <c r="B115" s="10"/>
-      <c r="C115" s="16"/>
+      <c r="C115" s="15"/>
       <c r="D115" s="5"/>
       <c r="E115" s="6"/>
       <c r="F115" s="7"/>
@@ -3364,7 +3400,7 @@
     <row r="116" spans="1:18">
       <c r="A116" s="8"/>
       <c r="B116" s="10"/>
-      <c r="C116" s="16"/>
+      <c r="C116" s="15"/>
       <c r="D116" s="5"/>
       <c r="E116" s="6"/>
       <c r="F116" s="7"/>
@@ -3384,7 +3420,7 @@
     <row r="117" spans="1:18">
       <c r="A117" s="8"/>
       <c r="B117" s="10"/>
-      <c r="C117" s="16"/>
+      <c r="C117" s="15"/>
       <c r="D117" s="5"/>
       <c r="E117" s="6"/>
       <c r="F117" s="7"/>
@@ -3404,7 +3440,7 @@
     <row r="118" spans="1:18">
       <c r="A118" s="8"/>
       <c r="B118" s="10"/>
-      <c r="C118" s="16"/>
+      <c r="C118" s="15"/>
       <c r="D118" s="5"/>
       <c r="E118" s="6"/>
       <c r="F118" s="7"/>
@@ -3424,7 +3460,7 @@
     <row r="119" spans="1:18">
       <c r="A119" s="8"/>
       <c r="B119" s="10"/>
-      <c r="C119" s="16"/>
+      <c r="C119" s="15"/>
       <c r="D119" s="5"/>
       <c r="E119" s="6"/>
       <c r="F119" s="7"/>
@@ -3444,7 +3480,7 @@
     <row r="120" spans="1:18">
       <c r="A120" s="8"/>
       <c r="B120" s="10"/>
-      <c r="C120" s="16"/>
+      <c r="C120" s="15"/>
       <c r="D120" s="5"/>
       <c r="E120" s="6"/>
       <c r="F120" s="7"/>
@@ -3464,7 +3500,7 @@
     <row r="121" spans="1:18">
       <c r="A121" s="8"/>
       <c r="B121" s="10"/>
-      <c r="C121" s="16"/>
+      <c r="C121" s="15"/>
       <c r="D121" s="5"/>
       <c r="E121" s="6"/>
       <c r="F121" s="7"/>
@@ -3484,7 +3520,7 @@
     <row r="122" spans="1:18">
       <c r="A122" s="8"/>
       <c r="B122" s="10"/>
-      <c r="C122" s="16"/>
+      <c r="C122" s="15"/>
       <c r="D122" s="5"/>
       <c r="E122" s="6"/>
       <c r="F122" s="7"/>
@@ -3504,7 +3540,7 @@
     <row r="123" spans="1:18">
       <c r="A123" s="8"/>
       <c r="B123" s="10"/>
-      <c r="C123" s="16"/>
+      <c r="C123" s="15"/>
       <c r="D123" s="5"/>
       <c r="E123" s="6"/>
       <c r="F123" s="7"/>
@@ -3524,7 +3560,7 @@
     <row r="124" spans="1:18">
       <c r="A124" s="8"/>
       <c r="B124" s="10"/>
-      <c r="C124" s="16"/>
+      <c r="C124" s="15"/>
       <c r="D124" s="5"/>
       <c r="E124" s="6"/>
       <c r="F124" s="7"/>
@@ -3544,7 +3580,7 @@
     <row r="125" spans="1:18">
       <c r="A125" s="8"/>
       <c r="B125" s="10"/>
-      <c r="C125" s="16"/>
+      <c r="C125" s="15"/>
       <c r="D125" s="5"/>
       <c r="E125" s="6"/>
       <c r="F125" s="7"/>
@@ -3564,7 +3600,7 @@
     <row r="126" spans="1:18">
       <c r="A126" s="8"/>
       <c r="B126" s="10"/>
-      <c r="C126" s="16"/>
+      <c r="C126" s="15"/>
       <c r="D126" s="5"/>
       <c r="E126" s="6"/>
       <c r="F126" s="7"/>
@@ -3584,7 +3620,7 @@
     <row r="127" spans="1:18">
       <c r="A127" s="8"/>
       <c r="B127" s="10"/>
-      <c r="C127" s="16"/>
+      <c r="C127" s="15"/>
       <c r="D127" s="5"/>
       <c r="E127" s="6"/>
       <c r="F127" s="7"/>
@@ -3604,7 +3640,7 @@
     <row r="128" spans="1:18">
       <c r="A128" s="8"/>
       <c r="B128" s="10"/>
-      <c r="C128" s="16"/>
+      <c r="C128" s="15"/>
       <c r="D128" s="5"/>
       <c r="E128" s="6"/>
       <c r="F128" s="7"/>
@@ -3624,7 +3660,7 @@
     <row r="129" spans="1:18">
       <c r="A129" s="8"/>
       <c r="B129" s="10"/>
-      <c r="C129" s="16"/>
+      <c r="C129" s="15"/>
       <c r="D129" s="5"/>
       <c r="E129" s="6"/>
       <c r="F129" s="7"/>
@@ -3644,7 +3680,7 @@
     <row r="130" spans="1:18">
       <c r="A130" s="8"/>
       <c r="B130" s="10"/>
-      <c r="C130" s="16"/>
+      <c r="C130" s="15"/>
       <c r="D130" s="5"/>
       <c r="E130" s="6"/>
       <c r="F130" s="7"/>
@@ -3664,7 +3700,7 @@
     <row r="131" spans="1:18">
       <c r="A131" s="8"/>
       <c r="B131" s="10"/>
-      <c r="C131" s="16"/>
+      <c r="C131" s="15"/>
       <c r="D131" s="5"/>
       <c r="E131" s="6"/>
       <c r="F131" s="7"/>
@@ -3684,7 +3720,7 @@
     <row r="132" spans="1:18">
       <c r="A132" s="8"/>
       <c r="B132" s="10"/>
-      <c r="C132" s="16"/>
+      <c r="C132" s="15"/>
       <c r="D132" s="5"/>
       <c r="E132" s="6"/>
       <c r="F132" s="7"/>
@@ -3704,7 +3740,7 @@
     <row r="133" spans="1:18">
       <c r="A133" s="8"/>
       <c r="B133" s="10"/>
-      <c r="C133" s="16"/>
+      <c r="C133" s="15"/>
       <c r="D133" s="5"/>
       <c r="E133" s="6"/>
       <c r="F133" s="7"/>
@@ -3724,7 +3760,7 @@
     <row r="134" spans="1:18">
       <c r="A134" s="8"/>
       <c r="B134" s="10"/>
-      <c r="C134" s="16"/>
+      <c r="C134" s="15"/>
       <c r="D134" s="5"/>
       <c r="E134" s="6"/>
       <c r="F134" s="7"/>
@@ -3744,7 +3780,7 @@
     <row r="135" spans="1:18">
       <c r="A135" s="8"/>
       <c r="B135" s="10"/>
-      <c r="C135" s="16"/>
+      <c r="C135" s="15"/>
       <c r="D135" s="5"/>
       <c r="E135" s="6"/>
       <c r="F135" s="7"/>
@@ -3764,7 +3800,7 @@
     <row r="136" spans="1:18">
       <c r="A136" s="8"/>
       <c r="B136" s="10"/>
-      <c r="C136" s="16"/>
+      <c r="C136" s="15"/>
       <c r="D136" s="5"/>
       <c r="E136" s="6"/>
       <c r="F136" s="7"/>
@@ -3784,7 +3820,7 @@
     <row r="137" spans="1:18">
       <c r="A137" s="8"/>
       <c r="B137" s="10"/>
-      <c r="C137" s="16"/>
+      <c r="C137" s="15"/>
       <c r="D137" s="5"/>
       <c r="E137" s="6"/>
       <c r="F137" s="7"/>
@@ -3804,7 +3840,7 @@
     <row r="138" spans="1:18">
       <c r="A138" s="8"/>
       <c r="B138" s="10"/>
-      <c r="C138" s="16"/>
+      <c r="C138" s="15"/>
       <c r="D138" s="5"/>
       <c r="E138" s="6"/>
       <c r="F138" s="7"/>
@@ -3824,7 +3860,7 @@
     <row r="139" spans="1:18">
       <c r="A139" s="8"/>
       <c r="B139" s="10"/>
-      <c r="C139" s="16"/>
+      <c r="C139" s="15"/>
       <c r="D139" s="5"/>
       <c r="E139" s="6"/>
       <c r="F139" s="7"/>
@@ -3844,7 +3880,7 @@
     <row r="140" spans="1:18">
       <c r="A140" s="8"/>
       <c r="B140" s="10"/>
-      <c r="C140" s="16"/>
+      <c r="C140" s="15"/>
       <c r="D140" s="5"/>
       <c r="E140" s="6"/>
       <c r="F140" s="7"/>
@@ -3864,7 +3900,7 @@
     <row r="141" spans="1:18">
       <c r="A141" s="8"/>
       <c r="B141" s="10"/>
-      <c r="C141" s="16"/>
+      <c r="C141" s="15"/>
       <c r="D141" s="5"/>
       <c r="E141" s="6"/>
       <c r="F141" s="7"/>
@@ -3884,7 +3920,7 @@
     <row r="142" spans="1:18">
       <c r="A142" s="8"/>
       <c r="B142" s="10"/>
-      <c r="C142" s="16"/>
+      <c r="C142" s="15"/>
       <c r="D142" s="5"/>
       <c r="E142" s="6"/>
       <c r="F142" s="7"/>
@@ -3904,7 +3940,7 @@
     <row r="143" spans="1:18">
       <c r="A143" s="8"/>
       <c r="B143" s="10"/>
-      <c r="C143" s="16"/>
+      <c r="C143" s="15"/>
       <c r="D143" s="5"/>
       <c r="E143" s="6"/>
       <c r="F143" s="7"/>
@@ -3924,7 +3960,7 @@
     <row r="144" spans="1:18">
       <c r="A144" s="8"/>
       <c r="B144" s="10"/>
-      <c r="C144" s="16"/>
+      <c r="C144" s="15"/>
       <c r="D144" s="5"/>
       <c r="E144" s="6"/>
       <c r="F144" s="7"/>
@@ -3944,7 +3980,7 @@
     <row r="145" spans="1:18">
       <c r="A145" s="8"/>
       <c r="B145" s="10"/>
-      <c r="C145" s="16"/>
+      <c r="C145" s="15"/>
       <c r="D145" s="5"/>
       <c r="E145" s="6"/>
       <c r="F145" s="7"/>
@@ -3964,7 +4000,7 @@
     <row r="146" spans="1:18">
       <c r="A146" s="8"/>
       <c r="B146" s="10"/>
-      <c r="C146" s="16"/>
+      <c r="C146" s="15"/>
       <c r="D146" s="5"/>
       <c r="E146" s="6"/>
       <c r="F146" s="7"/>
@@ -3984,7 +4020,7 @@
     <row r="147" spans="1:18">
       <c r="A147" s="8"/>
       <c r="B147" s="10"/>
-      <c r="C147" s="16"/>
+      <c r="C147" s="15"/>
       <c r="D147" s="5"/>
       <c r="E147" s="6"/>
       <c r="F147" s="7"/>
@@ -4004,7 +4040,7 @@
     <row r="148" spans="1:18">
       <c r="A148" s="8"/>
       <c r="B148" s="10"/>
-      <c r="C148" s="16"/>
+      <c r="C148" s="15"/>
       <c r="D148" s="5"/>
       <c r="E148" s="6"/>
       <c r="F148" s="7"/>
@@ -4024,7 +4060,7 @@
     <row r="149" spans="1:18">
       <c r="A149" s="8"/>
       <c r="B149" s="10"/>
-      <c r="C149" s="16"/>
+      <c r="C149" s="15"/>
       <c r="D149" s="5"/>
       <c r="E149" s="6"/>
       <c r="F149" s="7"/>
@@ -4044,7 +4080,7 @@
     <row r="150" spans="1:18">
       <c r="A150" s="8"/>
       <c r="B150" s="10"/>
-      <c r="C150" s="16"/>
+      <c r="C150" s="15"/>
       <c r="D150" s="5"/>
       <c r="E150" s="6"/>
       <c r="F150" s="7"/>
@@ -4064,7 +4100,7 @@
     <row r="151" spans="1:18">
       <c r="A151" s="8"/>
       <c r="B151" s="10"/>
-      <c r="C151" s="16"/>
+      <c r="C151" s="15"/>
       <c r="D151" s="5"/>
       <c r="E151" s="6"/>
       <c r="F151" s="7"/>
@@ -4084,7 +4120,7 @@
     <row r="152" spans="1:18">
       <c r="A152" s="8"/>
       <c r="B152" s="10"/>
-      <c r="C152" s="16"/>
+      <c r="C152" s="15"/>
       <c r="D152" s="5"/>
       <c r="E152" s="6"/>
       <c r="F152" s="7"/>
@@ -4104,7 +4140,7 @@
     <row r="153" spans="1:18">
       <c r="A153" s="8"/>
       <c r="B153" s="10"/>
-      <c r="C153" s="16"/>
+      <c r="C153" s="15"/>
       <c r="D153" s="5"/>
       <c r="E153" s="6"/>
       <c r="F153" s="7"/>
@@ -4124,7 +4160,7 @@
     <row r="154" spans="1:18">
       <c r="A154" s="8"/>
       <c r="B154" s="10"/>
-      <c r="C154" s="16"/>
+      <c r="C154" s="15"/>
       <c r="D154" s="5"/>
       <c r="E154" s="6"/>
       <c r="F154" s="7"/>
@@ -4144,7 +4180,7 @@
     <row r="155" spans="1:18">
       <c r="A155" s="8"/>
       <c r="B155" s="10"/>
-      <c r="C155" s="16"/>
+      <c r="C155" s="15"/>
       <c r="D155" s="5"/>
       <c r="E155" s="6"/>
       <c r="F155" s="7"/>
@@ -4164,7 +4200,7 @@
     <row r="156" spans="1:18">
       <c r="A156" s="8"/>
       <c r="B156" s="10"/>
-      <c r="C156" s="16"/>
+      <c r="C156" s="15"/>
       <c r="D156" s="5"/>
       <c r="E156" s="6"/>
       <c r="F156" s="7"/>
@@ -4184,7 +4220,7 @@
     <row r="157" spans="1:18">
       <c r="A157" s="8"/>
       <c r="B157" s="10"/>
-      <c r="C157" s="16"/>
+      <c r="C157" s="15"/>
       <c r="D157" s="5"/>
       <c r="E157" s="6"/>
       <c r="F157" s="7"/>
@@ -4204,7 +4240,7 @@
     <row r="158" spans="1:18">
       <c r="A158" s="8"/>
       <c r="B158" s="10"/>
-      <c r="C158" s="16"/>
+      <c r="C158" s="15"/>
       <c r="D158" s="5"/>
       <c r="E158" s="6"/>
       <c r="F158" s="7"/>
@@ -4224,7 +4260,7 @@
     <row r="159" spans="1:18">
       <c r="A159" s="8"/>
       <c r="B159" s="10"/>
-      <c r="C159" s="16"/>
+      <c r="C159" s="15"/>
       <c r="D159" s="5"/>
       <c r="E159" s="6"/>
       <c r="F159" s="7"/>
@@ -4244,7 +4280,7 @@
     <row r="160" spans="1:18">
       <c r="A160" s="8"/>
       <c r="B160" s="10"/>
-      <c r="C160" s="16"/>
+      <c r="C160" s="15"/>
       <c r="D160" s="5"/>
       <c r="E160" s="6"/>
       <c r="F160" s="7"/>
@@ -4264,7 +4300,7 @@
     <row r="161" spans="1:18">
       <c r="A161" s="8"/>
       <c r="B161" s="10"/>
-      <c r="C161" s="16"/>
+      <c r="C161" s="15"/>
       <c r="D161" s="5"/>
       <c r="E161" s="6"/>
       <c r="F161" s="7"/>
@@ -4284,7 +4320,7 @@
     <row r="162" spans="1:18">
       <c r="A162" s="8"/>
       <c r="B162" s="10"/>
-      <c r="C162" s="16"/>
+      <c r="C162" s="15"/>
       <c r="D162" s="5"/>
       <c r="E162" s="6"/>
       <c r="F162" s="7"/>
@@ -4304,7 +4340,7 @@
     <row r="163" spans="1:18">
       <c r="A163" s="8"/>
       <c r="B163" s="10"/>
-      <c r="C163" s="16"/>
+      <c r="C163" s="15"/>
       <c r="D163" s="5"/>
       <c r="E163" s="6"/>
       <c r="F163" s="7"/>
@@ -4324,7 +4360,7 @@
     <row r="164" spans="1:18">
       <c r="A164" s="8"/>
       <c r="B164" s="10"/>
-      <c r="C164" s="16"/>
+      <c r="C164" s="15"/>
       <c r="D164" s="5"/>
       <c r="E164" s="6"/>
       <c r="F164" s="7"/>
@@ -4344,7 +4380,7 @@
     <row r="165" spans="1:18">
       <c r="A165" s="8"/>
       <c r="B165" s="10"/>
-      <c r="C165" s="16"/>
+      <c r="C165" s="15"/>
       <c r="D165" s="5"/>
       <c r="E165" s="6"/>
       <c r="F165" s="7"/>
@@ -4364,7 +4400,7 @@
     <row r="166" spans="1:18">
       <c r="A166" s="8"/>
       <c r="B166" s="10"/>
-      <c r="C166" s="16"/>
+      <c r="C166" s="15"/>
       <c r="D166" s="5"/>
       <c r="E166" s="6"/>
       <c r="F166" s="7"/>
@@ -4384,7 +4420,7 @@
     <row r="167" spans="1:18">
       <c r="A167" s="8"/>
       <c r="B167" s="10"/>
-      <c r="C167" s="16"/>
+      <c r="C167" s="15"/>
       <c r="D167" s="5"/>
       <c r="E167" s="6"/>
       <c r="F167" s="7"/>
@@ -4404,7 +4440,7 @@
     <row r="168" spans="1:18">
       <c r="A168" s="8"/>
       <c r="B168" s="10"/>
-      <c r="C168" s="16"/>
+      <c r="C168" s="15"/>
       <c r="D168" s="5"/>
       <c r="E168" s="6"/>
       <c r="F168" s="7"/>
@@ -4424,7 +4460,7 @@
     <row r="169" spans="1:18">
       <c r="A169" s="8"/>
       <c r="B169" s="10"/>
-      <c r="C169" s="16"/>
+      <c r="C169" s="15"/>
       <c r="D169" s="5"/>
       <c r="E169" s="6"/>
       <c r="F169" s="7"/>
@@ -4444,7 +4480,7 @@
     <row r="170" spans="1:18">
       <c r="A170" s="8"/>
       <c r="B170" s="10"/>
-      <c r="C170" s="16"/>
+      <c r="C170" s="15"/>
       <c r="D170" s="5"/>
       <c r="E170" s="6"/>
       <c r="F170" s="7"/>
@@ -4464,7 +4500,7 @@
     <row r="171" spans="1:18">
       <c r="A171" s="8"/>
       <c r="B171" s="10"/>
-      <c r="C171" s="16"/>
+      <c r="C171" s="15"/>
       <c r="D171" s="5"/>
       <c r="E171" s="6"/>
       <c r="F171" s="7"/>
@@ -4484,7 +4520,7 @@
     <row r="172" spans="1:18">
       <c r="A172" s="8"/>
       <c r="B172" s="10"/>
-      <c r="C172" s="16"/>
+      <c r="C172" s="15"/>
       <c r="D172" s="5"/>
       <c r="E172" s="6"/>
       <c r="F172" s="7"/>
@@ -4504,7 +4540,7 @@
     <row r="173" spans="1:18">
       <c r="A173" s="8"/>
       <c r="B173" s="10"/>
-      <c r="C173" s="16"/>
+      <c r="C173" s="15"/>
       <c r="D173" s="5"/>
       <c r="E173" s="6"/>
       <c r="F173" s="7"/>
@@ -4524,7 +4560,7 @@
     <row r="174" spans="1:18">
       <c r="A174" s="8"/>
       <c r="B174" s="10"/>
-      <c r="C174" s="16"/>
+      <c r="C174" s="15"/>
       <c r="D174" s="5"/>
       <c r="E174" s="6"/>
       <c r="F174" s="7"/>
@@ -4544,7 +4580,7 @@
     <row r="175" spans="1:18">
       <c r="A175" s="8"/>
       <c r="B175" s="10"/>
-      <c r="C175" s="16"/>
+      <c r="C175" s="15"/>
       <c r="D175" s="5"/>
       <c r="E175" s="6"/>
       <c r="F175" s="7"/>
@@ -4564,7 +4600,7 @@
     <row r="176" spans="1:18">
       <c r="A176" s="8"/>
       <c r="B176" s="10"/>
-      <c r="C176" s="16"/>
+      <c r="C176" s="15"/>
       <c r="D176" s="5"/>
       <c r="E176" s="6"/>
       <c r="F176" s="7"/>
@@ -4584,7 +4620,7 @@
     <row r="177" spans="1:18">
       <c r="A177" s="8"/>
       <c r="B177" s="10"/>
-      <c r="C177" s="16"/>
+      <c r="C177" s="15"/>
       <c r="D177" s="5"/>
       <c r="E177" s="6"/>
       <c r="F177" s="7"/>
@@ -4604,7 +4640,7 @@
     <row r="178" spans="1:18">
       <c r="A178" s="8"/>
       <c r="B178" s="10"/>
-      <c r="C178" s="16"/>
+      <c r="C178" s="15"/>
       <c r="D178" s="5"/>
       <c r="E178" s="6"/>
       <c r="F178" s="7"/>
@@ -4624,7 +4660,7 @@
     <row r="179" spans="1:18">
       <c r="A179" s="8"/>
       <c r="B179" s="10"/>
-      <c r="C179" s="16"/>
+      <c r="C179" s="15"/>
       <c r="D179" s="5"/>
       <c r="E179" s="6"/>
       <c r="F179" s="7"/>
@@ -4644,7 +4680,7 @@
     <row r="180" spans="1:18">
       <c r="A180" s="8"/>
       <c r="B180" s="10"/>
-      <c r="C180" s="16"/>
+      <c r="C180" s="15"/>
       <c r="D180" s="5"/>
       <c r="E180" s="6"/>
       <c r="F180" s="7"/>
@@ -4664,7 +4700,7 @@
     <row r="181" spans="1:18">
       <c r="A181" s="8"/>
       <c r="B181" s="10"/>
-      <c r="C181" s="16"/>
+      <c r="C181" s="15"/>
       <c r="D181" s="5"/>
       <c r="E181" s="6"/>
       <c r="F181" s="7"/>
@@ -4684,7 +4720,7 @@
     <row r="182" spans="1:18">
       <c r="A182" s="8"/>
       <c r="B182" s="10"/>
-      <c r="C182" s="16"/>
+      <c r="C182" s="15"/>
       <c r="D182" s="5"/>
       <c r="E182" s="6"/>
       <c r="F182" s="7"/>
@@ -4704,7 +4740,7 @@
     <row r="183" spans="1:18">
       <c r="A183" s="8"/>
       <c r="B183" s="10"/>
-      <c r="C183" s="16"/>
+      <c r="C183" s="15"/>
       <c r="D183" s="5"/>
       <c r="E183" s="6"/>
       <c r="F183" s="7"/>
@@ -4724,7 +4760,7 @@
     <row r="184" spans="1:18">
       <c r="A184" s="8"/>
       <c r="B184" s="10"/>
-      <c r="C184" s="16"/>
+      <c r="C184" s="15"/>
       <c r="D184" s="5"/>
       <c r="E184" s="6"/>
       <c r="F184" s="7"/>
@@ -4744,7 +4780,7 @@
     <row r="185" spans="1:18">
       <c r="A185" s="8"/>
       <c r="B185" s="10"/>
-      <c r="C185" s="16"/>
+      <c r="C185" s="15"/>
       <c r="D185" s="5"/>
       <c r="E185" s="6"/>
       <c r="F185" s="7"/>
@@ -4764,7 +4800,7 @@
     <row r="186" spans="1:18">
       <c r="A186" s="8"/>
       <c r="B186" s="10"/>
-      <c r="C186" s="16"/>
+      <c r="C186" s="15"/>
       <c r="D186" s="5"/>
       <c r="E186" s="6"/>
       <c r="F186" s="7"/>
@@ -4784,7 +4820,7 @@
     <row r="187" spans="1:18">
       <c r="A187" s="8"/>
       <c r="B187" s="10"/>
-      <c r="C187" s="16"/>
+      <c r="C187" s="15"/>
       <c r="D187" s="5"/>
       <c r="E187" s="6"/>
       <c r="F187" s="7"/>
@@ -4804,7 +4840,7 @@
     <row r="188" spans="1:18">
       <c r="A188" s="8"/>
       <c r="B188" s="10"/>
-      <c r="C188" s="16"/>
+      <c r="C188" s="15"/>
       <c r="D188" s="5"/>
       <c r="E188" s="6"/>
       <c r="F188" s="7"/>
@@ -4824,7 +4860,7 @@
     <row r="189" spans="1:18">
       <c r="A189" s="8"/>
       <c r="B189" s="10"/>
-      <c r="C189" s="16"/>
+      <c r="C189" s="15"/>
       <c r="D189" s="5"/>
       <c r="E189" s="6"/>
       <c r="F189" s="7"/>
@@ -4844,7 +4880,7 @@
     <row r="190" spans="1:18">
       <c r="A190" s="8"/>
       <c r="B190" s="10"/>
-      <c r="C190" s="16"/>
+      <c r="C190" s="15"/>
       <c r="D190" s="5"/>
       <c r="E190" s="6"/>
       <c r="F190" s="7"/>
@@ -4864,7 +4900,7 @@
     <row r="191" spans="1:18">
       <c r="A191" s="8"/>
       <c r="B191" s="10"/>
-      <c r="C191" s="16"/>
+      <c r="C191" s="15"/>
       <c r="D191" s="5"/>
       <c r="E191" s="6"/>
       <c r="F191" s="7"/>
@@ -4884,7 +4920,7 @@
     <row r="192" spans="1:18">
       <c r="A192" s="8"/>
       <c r="B192" s="10"/>
-      <c r="C192" s="16"/>
+      <c r="C192" s="15"/>
       <c r="D192" s="5"/>
       <c r="E192" s="6"/>
       <c r="F192" s="7"/>
@@ -4904,7 +4940,7 @@
     <row r="193" spans="1:18">
       <c r="A193" s="8"/>
       <c r="B193" s="10"/>
-      <c r="C193" s="16"/>
+      <c r="C193" s="15"/>
       <c r="D193" s="5"/>
       <c r="E193" s="6"/>
       <c r="F193" s="7"/>
@@ -4924,7 +4960,7 @@
     <row r="194" spans="1:18">
       <c r="A194" s="8"/>
       <c r="B194" s="10"/>
-      <c r="C194" s="16"/>
+      <c r="C194" s="15"/>
       <c r="D194" s="5"/>
       <c r="E194" s="6"/>
       <c r="F194" s="7"/>
@@ -4944,7 +4980,7 @@
     <row r="195" spans="1:18">
       <c r="A195" s="8"/>
       <c r="B195" s="10"/>
-      <c r="C195" s="16"/>
+      <c r="C195" s="15"/>
       <c r="D195" s="5"/>
       <c r="E195" s="6"/>
       <c r="F195" s="7"/>
@@ -4964,7 +5000,7 @@
     <row r="196" spans="1:18">
       <c r="A196" s="8"/>
       <c r="B196" s="10"/>
-      <c r="C196" s="16"/>
+      <c r="C196" s="15"/>
       <c r="D196" s="5"/>
       <c r="E196" s="6"/>
       <c r="F196" s="7"/>
@@ -4984,7 +5020,7 @@
     <row r="197" spans="1:18">
       <c r="A197" s="8"/>
       <c r="B197" s="10"/>
-      <c r="C197" s="16"/>
+      <c r="C197" s="15"/>
       <c r="D197" s="5"/>
       <c r="E197" s="6"/>
       <c r="F197" s="7"/>
@@ -5004,7 +5040,7 @@
     <row r="198" spans="1:18">
       <c r="A198" s="8"/>
       <c r="B198" s="10"/>
-      <c r="C198" s="16"/>
+      <c r="C198" s="15"/>
       <c r="D198" s="5"/>
       <c r="E198" s="6"/>
       <c r="F198" s="7"/>
@@ -5024,7 +5060,7 @@
     <row r="199" spans="1:18">
       <c r="A199" s="8"/>
       <c r="B199" s="10"/>
-      <c r="C199" s="16"/>
+      <c r="C199" s="15"/>
       <c r="D199" s="5"/>
       <c r="E199" s="6"/>
       <c r="F199" s="7"/>
@@ -5044,7 +5080,7 @@
     <row r="200" spans="1:18">
       <c r="A200" s="8"/>
       <c r="B200" s="10"/>
-      <c r="C200" s="16"/>
+      <c r="C200" s="15"/>
       <c r="D200" s="5"/>
       <c r="E200" s="6"/>
       <c r="F200" s="7"/>
@@ -5064,7 +5100,7 @@
     <row r="201" spans="1:18">
       <c r="A201" s="8"/>
       <c r="B201" s="10"/>
-      <c r="C201" s="16"/>
+      <c r="C201" s="15"/>
       <c r="D201" s="5"/>
       <c r="E201" s="6"/>
       <c r="F201" s="7"/>
@@ -5084,7 +5120,7 @@
     <row r="202" spans="1:18">
       <c r="A202" s="8"/>
       <c r="B202" s="10"/>
-      <c r="C202" s="16"/>
+      <c r="C202" s="15"/>
       <c r="D202" s="5"/>
       <c r="E202" s="6"/>
       <c r="F202" s="7"/>
@@ -5104,7 +5140,7 @@
     <row r="203" spans="1:18">
       <c r="A203" s="8"/>
       <c r="B203" s="10"/>
-      <c r="C203" s="16"/>
+      <c r="C203" s="15"/>
       <c r="D203" s="5"/>
       <c r="E203" s="6"/>
       <c r="F203" s="7"/>
@@ -5124,7 +5160,7 @@
     <row r="204" spans="1:18">
       <c r="A204" s="8"/>
       <c r="B204" s="10"/>
-      <c r="C204" s="16"/>
+      <c r="C204" s="15"/>
       <c r="D204" s="5"/>
       <c r="E204" s="6"/>
       <c r="F204" s="7"/>
@@ -5144,7 +5180,7 @@
     <row r="205" spans="1:18">
       <c r="A205" s="8"/>
       <c r="B205" s="10"/>
-      <c r="C205" s="16"/>
+      <c r="C205" s="15"/>
       <c r="D205" s="5"/>
       <c r="E205" s="6"/>
       <c r="F205" s="7"/>
@@ -5164,7 +5200,7 @@
     <row r="206" spans="1:18">
       <c r="A206" s="8"/>
       <c r="B206" s="10"/>
-      <c r="C206" s="16"/>
+      <c r="C206" s="15"/>
       <c r="D206" s="5"/>
       <c r="E206" s="6"/>
       <c r="F206" s="7"/>
@@ -5184,7 +5220,7 @@
     <row r="207" spans="1:18">
       <c r="A207" s="8"/>
       <c r="B207" s="10"/>
-      <c r="C207" s="16"/>
+      <c r="C207" s="15"/>
       <c r="D207" s="5"/>
       <c r="E207" s="6"/>
       <c r="F207" s="7"/>
@@ -5204,7 +5240,7 @@
     <row r="208" spans="1:18">
       <c r="A208" s="8"/>
       <c r="B208" s="10"/>
-      <c r="C208" s="16"/>
+      <c r="C208" s="15"/>
       <c r="D208" s="5"/>
       <c r="E208" s="6"/>
       <c r="F208" s="7"/>
@@ -5224,7 +5260,7 @@
     <row r="209" spans="1:18">
       <c r="A209" s="8"/>
       <c r="B209" s="10"/>
-      <c r="C209" s="16"/>
+      <c r="C209" s="15"/>
       <c r="D209" s="5"/>
       <c r="E209" s="6"/>
       <c r="F209" s="7"/>
@@ -5244,7 +5280,7 @@
     <row r="210" spans="1:18">
       <c r="A210" s="8"/>
       <c r="B210" s="10"/>
-      <c r="C210" s="16"/>
+      <c r="C210" s="15"/>
       <c r="D210" s="5"/>
       <c r="E210" s="6"/>
       <c r="F210" s="7"/>
@@ -5264,7 +5300,7 @@
     <row r="211" spans="1:18">
       <c r="A211" s="8"/>
       <c r="B211" s="10"/>
-      <c r="C211" s="16"/>
+      <c r="C211" s="15"/>
       <c r="D211" s="5"/>
       <c r="E211" s="6"/>
       <c r="F211" s="7"/>
@@ -5284,7 +5320,7 @@
     <row r="212" spans="1:18">
       <c r="A212" s="8"/>
       <c r="B212" s="10"/>
-      <c r="C212" s="16"/>
+      <c r="C212" s="15"/>
       <c r="D212" s="5"/>
       <c r="E212" s="6"/>
       <c r="F212" s="7"/>
@@ -5304,7 +5340,7 @@
     <row r="213" spans="1:18">
       <c r="A213" s="8"/>
       <c r="B213" s="10"/>
-      <c r="C213" s="16"/>
+      <c r="C213" s="15"/>
       <c r="D213" s="5"/>
       <c r="E213" s="6"/>
       <c r="F213" s="7"/>
@@ -5324,7 +5360,7 @@
     <row r="214" spans="1:18">
       <c r="A214" s="8"/>
       <c r="B214" s="10"/>
-      <c r="C214" s="16"/>
+      <c r="C214" s="15"/>
       <c r="D214" s="5"/>
       <c r="E214" s="6"/>
       <c r="F214" s="7"/>
@@ -5344,7 +5380,7 @@
     <row r="215" spans="1:18">
       <c r="A215" s="8"/>
       <c r="B215" s="10"/>
-      <c r="C215" s="16"/>
+      <c r="C215" s="15"/>
       <c r="D215" s="5"/>
       <c r="E215" s="6"/>
       <c r="F215" s="7"/>
@@ -5364,7 +5400,7 @@
     <row r="216" spans="1:18">
       <c r="A216" s="8"/>
       <c r="B216" s="10"/>
-      <c r="C216" s="16"/>
+      <c r="C216" s="15"/>
       <c r="D216" s="5"/>
       <c r="E216" s="6"/>
       <c r="F216" s="7"/>
@@ -5384,7 +5420,7 @@
     <row r="217" spans="1:18">
       <c r="A217" s="8"/>
       <c r="B217" s="10"/>
-      <c r="C217" s="16"/>
+      <c r="C217" s="15"/>
       <c r="D217" s="5"/>
       <c r="E217" s="6"/>
       <c r="F217" s="7"/>
@@ -5404,7 +5440,7 @@
     <row r="218" spans="1:18">
       <c r="A218" s="8"/>
       <c r="B218" s="10"/>
-      <c r="C218" s="16"/>
+      <c r="C218" s="15"/>
       <c r="D218" s="5"/>
       <c r="E218" s="6"/>
       <c r="F218" s="7"/>
@@ -5424,7 +5460,7 @@
     <row r="219" spans="1:18">
       <c r="A219" s="8"/>
       <c r="B219" s="10"/>
-      <c r="C219" s="16"/>
+      <c r="C219" s="15"/>
       <c r="D219" s="5"/>
       <c r="E219" s="6"/>
       <c r="F219" s="7"/>
@@ -5444,7 +5480,7 @@
     <row r="220" spans="1:18">
       <c r="A220" s="8"/>
       <c r="B220" s="10"/>
-      <c r="C220" s="16"/>
+      <c r="C220" s="15"/>
       <c r="D220" s="5"/>
       <c r="E220" s="6"/>
       <c r="F220" s="7"/>
@@ -5464,7 +5500,7 @@
     <row r="221" spans="1:18">
       <c r="A221" s="8"/>
       <c r="B221" s="10"/>
-      <c r="C221" s="16"/>
+      <c r="C221" s="15"/>
       <c r="D221" s="5"/>
       <c r="E221" s="6"/>
       <c r="F221" s="7"/>
@@ -5484,7 +5520,7 @@
     <row r="222" spans="1:18">
       <c r="A222" s="8"/>
       <c r="B222" s="10"/>
-      <c r="C222" s="16"/>
+      <c r="C222" s="15"/>
       <c r="D222" s="5"/>
       <c r="E222" s="6"/>
       <c r="F222" s="7"/>
@@ -5504,7 +5540,7 @@
     <row r="223" spans="1:18">
       <c r="A223" s="8"/>
       <c r="B223" s="10"/>
-      <c r="C223" s="16"/>
+      <c r="C223" s="15"/>
       <c r="D223" s="5"/>
       <c r="E223" s="6"/>
       <c r="F223" s="7"/>
@@ -5524,7 +5560,7 @@
     <row r="224" spans="1:18">
       <c r="A224" s="8"/>
       <c r="B224" s="10"/>
-      <c r="C224" s="16"/>
+      <c r="C224" s="15"/>
       <c r="D224" s="5"/>
       <c r="E224" s="6"/>
       <c r="F224" s="7"/>
@@ -5544,7 +5580,7 @@
     <row r="225" spans="1:18">
       <c r="A225" s="8"/>
       <c r="B225" s="10"/>
-      <c r="C225" s="16"/>
+      <c r="C225" s="15"/>
       <c r="D225" s="5"/>
       <c r="E225" s="6"/>
       <c r="F225" s="7"/>
@@ -5564,7 +5600,7 @@
     <row r="226" spans="1:18">
       <c r="A226" s="8"/>
       <c r="B226" s="10"/>
-      <c r="C226" s="16"/>
+      <c r="C226" s="15"/>
       <c r="D226" s="5"/>
       <c r="E226" s="6"/>
       <c r="F226" s="7"/>
@@ -5584,7 +5620,7 @@
     <row r="227" spans="1:18">
       <c r="A227" s="8"/>
       <c r="B227" s="10"/>
-      <c r="C227" s="16"/>
+      <c r="C227" s="15"/>
       <c r="D227" s="5"/>
       <c r="E227" s="6"/>
       <c r="F227" s="7"/>
@@ -5604,7 +5640,7 @@
     <row r="228" spans="1:18">
       <c r="A228" s="8"/>
       <c r="B228" s="10"/>
-      <c r="C228" s="16"/>
+      <c r="C228" s="15"/>
       <c r="D228" s="5"/>
       <c r="E228" s="6"/>
       <c r="F228" s="7"/>
@@ -5624,7 +5660,7 @@
     <row r="229" spans="1:18">
       <c r="A229" s="8"/>
       <c r="B229" s="10"/>
-      <c r="C229" s="16"/>
+      <c r="C229" s="15"/>
       <c r="D229" s="5"/>
       <c r="E229" s="6"/>
       <c r="F229" s="7"/>
@@ -5644,7 +5680,7 @@
     <row r="230" spans="1:18">
       <c r="A230" s="8"/>
       <c r="B230" s="10"/>
-      <c r="C230" s="16"/>
+      <c r="C230" s="15"/>
       <c r="D230" s="5"/>
       <c r="E230" s="6"/>
       <c r="F230" s="7"/>
@@ -5664,7 +5700,7 @@
     <row r="231" spans="1:18">
       <c r="A231" s="8"/>
       <c r="B231" s="10"/>
-      <c r="C231" s="16"/>
+      <c r="C231" s="15"/>
       <c r="D231" s="5"/>
       <c r="E231" s="6"/>
       <c r="F231" s="7"/>
@@ -5684,7 +5720,7 @@
     <row r="232" spans="1:18">
       <c r="A232" s="8"/>
       <c r="B232" s="10"/>
-      <c r="C232" s="16"/>
+      <c r="C232" s="15"/>
       <c r="D232" s="5"/>
       <c r="E232" s="6"/>
       <c r="F232" s="7"/>
@@ -5704,7 +5740,7 @@
     <row r="233" spans="1:18">
       <c r="A233" s="8"/>
       <c r="B233" s="10"/>
-      <c r="C233" s="16"/>
+      <c r="C233" s="15"/>
       <c r="D233" s="5"/>
       <c r="E233" s="6"/>
       <c r="F233" s="7"/>
@@ -5724,7 +5760,7 @@
     <row r="234" spans="1:18">
       <c r="A234" s="8"/>
       <c r="B234" s="10"/>
-      <c r="C234" s="16"/>
+      <c r="C234" s="15"/>
       <c r="D234" s="5"/>
       <c r="E234" s="6"/>
       <c r="F234" s="7"/>
@@ -5744,7 +5780,7 @@
     <row r="235" spans="1:18">
       <c r="A235" s="8"/>
       <c r="B235" s="10"/>
-      <c r="C235" s="16"/>
+      <c r="C235" s="15"/>
       <c r="D235" s="5"/>
       <c r="E235" s="6"/>
       <c r="F235" s="7"/>
@@ -5764,7 +5800,7 @@
     <row r="236" spans="1:18">
       <c r="A236" s="8"/>
       <c r="B236" s="10"/>
-      <c r="C236" s="16"/>
+      <c r="C236" s="15"/>
       <c r="D236" s="5"/>
       <c r="E236" s="6"/>
       <c r="F236" s="7"/>
@@ -5784,7 +5820,7 @@
     <row r="237" spans="1:18">
       <c r="A237" s="8"/>
       <c r="B237" s="10"/>
-      <c r="C237" s="16"/>
+      <c r="C237" s="15"/>
       <c r="D237" s="5"/>
       <c r="E237" s="6"/>
       <c r="F237" s="7"/>
@@ -5804,7 +5840,7 @@
     <row r="238" spans="1:18">
       <c r="A238" s="8"/>
       <c r="B238" s="10"/>
-      <c r="C238" s="16"/>
+      <c r="C238" s="15"/>
       <c r="D238" s="5"/>
       <c r="E238" s="6"/>
       <c r="F238" s="7"/>
@@ -5824,7 +5860,7 @@
     <row r="239" spans="1:18">
       <c r="A239" s="8"/>
       <c r="B239" s="10"/>
-      <c r="C239" s="16"/>
+      <c r="C239" s="15"/>
       <c r="D239" s="5"/>
       <c r="E239" s="6"/>
       <c r="F239" s="7"/>
@@ -5844,7 +5880,7 @@
     <row r="240" spans="1:18">
       <c r="A240" s="8"/>
       <c r="B240" s="10"/>
-      <c r="C240" s="16"/>
+      <c r="C240" s="15"/>
       <c r="D240" s="5"/>
       <c r="E240" s="6"/>
       <c r="F240" s="7"/>
@@ -5864,7 +5900,7 @@
     <row r="241" spans="1:18">
       <c r="A241" s="8"/>
       <c r="B241" s="10"/>
-      <c r="C241" s="16"/>
+      <c r="C241" s="15"/>
       <c r="D241" s="5"/>
       <c r="E241" s="6"/>
       <c r="F241" s="7"/>
@@ -5884,7 +5920,7 @@
     <row r="242" spans="1:18">
       <c r="A242" s="8"/>
       <c r="B242" s="10"/>
-      <c r="C242" s="16"/>
+      <c r="C242" s="15"/>
       <c r="D242" s="5"/>
       <c r="E242" s="6"/>
       <c r="F242" s="7"/>
@@ -5904,7 +5940,7 @@
     <row r="243" spans="1:18">
       <c r="A243" s="8"/>
       <c r="B243" s="10"/>
-      <c r="C243" s="16"/>
+      <c r="C243" s="15"/>
       <c r="D243" s="5"/>
       <c r="E243" s="6"/>
       <c r="F243" s="7"/>
@@ -5924,7 +5960,7 @@
     <row r="244" spans="1:18">
       <c r="A244" s="8"/>
       <c r="B244" s="10"/>
-      <c r="C244" s="16"/>
+      <c r="C244" s="15"/>
       <c r="D244" s="5"/>
       <c r="E244" s="6"/>
       <c r="F244" s="7"/>
@@ -5944,7 +5980,7 @@
     <row r="245" spans="1:18">
       <c r="A245" s="8"/>
       <c r="B245" s="10"/>
-      <c r="C245" s="16"/>
+      <c r="C245" s="15"/>
       <c r="D245" s="5"/>
       <c r="E245" s="6"/>
       <c r="F245" s="7"/>
@@ -5964,7 +6000,7 @@
     <row r="246" spans="1:18">
       <c r="A246" s="8"/>
       <c r="B246" s="10"/>
-      <c r="C246" s="16"/>
+      <c r="C246" s="15"/>
       <c r="D246" s="5"/>
       <c r="E246" s="6"/>
       <c r="F246" s="7"/>
@@ -5984,7 +6020,7 @@
     <row r="247" spans="1:18">
       <c r="A247" s="8"/>
       <c r="B247" s="10"/>
-      <c r="C247" s="16"/>
+      <c r="C247" s="15"/>
       <c r="D247" s="5"/>
       <c r="E247" s="6"/>
       <c r="F247" s="7"/>
@@ -6004,7 +6040,7 @@
     <row r="248" spans="1:18">
       <c r="A248" s="8"/>
       <c r="B248" s="10"/>
-      <c r="C248" s="16"/>
+      <c r="C248" s="15"/>
       <c r="D248" s="5"/>
       <c r="E248" s="6"/>
       <c r="F248" s="7"/>
@@ -6024,7 +6060,7 @@
     <row r="249" spans="1:18">
       <c r="A249" s="8"/>
       <c r="B249" s="10"/>
-      <c r="C249" s="16"/>
+      <c r="C249" s="15"/>
       <c r="D249" s="5"/>
       <c r="E249" s="6"/>
       <c r="F249" s="7"/>
@@ -6044,7 +6080,7 @@
     <row r="250" spans="1:18">
       <c r="A250" s="8"/>
       <c r="B250" s="10"/>
-      <c r="C250" s="16"/>
+      <c r="C250" s="15"/>
       <c r="D250" s="5"/>
       <c r="E250" s="6"/>
       <c r="F250" s="7"/>
@@ -6064,7 +6100,7 @@
     <row r="251" spans="1:18">
       <c r="A251" s="8"/>
       <c r="B251" s="10"/>
-      <c r="C251" s="16"/>
+      <c r="C251" s="15"/>
       <c r="D251" s="5"/>
       <c r="E251" s="6"/>
       <c r="F251" s="7"/>
@@ -6084,7 +6120,7 @@
     <row r="252" spans="1:18">
       <c r="A252" s="8"/>
       <c r="B252" s="10"/>
-      <c r="C252" s="16"/>
+      <c r="C252" s="15"/>
       <c r="D252" s="5"/>
       <c r="E252" s="6"/>
       <c r="F252" s="7"/>
@@ -6104,7 +6140,7 @@
     <row r="253" spans="1:18">
       <c r="A253" s="8"/>
       <c r="B253" s="10"/>
-      <c r="C253" s="16"/>
+      <c r="C253" s="15"/>
       <c r="D253" s="5"/>
       <c r="E253" s="6"/>
       <c r="F253" s="7"/>
@@ -6124,7 +6160,7 @@
     <row r="254" spans="1:18">
       <c r="A254" s="8"/>
       <c r="B254" s="10"/>
-      <c r="C254" s="16"/>
+      <c r="C254" s="15"/>
       <c r="D254" s="5"/>
       <c r="E254" s="6"/>
       <c r="F254" s="7"/>
@@ -6144,7 +6180,7 @@
     <row r="255" spans="1:18">
       <c r="A255" s="8"/>
       <c r="B255" s="10"/>
-      <c r="C255" s="16"/>
+      <c r="C255" s="15"/>
       <c r="D255" s="5"/>
       <c r="E255" s="6"/>
       <c r="F255" s="7"/>
@@ -6164,7 +6200,7 @@
     <row r="256" spans="1:18">
       <c r="A256" s="8"/>
       <c r="B256" s="10"/>
-      <c r="C256" s="16"/>
+      <c r="C256" s="15"/>
       <c r="D256" s="5"/>
       <c r="E256" s="6"/>
       <c r="F256" s="7"/>
@@ -6184,7 +6220,7 @@
     <row r="257" spans="1:18">
       <c r="A257" s="8"/>
       <c r="B257" s="10"/>
-      <c r="C257" s="16"/>
+      <c r="C257" s="15"/>
       <c r="D257" s="5"/>
       <c r="E257" s="6"/>
       <c r="F257" s="7"/>
@@ -6204,7 +6240,7 @@
     <row r="258" spans="1:18">
       <c r="A258" s="8"/>
       <c r="B258" s="10"/>
-      <c r="C258" s="16"/>
+      <c r="C258" s="15"/>
       <c r="D258" s="5"/>
       <c r="E258" s="6"/>
       <c r="F258" s="7"/>
@@ -6224,7 +6260,7 @@
     <row r="259" spans="1:18">
       <c r="A259" s="8"/>
       <c r="B259" s="10"/>
-      <c r="C259" s="16"/>
+      <c r="C259" s="15"/>
       <c r="D259" s="5"/>
       <c r="E259" s="6"/>
       <c r="F259" s="7"/>
@@ -6244,7 +6280,7 @@
     <row r="260" spans="1:18">
       <c r="A260" s="8"/>
       <c r="B260" s="10"/>
-      <c r="C260" s="16"/>
+      <c r="C260" s="15"/>
       <c r="D260" s="5"/>
       <c r="E260" s="6"/>
       <c r="F260" s="7"/>
@@ -6264,7 +6300,7 @@
     <row r="261" spans="1:18">
       <c r="A261" s="8"/>
       <c r="B261" s="10"/>
-      <c r="C261" s="16"/>
+      <c r="C261" s="15"/>
       <c r="D261" s="5"/>
       <c r="E261" s="6"/>
       <c r="F261" s="7"/>
@@ -6284,7 +6320,7 @@
     <row r="262" spans="1:18">
       <c r="A262" s="8"/>
       <c r="B262" s="10"/>
-      <c r="C262" s="16"/>
+      <c r="C262" s="15"/>
       <c r="D262" s="5"/>
       <c r="E262" s="6"/>
       <c r="F262" s="7"/>
@@ -6304,7 +6340,7 @@
     <row r="263" spans="1:18">
       <c r="A263" s="8"/>
       <c r="B263" s="10"/>
-      <c r="C263" s="16"/>
+      <c r="C263" s="15"/>
       <c r="D263" s="5"/>
       <c r="E263" s="6"/>
       <c r="F263" s="7"/>
@@ -6324,7 +6360,7 @@
     <row r="264" spans="1:18">
       <c r="A264" s="8"/>
       <c r="B264" s="10"/>
-      <c r="C264" s="16"/>
+      <c r="C264" s="15"/>
       <c r="D264" s="5"/>
       <c r="E264" s="6"/>
       <c r="F264" s="7"/>
@@ -6344,7 +6380,7 @@
     <row r="265" spans="1:18">
       <c r="A265" s="8"/>
       <c r="B265" s="10"/>
-      <c r="C265" s="16"/>
+      <c r="C265" s="15"/>
       <c r="D265" s="5"/>
       <c r="E265" s="6"/>
       <c r="F265" s="7"/>
@@ -6364,7 +6400,7 @@
     <row r="266" spans="1:18">
       <c r="A266" s="8"/>
       <c r="B266" s="10"/>
-      <c r="C266" s="16"/>
+      <c r="C266" s="15"/>
       <c r="D266" s="5"/>
       <c r="E266" s="6"/>
       <c r="F266" s="7"/>
@@ -6384,7 +6420,7 @@
     <row r="267" spans="1:18">
       <c r="A267" s="8"/>
       <c r="B267" s="10"/>
-      <c r="C267" s="16"/>
+      <c r="C267" s="15"/>
       <c r="D267" s="5"/>
       <c r="E267" s="6"/>
       <c r="F267" s="7"/>
@@ -6404,7 +6440,7 @@
     <row r="268" spans="1:18">
       <c r="A268" s="8"/>
       <c r="B268" s="10"/>
-      <c r="C268" s="16"/>
+      <c r="C268" s="15"/>
       <c r="D268" s="5"/>
       <c r="E268" s="6"/>
       <c r="F268" s="7"/>
@@ -6424,7 +6460,7 @@
     <row r="269" spans="1:18">
       <c r="A269" s="8"/>
       <c r="B269" s="10"/>
-      <c r="C269" s="16"/>
+      <c r="C269" s="15"/>
       <c r="D269" s="5"/>
       <c r="E269" s="6"/>
       <c r="F269" s="7"/>
@@ -6444,7 +6480,7 @@
     <row r="270" spans="1:18">
       <c r="A270" s="8"/>
       <c r="B270" s="10"/>
-      <c r="C270" s="16"/>
+      <c r="C270" s="15"/>
       <c r="D270" s="5"/>
       <c r="E270" s="6"/>
       <c r="F270" s="7"/>
@@ -6464,7 +6500,7 @@
     <row r="271" spans="1:18">
       <c r="A271" s="8"/>
       <c r="B271" s="10"/>
-      <c r="C271" s="16"/>
+      <c r="C271" s="15"/>
       <c r="D271" s="5"/>
       <c r="E271" s="6"/>
       <c r="F271" s="7"/>
@@ -6484,7 +6520,7 @@
     <row r="272" spans="1:18">
       <c r="A272" s="8"/>
       <c r="B272" s="10"/>
-      <c r="C272" s="16"/>
+      <c r="C272" s="15"/>
       <c r="D272" s="5"/>
       <c r="E272" s="6"/>
       <c r="F272" s="7"/>
@@ -6504,7 +6540,7 @@
     <row r="273" spans="1:18">
       <c r="A273" s="8"/>
       <c r="B273" s="10"/>
-      <c r="C273" s="16"/>
+      <c r="C273" s="15"/>
       <c r="D273" s="5"/>
       <c r="E273" s="6"/>
       <c r="F273" s="7"/>
@@ -6524,7 +6560,7 @@
     <row r="274" spans="1:18">
       <c r="A274" s="8"/>
       <c r="B274" s="10"/>
-      <c r="C274" s="16"/>
+      <c r="C274" s="15"/>
       <c r="D274" s="5"/>
       <c r="E274" s="6"/>
       <c r="F274" s="7"/>
@@ -6544,7 +6580,7 @@
     <row r="275" spans="1:18">
       <c r="A275" s="8"/>
       <c r="B275" s="10"/>
-      <c r="C275" s="16"/>
+      <c r="C275" s="15"/>
       <c r="D275" s="5"/>
       <c r="E275" s="6"/>
       <c r="F275" s="7"/>
@@ -6564,7 +6600,7 @@
     <row r="276" spans="1:18">
       <c r="A276" s="8"/>
       <c r="B276" s="10"/>
-      <c r="C276" s="16"/>
+      <c r="C276" s="15"/>
       <c r="D276" s="5"/>
       <c r="E276" s="6"/>
       <c r="F276" s="7"/>
@@ -6584,7 +6620,7 @@
     <row r="277" spans="1:18">
       <c r="A277" s="8"/>
       <c r="B277" s="10"/>
-      <c r="C277" s="16"/>
+      <c r="C277" s="15"/>
       <c r="D277" s="5"/>
       <c r="E277" s="6"/>
       <c r="F277" s="7"/>
@@ -6604,7 +6640,7 @@
     <row r="278" spans="1:18">
       <c r="A278" s="8"/>
       <c r="B278" s="10"/>
-      <c r="C278" s="16"/>
+      <c r="C278" s="15"/>
       <c r="D278" s="5"/>
       <c r="E278" s="6"/>
       <c r="F278" s="7"/>
@@ -6624,7 +6660,7 @@
     <row r="279" spans="1:18">
       <c r="A279" s="8"/>
       <c r="B279" s="10"/>
-      <c r="C279" s="16"/>
+      <c r="C279" s="15"/>
       <c r="D279" s="5"/>
       <c r="E279" s="6"/>
       <c r="F279" s="7"/>
@@ -6644,7 +6680,7 @@
     <row r="280" spans="1:18">
       <c r="A280" s="8"/>
       <c r="B280" s="10"/>
-      <c r="C280" s="16"/>
+      <c r="C280" s="15"/>
       <c r="D280" s="5"/>
       <c r="E280" s="6"/>
       <c r="F280" s="7"/>
@@ -6664,7 +6700,7 @@
     <row r="281" spans="1:18">
       <c r="A281" s="8"/>
       <c r="B281" s="10"/>
-      <c r="C281" s="16"/>
+      <c r="C281" s="15"/>
       <c r="D281" s="5"/>
       <c r="E281" s="6"/>
       <c r="F281" s="7"/>
@@ -6684,7 +6720,7 @@
     <row r="282" spans="1:18">
       <c r="A282" s="8"/>
       <c r="B282" s="10"/>
-      <c r="C282" s="16"/>
+      <c r="C282" s="15"/>
       <c r="D282" s="5"/>
       <c r="E282" s="6"/>
       <c r="F282" s="7"/>
@@ -6704,7 +6740,7 @@
     <row r="283" spans="1:18">
       <c r="A283" s="8"/>
       <c r="B283" s="10"/>
-      <c r="C283" s="16"/>
+      <c r="C283" s="15"/>
       <c r="D283" s="5"/>
       <c r="E283" s="6"/>
       <c r="F283" s="7"/>
@@ -6724,7 +6760,7 @@
     <row r="284" spans="1:18">
       <c r="A284" s="8"/>
       <c r="B284" s="10"/>
-      <c r="C284" s="16"/>
+      <c r="C284" s="15"/>
       <c r="D284" s="5"/>
       <c r="E284" s="6"/>
       <c r="F284" s="7"/>
@@ -6744,7 +6780,7 @@
     <row r="285" spans="1:18">
       <c r="A285" s="8"/>
       <c r="B285" s="10"/>
-      <c r="C285" s="16"/>
+      <c r="C285" s="15"/>
       <c r="D285" s="5"/>
       <c r="E285" s="6"/>
       <c r="F285" s="7"/>
@@ -6764,7 +6800,7 @@
     <row r="286" spans="1:18">
       <c r="A286" s="8"/>
       <c r="B286" s="10"/>
-      <c r="C286" s="16"/>
+      <c r="C286" s="15"/>
       <c r="D286" s="5"/>
       <c r="E286" s="6"/>
       <c r="F286" s="7"/>
@@ -6784,7 +6820,7 @@
     <row r="287" spans="1:18">
       <c r="A287" s="8"/>
       <c r="B287" s="10"/>
-      <c r="C287" s="16"/>
+      <c r="C287" s="15"/>
       <c r="D287" s="5"/>
       <c r="E287" s="6"/>
       <c r="F287" s="7"/>
@@ -6804,7 +6840,7 @@
     <row r="288" spans="1:18">
       <c r="A288" s="8"/>
       <c r="B288" s="10"/>
-      <c r="C288" s="16"/>
+      <c r="C288" s="15"/>
       <c r="D288" s="5"/>
       <c r="E288" s="6"/>
       <c r="F288" s="7"/>
@@ -6824,7 +6860,7 @@
     <row r="289" spans="1:18">
       <c r="A289" s="8"/>
       <c r="B289" s="10"/>
-      <c r="C289" s="16"/>
+      <c r="C289" s="15"/>
       <c r="D289" s="5"/>
       <c r="E289" s="6"/>
       <c r="F289" s="7"/>
@@ -6844,7 +6880,7 @@
     <row r="290" spans="1:18">
       <c r="A290" s="8"/>
       <c r="B290" s="10"/>
-      <c r="C290" s="16"/>
+      <c r="C290" s="15"/>
       <c r="D290" s="5"/>
       <c r="E290" s="6"/>
       <c r="F290" s="7"/>
@@ -6864,7 +6900,7 @@
     <row r="291" spans="1:18">
       <c r="A291" s="8"/>
       <c r="B291" s="10"/>
-      <c r="C291" s="16"/>
+      <c r="C291" s="15"/>
       <c r="D291" s="5"/>
       <c r="E291" s="6"/>
       <c r="F291" s="7"/>
@@ -6884,7 +6920,7 @@
     <row r="292" spans="1:18">
       <c r="A292" s="8"/>
       <c r="B292" s="10"/>
-      <c r="C292" s="16"/>
+      <c r="C292" s="15"/>
       <c r="D292" s="5"/>
       <c r="E292" s="6"/>
       <c r="F292" s="7"/>
@@ -6904,7 +6940,7 @@
     <row r="293" spans="1:18">
       <c r="A293" s="8"/>
       <c r="B293" s="10"/>
-      <c r="C293" s="16"/>
+      <c r="C293" s="15"/>
       <c r="D293" s="5"/>
       <c r="E293" s="6"/>
       <c r="F293" s="7"/>
@@ -6924,7 +6960,7 @@
     <row r="294" spans="1:18">
       <c r="A294" s="8"/>
       <c r="B294" s="10"/>
-      <c r="C294" s="16"/>
+      <c r="C294" s="15"/>
       <c r="D294" s="5"/>
       <c r="E294" s="6"/>
       <c r="F294" s="7"/>
@@ -6944,7 +6980,7 @@
     <row r="295" spans="1:18">
       <c r="A295" s="8"/>
       <c r="B295" s="10"/>
-      <c r="C295" s="16"/>
+      <c r="C295" s="15"/>
       <c r="D295" s="5"/>
       <c r="E295" s="6"/>
       <c r="F295" s="7"/>
@@ -6964,7 +7000,7 @@
     <row r="296" spans="1:18">
       <c r="A296" s="8"/>
       <c r="B296" s="10"/>
-      <c r="C296" s="16"/>
+      <c r="C296" s="15"/>
       <c r="D296" s="5"/>
       <c r="E296" s="6"/>
       <c r="F296" s="7"/>
@@ -6984,7 +7020,7 @@
     <row r="297" spans="1:18">
       <c r="A297" s="8"/>
       <c r="B297" s="10"/>
-      <c r="C297" s="16"/>
+      <c r="C297" s="15"/>
       <c r="D297" s="5"/>
       <c r="E297" s="6"/>
       <c r="F297" s="7"/>
@@ -7004,7 +7040,7 @@
     <row r="298" spans="1:18">
       <c r="A298" s="8"/>
       <c r="B298" s="10"/>
-      <c r="C298" s="16"/>
+      <c r="C298" s="15"/>
       <c r="D298" s="5"/>
       <c r="E298" s="6"/>
       <c r="F298" s="7"/>
@@ -7024,7 +7060,7 @@
     <row r="299" spans="1:18">
       <c r="A299" s="8"/>
       <c r="B299" s="10"/>
-      <c r="C299" s="16"/>
+      <c r="C299" s="15"/>
       <c r="D299" s="5"/>
       <c r="E299" s="6"/>
       <c r="F299" s="7"/>
@@ -7044,7 +7080,7 @@
     <row r="300" spans="1:18">
       <c r="A300" s="8"/>
       <c r="B300" s="10"/>
-      <c r="C300" s="16"/>
+      <c r="C300" s="15"/>
       <c r="D300" s="5"/>
       <c r="E300" s="6"/>
       <c r="F300" s="7"/>
@@ -7064,7 +7100,7 @@
     <row r="301" spans="1:18">
       <c r="A301" s="8"/>
       <c r="B301" s="10"/>
-      <c r="C301" s="16"/>
+      <c r="C301" s="15"/>
       <c r="D301" s="5"/>
       <c r="E301" s="6"/>
       <c r="F301" s="7"/>
@@ -7084,7 +7120,7 @@
     <row r="302" spans="1:18">
       <c r="A302" s="8"/>
       <c r="B302" s="10"/>
-      <c r="C302" s="16"/>
+      <c r="C302" s="15"/>
       <c r="D302" s="5"/>
       <c r="E302" s="6"/>
       <c r="F302" s="7"/>
@@ -7104,7 +7140,7 @@
     <row r="303" spans="1:18">
       <c r="A303" s="8"/>
       <c r="B303" s="10"/>
-      <c r="C303" s="16"/>
+      <c r="C303" s="15"/>
       <c r="D303" s="5"/>
       <c r="E303" s="6"/>
       <c r="F303" s="7"/>
@@ -7124,7 +7160,7 @@
     <row r="304" spans="1:18">
       <c r="A304" s="8"/>
       <c r="B304" s="10"/>
-      <c r="C304" s="16"/>
+      <c r="C304" s="15"/>
       <c r="D304" s="5"/>
       <c r="E304" s="6"/>
       <c r="F304" s="7"/>
@@ -7144,7 +7180,7 @@
     <row r="305" spans="1:18">
       <c r="A305" s="8"/>
       <c r="B305" s="10"/>
-      <c r="C305" s="16"/>
+      <c r="C305" s="15"/>
       <c r="D305" s="5"/>
       <c r="E305" s="6"/>
       <c r="F305" s="7"/>
@@ -7164,7 +7200,7 @@
     <row r="306" spans="1:18">
       <c r="A306" s="8"/>
       <c r="B306" s="10"/>
-      <c r="C306" s="16"/>
+      <c r="C306" s="15"/>
       <c r="D306" s="5"/>
       <c r="E306" s="6"/>
       <c r="F306" s="7"/>
@@ -7184,7 +7220,7 @@
     <row r="307" spans="1:18">
       <c r="A307" s="8"/>
       <c r="B307" s="10"/>
-      <c r="C307" s="16"/>
+      <c r="C307" s="15"/>
       <c r="D307" s="5"/>
       <c r="E307" s="6"/>
       <c r="F307" s="7"/>
@@ -7204,7 +7240,7 @@
     <row r="308" spans="1:18">
       <c r="A308" s="8"/>
       <c r="B308" s="10"/>
-      <c r="C308" s="16"/>
+      <c r="C308" s="15"/>
       <c r="D308" s="5"/>
       <c r="E308" s="6"/>
       <c r="F308" s="7"/>
@@ -7224,7 +7260,7 @@
     <row r="309" spans="1:18">
       <c r="A309" s="8"/>
       <c r="B309" s="10"/>
-      <c r="C309" s="16"/>
+      <c r="C309" s="15"/>
       <c r="D309" s="5"/>
       <c r="E309" s="6"/>
       <c r="F309" s="7"/>
@@ -7244,7 +7280,7 @@
     <row r="310" spans="1:18">
       <c r="A310" s="8"/>
       <c r="B310" s="10"/>
-      <c r="C310" s="16"/>
+      <c r="C310" s="15"/>
       <c r="D310" s="5"/>
       <c r="E310" s="6"/>
       <c r="F310" s="7"/>
@@ -7264,7 +7300,7 @@
     <row r="311" spans="1:18">
       <c r="A311" s="8"/>
       <c r="B311" s="10"/>
-      <c r="C311" s="16"/>
+      <c r="C311" s="15"/>
       <c r="D311" s="5"/>
       <c r="E311" s="6"/>
       <c r="F311" s="7"/>
@@ -7284,7 +7320,7 @@
     <row r="312" spans="1:18">
       <c r="A312" s="8"/>
       <c r="B312" s="10"/>
-      <c r="C312" s="16"/>
+      <c r="C312" s="15"/>
       <c r="D312" s="5"/>
       <c r="E312" s="6"/>
       <c r="F312" s="7"/>
@@ -7304,7 +7340,7 @@
     <row r="313" spans="1:18">
       <c r="A313" s="8"/>
       <c r="B313" s="10"/>
-      <c r="C313" s="16"/>
+      <c r="C313" s="15"/>
       <c r="D313" s="5"/>
       <c r="E313" s="6"/>
       <c r="F313" s="7"/>
@@ -7324,7 +7360,7 @@
     <row r="314" spans="1:18">
       <c r="A314" s="8"/>
       <c r="B314" s="10"/>
-      <c r="C314" s="16"/>
+      <c r="C314" s="15"/>
       <c r="D314" s="5"/>
       <c r="E314" s="6"/>
       <c r="F314" s="7"/>
@@ -7344,7 +7380,7 @@
     <row r="315" spans="1:18">
       <c r="A315" s="8"/>
       <c r="B315" s="10"/>
-      <c r="C315" s="16"/>
+      <c r="C315" s="15"/>
       <c r="D315" s="5"/>
       <c r="E315" s="6"/>
       <c r="F315" s="7"/>
@@ -7364,7 +7400,7 @@
     <row r="316" spans="1:18">
       <c r="A316" s="8"/>
       <c r="B316" s="10"/>
-      <c r="C316" s="16"/>
+      <c r="C316" s="15"/>
       <c r="D316" s="5"/>
       <c r="E316" s="6"/>
       <c r="F316" s="7"/>
@@ -7384,7 +7420,7 @@
     <row r="317" spans="1:18">
       <c r="A317" s="8"/>
       <c r="B317" s="10"/>
-      <c r="C317" s="16"/>
+      <c r="C317" s="15"/>
       <c r="D317" s="5"/>
       <c r="E317" s="6"/>
       <c r="F317" s="7"/>
@@ -7404,7 +7440,7 @@
     <row r="318" spans="1:18">
       <c r="A318" s="8"/>
       <c r="B318" s="10"/>
-      <c r="C318" s="16"/>
+      <c r="C318" s="15"/>
       <c r="D318" s="5"/>
       <c r="E318" s="6"/>
       <c r="F318" s="7"/>
@@ -7424,7 +7460,7 @@
     <row r="319" spans="1:18">
       <c r="A319" s="8"/>
       <c r="B319" s="10"/>
-      <c r="C319" s="16"/>
+      <c r="C319" s="15"/>
       <c r="D319" s="5"/>
       <c r="E319" s="6"/>
       <c r="F319" s="7"/>
@@ -7444,7 +7480,7 @@
     <row r="320" spans="1:18">
       <c r="A320" s="8"/>
       <c r="B320" s="10"/>
-      <c r="C320" s="16"/>
+      <c r="C320" s="15"/>
       <c r="D320" s="5"/>
       <c r="E320" s="6"/>
       <c r="F320" s="7"/>
@@ -7464,7 +7500,7 @@
     <row r="321" spans="1:18">
       <c r="A321" s="8"/>
       <c r="B321" s="10"/>
-      <c r="C321" s="16"/>
+      <c r="C321" s="15"/>
       <c r="D321" s="5"/>
       <c r="E321" s="6"/>
       <c r="F321" s="7"/>
@@ -7484,7 +7520,7 @@
     <row r="322" spans="1:18">
       <c r="A322" s="8"/>
       <c r="B322" s="10"/>
-      <c r="C322" s="16"/>
+      <c r="C322" s="15"/>
       <c r="D322" s="5"/>
       <c r="E322" s="6"/>
       <c r="F322" s="7"/>
@@ -7504,7 +7540,7 @@
     <row r="323" spans="1:18">
       <c r="A323" s="8"/>
       <c r="B323" s="10"/>
-      <c r="C323" s="16"/>
+      <c r="C323" s="15"/>
       <c r="D323" s="5"/>
       <c r="E323" s="6"/>
       <c r="F323" s="7"/>
@@ -7524,7 +7560,7 @@
     <row r="324" spans="1:18">
       <c r="A324" s="8"/>
       <c r="B324" s="10"/>
-      <c r="C324" s="16"/>
+      <c r="C324" s="15"/>
       <c r="D324" s="5"/>
       <c r="E324" s="6"/>
       <c r="F324" s="7"/>
@@ -7544,7 +7580,7 @@
     <row r="325" spans="1:18">
       <c r="A325" s="8"/>
       <c r="B325" s="10"/>
-      <c r="C325" s="16"/>
+      <c r="C325" s="15"/>
       <c r="D325" s="5"/>
       <c r="E325" s="6"/>
       <c r="F325" s="7"/>
@@ -7564,7 +7600,7 @@
     <row r="326" spans="1:18">
       <c r="A326" s="8"/>
       <c r="B326" s="10"/>
-      <c r="C326" s="16"/>
+      <c r="C326" s="15"/>
       <c r="D326" s="5"/>
       <c r="E326" s="6"/>
       <c r="F326" s="7"/>
@@ -7584,7 +7620,7 @@
     <row r="327" spans="1:18">
       <c r="A327" s="8"/>
       <c r="B327" s="10"/>
-      <c r="C327" s="16"/>
+      <c r="C327" s="15"/>
       <c r="D327" s="5"/>
       <c r="E327" s="6"/>
       <c r="F327" s="7"/>
@@ -7604,7 +7640,7 @@
     <row r="328" spans="1:18">
       <c r="A328" s="8"/>
       <c r="B328" s="10"/>
-      <c r="C328" s="16"/>
+      <c r="C328" s="15"/>
       <c r="D328" s="5"/>
       <c r="E328" s="6"/>
       <c r="F328" s="7"/>
@@ -7624,7 +7660,7 @@
     <row r="329" spans="1:18">
       <c r="A329" s="8"/>
       <c r="B329" s="10"/>
-      <c r="C329" s="16"/>
+      <c r="C329" s="15"/>
       <c r="D329" s="5"/>
       <c r="E329" s="6"/>
       <c r="F329" s="7"/>
@@ -7644,7 +7680,7 @@
     <row r="330" spans="1:18">
       <c r="A330" s="8"/>
       <c r="B330" s="10"/>
-      <c r="C330" s="16"/>
+      <c r="C330" s="15"/>
       <c r="D330" s="5"/>
       <c r="E330" s="6"/>
       <c r="F330" s="7"/>
@@ -7664,7 +7700,7 @@
     <row r="331" spans="1:18">
       <c r="A331" s="8"/>
       <c r="B331" s="10"/>
-      <c r="C331" s="16"/>
+      <c r="C331" s="15"/>
       <c r="D331" s="5"/>
       <c r="E331" s="6"/>
       <c r="F331" s="7"/>
@@ -7684,7 +7720,7 @@
     <row r="332" spans="1:18">
       <c r="A332" s="8"/>
       <c r="B332" s="10"/>
-      <c r="C332" s="16"/>
+      <c r="C332" s="15"/>
       <c r="D332" s="5"/>
       <c r="E332" s="6"/>
       <c r="F332" s="7"/>
@@ -7704,7 +7740,7 @@
     <row r="333" spans="1:18">
       <c r="A333" s="8"/>
       <c r="B333" s="10"/>
-      <c r="C333" s="16"/>
+      <c r="C333" s="15"/>
       <c r="D333" s="5"/>
       <c r="E333" s="6"/>
       <c r="F333" s="7"/>
@@ -7724,7 +7760,7 @@
     <row r="334" spans="1:18">
       <c r="A334" s="8"/>
       <c r="B334" s="10"/>
-      <c r="C334" s="16"/>
+      <c r="C334" s="15"/>
       <c r="D334" s="5"/>
       <c r="E334" s="6"/>
       <c r="F334" s="7"/>
@@ -7744,7 +7780,7 @@
     <row r="335" spans="1:18">
       <c r="A335" s="8"/>
       <c r="B335" s="10"/>
-      <c r="C335" s="16"/>
+      <c r="C335" s="15"/>
       <c r="D335" s="5"/>
       <c r="E335" s="6"/>
       <c r="F335" s="7"/>
@@ -7764,7 +7800,7 @@
     <row r="336" spans="1:18">
       <c r="A336" s="8"/>
       <c r="B336" s="10"/>
-      <c r="C336" s="16"/>
+      <c r="C336" s="15"/>
       <c r="D336" s="5"/>
       <c r="E336" s="6"/>
       <c r="F336" s="7"/>
@@ -7784,7 +7820,7 @@
     <row r="337" spans="1:18">
       <c r="A337" s="8"/>
       <c r="B337" s="10"/>
-      <c r="C337" s="16"/>
+      <c r="C337" s="15"/>
       <c r="D337" s="5"/>
       <c r="E337" s="6"/>
       <c r="F337" s="7"/>
@@ -7804,7 +7840,7 @@
     <row r="338" spans="1:18">
       <c r="A338" s="8"/>
       <c r="B338" s="10"/>
-      <c r="C338" s="16"/>
+      <c r="C338" s="15"/>
       <c r="D338" s="5"/>
       <c r="E338" s="6"/>
       <c r="F338" s="7"/>
@@ -7824,7 +7860,7 @@
     <row r="339" spans="1:18">
       <c r="A339" s="8"/>
       <c r="B339" s="10"/>
-      <c r="C339" s="16"/>
+      <c r="C339" s="15"/>
       <c r="D339" s="5"/>
       <c r="E339" s="6"/>
       <c r="F339" s="7"/>
@@ -7844,7 +7880,7 @@
     <row r="340" spans="1:18">
       <c r="A340" s="8"/>
       <c r="B340" s="10"/>
-      <c r="C340" s="16"/>
+      <c r="C340" s="15"/>
       <c r="D340" s="5"/>
       <c r="E340" s="6"/>
       <c r="F340" s="7"/>
@@ -7864,7 +7900,7 @@
     <row r="341" spans="1:18">
       <c r="A341" s="8"/>
       <c r="B341" s="10"/>
-      <c r="C341" s="16"/>
+      <c r="C341" s="15"/>
       <c r="D341" s="5"/>
       <c r="E341" s="6"/>
       <c r="F341" s="7"/>
@@ -7884,7 +7920,7 @@
     <row r="342" spans="1:18">
       <c r="A342" s="8"/>
       <c r="B342" s="10"/>
-      <c r="C342" s="16"/>
+      <c r="C342" s="15"/>
       <c r="D342" s="5"/>
       <c r="E342" s="6"/>
       <c r="F342" s="7"/>
@@ -7904,7 +7940,7 @@
     <row r="343" spans="1:18">
       <c r="A343" s="8"/>
       <c r="B343" s="10"/>
-      <c r="C343" s="16"/>
+      <c r="C343" s="15"/>
       <c r="D343" s="5"/>
       <c r="E343" s="6"/>
       <c r="F343" s="7"/>
@@ -7924,7 +7960,7 @@
     <row r="344" spans="1:18">
       <c r="A344" s="8"/>
       <c r="B344" s="10"/>
-      <c r="C344" s="16"/>
+      <c r="C344" s="15"/>
       <c r="D344" s="5"/>
       <c r="E344" s="6"/>
       <c r="F344" s="7"/>
@@ -7944,7 +7980,7 @@
     <row r="345" spans="1:18">
       <c r="A345" s="8"/>
       <c r="B345" s="10"/>
-      <c r="C345" s="16"/>
+      <c r="C345" s="15"/>
       <c r="D345" s="5"/>
       <c r="E345" s="6"/>
       <c r="F345" s="7"/>
@@ -7964,7 +8000,7 @@
     <row r="346" spans="1:18">
       <c r="A346" s="8"/>
       <c r="B346" s="10"/>
-      <c r="C346" s="16"/>
+      <c r="C346" s="15"/>
       <c r="D346" s="5"/>
       <c r="E346" s="6"/>
       <c r="F346" s="7"/>
@@ -7984,7 +8020,7 @@
     <row r="347" spans="1:18">
       <c r="A347" s="8"/>
       <c r="B347" s="10"/>
-      <c r="C347" s="16"/>
+      <c r="C347" s="15"/>
       <c r="D347" s="5"/>
       <c r="E347" s="6"/>
       <c r="F347" s="7"/>
@@ -8004,7 +8040,7 @@
     <row r="348" spans="1:18">
       <c r="A348" s="8"/>
       <c r="B348" s="10"/>
-      <c r="C348" s="16"/>
+      <c r="C348" s="15"/>
       <c r="D348" s="5"/>
       <c r="E348" s="6"/>
       <c r="F348" s="7"/>
@@ -8024,7 +8060,7 @@
     <row r="349" spans="1:18">
       <c r="A349" s="8"/>
       <c r="B349" s="10"/>
-      <c r="C349" s="16"/>
+      <c r="C349" s="15"/>
       <c r="D349" s="5"/>
       <c r="E349" s="6"/>
       <c r="F349" s="7"/>
@@ -8044,7 +8080,7 @@
     <row r="350" spans="1:18">
       <c r="A350" s="8"/>
       <c r="B350" s="10"/>
-      <c r="C350" s="16"/>
+      <c r="C350" s="15"/>
       <c r="D350" s="5"/>
       <c r="E350" s="6"/>
       <c r="F350" s="7"/>
@@ -8064,7 +8100,7 @@
     <row r="351" spans="1:18">
       <c r="A351" s="8"/>
       <c r="B351" s="10"/>
-      <c r="C351" s="16"/>
+      <c r="C351" s="15"/>
       <c r="D351" s="5"/>
       <c r="E351" s="6"/>
       <c r="F351" s="7"/>
@@ -8084,7 +8120,7 @@
     <row r="352" spans="1:18">
       <c r="A352" s="8"/>
       <c r="B352" s="10"/>
-      <c r="C352" s="16"/>
+      <c r="C352" s="15"/>
       <c r="D352" s="5"/>
       <c r="E352" s="6"/>
       <c r="F352" s="7"/>
@@ -8104,7 +8140,7 @@
     <row r="353" spans="1:18">
       <c r="A353" s="8"/>
       <c r="B353" s="10"/>
-      <c r="C353" s="16"/>
+      <c r="C353" s="15"/>
       <c r="D353" s="5"/>
       <c r="E353" s="6"/>
       <c r="F353" s="7"/>
@@ -8124,7 +8160,7 @@
     <row r="354" spans="1:18">
       <c r="A354" s="8"/>
       <c r="B354" s="10"/>
-      <c r="C354" s="16"/>
+      <c r="C354" s="15"/>
       <c r="D354" s="5"/>
       <c r="E354" s="6"/>
       <c r="F354" s="7"/>
@@ -8144,7 +8180,7 @@
     <row r="355" spans="1:18">
       <c r="A355" s="8"/>
       <c r="B355" s="10"/>
-      <c r="C355" s="16"/>
+      <c r="C355" s="15"/>
       <c r="D355" s="5"/>
       <c r="E355" s="6"/>
       <c r="F355" s="7"/>
@@ -8164,7 +8200,7 @@
     <row r="356" spans="1:18">
       <c r="A356" s="8"/>
       <c r="B356" s="10"/>
-      <c r="C356" s="16"/>
+      <c r="C356" s="15"/>
       <c r="D356" s="5"/>
       <c r="E356" s="6"/>
       <c r="F356" s="7"/>
@@ -8184,7 +8220,7 @@
     <row r="357" spans="1:18">
       <c r="A357" s="8"/>
       <c r="B357" s="10"/>
-      <c r="C357" s="16"/>
+      <c r="C357" s="15"/>
       <c r="D357" s="5"/>
       <c r="E357" s="6"/>
       <c r="F357" s="7"/>
@@ -8204,7 +8240,7 @@
     <row r="358" spans="1:18">
       <c r="A358" s="8"/>
       <c r="B358" s="10"/>
-      <c r="C358" s="16"/>
+      <c r="C358" s="15"/>
       <c r="D358" s="5"/>
       <c r="E358" s="6"/>
       <c r="F358" s="7"/>
@@ -8224,7 +8260,7 @@
     <row r="359" spans="1:18">
       <c r="A359" s="8"/>
       <c r="B359" s="10"/>
-      <c r="C359" s="16"/>
+      <c r="C359" s="15"/>
       <c r="D359" s="5"/>
       <c r="E359" s="6"/>
       <c r="F359" s="7"/>
@@ -8244,7 +8280,7 @@
     <row r="360" spans="1:18">
       <c r="A360" s="8"/>
       <c r="B360" s="10"/>
-      <c r="C360" s="16"/>
+      <c r="C360" s="15"/>
       <c r="D360" s="5"/>
       <c r="E360" s="6"/>
       <c r="F360" s="7"/>
@@ -8264,7 +8300,7 @@
     <row r="361" spans="1:18">
       <c r="A361" s="8"/>
       <c r="B361" s="10"/>
-      <c r="C361" s="16"/>
+      <c r="C361" s="15"/>
       <c r="D361" s="5"/>
       <c r="E361" s="6"/>
       <c r="F361" s="7"/>
@@ -8284,7 +8320,7 @@
     <row r="362" spans="1:18">
       <c r="A362" s="8"/>
       <c r="B362" s="10"/>
-      <c r="C362" s="16"/>
+      <c r="C362" s="15"/>
       <c r="D362" s="5"/>
       <c r="E362" s="6"/>
       <c r="F362" s="7"/>
@@ -8304,7 +8340,7 @@
     <row r="363" spans="1:18">
       <c r="A363" s="8"/>
       <c r="B363" s="10"/>
-      <c r="C363" s="16"/>
+      <c r="C363" s="15"/>
       <c r="D363" s="5"/>
       <c r="E363" s="6"/>
       <c r="F363" s="7"/>
@@ -8324,7 +8360,7 @@
     <row r="364" spans="1:18">
       <c r="A364" s="8"/>
       <c r="B364" s="10"/>
-      <c r="C364" s="16"/>
+      <c r="C364" s="15"/>
       <c r="D364" s="5"/>
       <c r="E364" s="6"/>
       <c r="F364" s="7"/>
@@ -8344,7 +8380,7 @@
     <row r="365" spans="1:18">
       <c r="A365" s="8"/>
       <c r="B365" s="10"/>
-      <c r="C365" s="16"/>
+      <c r="C365" s="15"/>
       <c r="D365" s="5"/>
       <c r="E365" s="6"/>
       <c r="F365" s="7"/>
@@ -8364,7 +8400,7 @@
     <row r="366" spans="1:18">
       <c r="A366" s="8"/>
       <c r="B366" s="10"/>
-      <c r="C366" s="16"/>
+      <c r="C366" s="15"/>
       <c r="D366" s="5"/>
       <c r="E366" s="6"/>
       <c r="F366" s="7"/>
@@ -8384,7 +8420,7 @@
     <row r="367" spans="1:18">
       <c r="A367" s="8"/>
       <c r="B367" s="10"/>
-      <c r="C367" s="16"/>
+      <c r="C367" s="15"/>
       <c r="D367" s="5"/>
       <c r="E367" s="6"/>
       <c r="F367" s="7"/>
@@ -8404,7 +8440,7 @@
     <row r="368" spans="1:18">
       <c r="A368" s="8"/>
       <c r="B368" s="10"/>
-      <c r="C368" s="16"/>
+      <c r="C368" s="15"/>
       <c r="D368" s="5"/>
       <c r="E368" s="6"/>
       <c r="F368" s="7"/>
@@ -8424,7 +8460,7 @@
     <row r="369" spans="1:18">
       <c r="A369" s="8"/>
       <c r="B369" s="10"/>
-      <c r="C369" s="16"/>
+      <c r="C369" s="15"/>
       <c r="D369" s="5"/>
       <c r="E369" s="6"/>
       <c r="F369" s="7"/>
@@ -8444,7 +8480,7 @@
     <row r="370" spans="1:18">
       <c r="A370" s="8"/>
       <c r="B370" s="10"/>
-      <c r="C370" s="16"/>
+      <c r="C370" s="15"/>
       <c r="D370" s="5"/>
       <c r="E370" s="6"/>
       <c r="F370" s="7"/>
@@ -8464,7 +8500,7 @@
     <row r="371" spans="1:18">
       <c r="A371" s="8"/>
       <c r="B371" s="10"/>
-      <c r="C371" s="16"/>
+      <c r="C371" s="15"/>
       <c r="D371" s="5"/>
       <c r="E371" s="6"/>
       <c r="F371" s="7"/>
@@ -8484,7 +8520,7 @@
     <row r="372" spans="1:18">
       <c r="A372" s="8"/>
       <c r="B372" s="10"/>
-      <c r="C372" s="16"/>
+      <c r="C372" s="15"/>
       <c r="D372" s="5"/>
       <c r="E372" s="6"/>
       <c r="F372" s="7"/>
@@ -8504,7 +8540,7 @@
     <row r="373" spans="1:18">
       <c r="A373" s="8"/>
       <c r="B373" s="10"/>
-      <c r="C373" s="16"/>
+      <c r="C373" s="15"/>
       <c r="D373" s="5"/>
       <c r="E373" s="6"/>
       <c r="F373" s="7"/>
@@ -8524,7 +8560,7 @@
     <row r="374" spans="1:18">
       <c r="A374" s="8"/>
       <c r="B374" s="10"/>
-      <c r="C374" s="16"/>
+      <c r="C374" s="15"/>
       <c r="D374" s="5"/>
       <c r="E374" s="6"/>
       <c r="F374" s="7"/>
@@ -8544,7 +8580,7 @@
     <row r="375" spans="1:18">
       <c r="A375" s="8"/>
       <c r="B375" s="10"/>
-      <c r="C375" s="16"/>
+      <c r="C375" s="15"/>
       <c r="D375" s="5"/>
       <c r="E375" s="6"/>
       <c r="F375" s="7"/>
@@ -8564,7 +8600,7 @@
     <row r="376" spans="1:18">
       <c r="A376" s="8"/>
       <c r="B376" s="10"/>
-      <c r="C376" s="16"/>
+      <c r="C376" s="15"/>
       <c r="D376" s="5"/>
       <c r="E376" s="6"/>
       <c r="F376" s="7"/>
@@ -8584,7 +8620,7 @@
     <row r="377" spans="1:18">
       <c r="A377" s="8"/>
       <c r="B377" s="10"/>
-      <c r="C377" s="16"/>
+      <c r="C377" s="15"/>
       <c r="D377" s="5"/>
       <c r="E377" s="6"/>
       <c r="F377" s="7"/>
@@ -8604,7 +8640,7 @@
     <row r="378" spans="1:18">
       <c r="A378" s="8"/>
       <c r="B378" s="10"/>
-      <c r="C378" s="16"/>
+      <c r="C378" s="15"/>
       <c r="D378" s="5"/>
       <c r="E378" s="6"/>
       <c r="F378" s="7"/>
@@ -8624,7 +8660,7 @@
     <row r="379" spans="1:18">
       <c r="A379" s="8"/>
       <c r="B379" s="10"/>
-      <c r="C379" s="16"/>
+      <c r="C379" s="15"/>
       <c r="D379" s="5"/>
       <c r="E379" s="6"/>
       <c r="F379" s="7"/>
@@ -8644,7 +8680,7 @@
     <row r="380" spans="1:18">
       <c r="A380" s="8"/>
       <c r="B380" s="10"/>
-      <c r="C380" s="16"/>
+      <c r="C380" s="15"/>
       <c r="D380" s="5"/>
       <c r="E380" s="6"/>
       <c r="F380" s="7"/>
@@ -8664,7 +8700,7 @@
     <row r="381" spans="1:18">
       <c r="A381" s="8"/>
       <c r="B381" s="10"/>
-      <c r="C381" s="16"/>
+      <c r="C381" s="15"/>
       <c r="D381" s="5"/>
       <c r="E381" s="6"/>
       <c r="F381" s="7"/>
@@ -8684,7 +8720,7 @@
     <row r="382" spans="1:18">
       <c r="A382" s="8"/>
       <c r="B382" s="10"/>
-      <c r="C382" s="16"/>
+      <c r="C382" s="15"/>
       <c r="D382" s="5"/>
       <c r="E382" s="6"/>
       <c r="F382" s="7"/>
@@ -8704,7 +8740,7 @@
     <row r="383" spans="1:18">
       <c r="A383" s="8"/>
       <c r="B383" s="10"/>
-      <c r="C383" s="16"/>
+      <c r="C383" s="15"/>
       <c r="D383" s="5"/>
       <c r="E383" s="6"/>
       <c r="F383" s="7"/>
@@ -8724,7 +8760,7 @@
     <row r="384" spans="1:18">
       <c r="A384" s="8"/>
       <c r="B384" s="10"/>
-      <c r="C384" s="16"/>
+      <c r="C384" s="15"/>
       <c r="D384" s="5"/>
       <c r="E384" s="6"/>
       <c r="F384" s="7"/>
@@ -8744,7 +8780,7 @@
     <row r="385" spans="1:18">
       <c r="A385" s="8"/>
       <c r="B385" s="10"/>
-      <c r="C385" s="16"/>
+      <c r="C385" s="15"/>
       <c r="D385" s="5"/>
       <c r="E385" s="6"/>
       <c r="F385" s="7"/>
@@ -8764,7 +8800,7 @@
     <row r="386" spans="1:18">
       <c r="A386" s="8"/>
       <c r="B386" s="10"/>
-      <c r="C386" s="16"/>
+      <c r="C386" s="15"/>
       <c r="D386" s="5"/>
       <c r="E386" s="6"/>
       <c r="F386" s="7"/>
@@ -8784,7 +8820,7 @@
     <row r="387" spans="1:18">
       <c r="A387" s="8"/>
       <c r="B387" s="10"/>
-      <c r="C387" s="16"/>
+      <c r="C387" s="15"/>
       <c r="D387" s="5"/>
       <c r="E387" s="6"/>
       <c r="F387" s="7"/>
@@ -8804,7 +8840,7 @@
     <row r="388" spans="1:18">
       <c r="A388" s="8"/>
       <c r="B388" s="10"/>
-      <c r="C388" s="16"/>
+      <c r="C388" s="15"/>
       <c r="D388" s="5"/>
       <c r="E388" s="6"/>
       <c r="F388" s="7"/>
@@ -8824,7 +8860,7 @@
     <row r="389" spans="1:18">
       <c r="A389" s="8"/>
       <c r="B389" s="10"/>
-      <c r="C389" s="16"/>
+      <c r="C389" s="15"/>
       <c r="D389" s="5"/>
       <c r="E389" s="6"/>
       <c r="F389" s="7"/>
@@ -8844,7 +8880,7 @@
     <row r="390" spans="1:18">
       <c r="A390" s="8"/>
       <c r="B390" s="10"/>
-      <c r="C390" s="16"/>
+      <c r="C390" s="15"/>
       <c r="D390" s="5"/>
       <c r="E390" s="6"/>
       <c r="F390" s="7"/>
@@ -8864,7 +8900,7 @@
     <row r="391" spans="1:18">
       <c r="A391" s="8"/>
       <c r="B391" s="10"/>
-      <c r="C391" s="16"/>
+      <c r="C391" s="15"/>
       <c r="D391" s="5"/>
       <c r="E391" s="6"/>
       <c r="F391" s="7"/>
@@ -8884,7 +8920,7 @@
     <row r="392" spans="1:18">
       <c r="A392" s="8"/>
       <c r="B392" s="10"/>
-      <c r="C392" s="16"/>
+      <c r="C392" s="15"/>
       <c r="D392" s="5"/>
       <c r="E392" s="6"/>
       <c r="F392" s="7"/>
@@ -8904,7 +8940,7 @@
     <row r="393" spans="1:18">
       <c r="A393" s="8"/>
       <c r="B393" s="10"/>
-      <c r="C393" s="16"/>
+      <c r="C393" s="15"/>
       <c r="D393" s="5"/>
       <c r="E393" s="6"/>
       <c r="F393" s="7"/>
@@ -8924,7 +8960,7 @@
     <row r="394" spans="1:18">
       <c r="A394" s="8"/>
       <c r="B394" s="10"/>
-      <c r="C394" s="16"/>
+      <c r="C394" s="15"/>
       <c r="D394" s="5"/>
       <c r="E394" s="6"/>
       <c r="F394" s="7"/>
@@ -8944,7 +8980,7 @@
     <row r="395" spans="1:18">
       <c r="A395" s="8"/>
       <c r="B395" s="10"/>
-      <c r="C395" s="16"/>
+      <c r="C395" s="15"/>
       <c r="D395" s="5"/>
       <c r="E395" s="6"/>
       <c r="F395" s="7"/>
@@ -8964,7 +9000,7 @@
     <row r="396" spans="1:18">
       <c r="A396" s="8"/>
       <c r="B396" s="10"/>
-      <c r="C396" s="16"/>
+      <c r="C396" s="15"/>
       <c r="D396" s="5"/>
       <c r="E396" s="6"/>
       <c r="F396" s="7"/>
@@ -8984,7 +9020,7 @@
     <row r="397" spans="1:18">
       <c r="A397" s="8"/>
       <c r="B397" s="10"/>
-      <c r="C397" s="16"/>
+      <c r="C397" s="15"/>
       <c r="D397" s="5"/>
       <c r="E397" s="6"/>
       <c r="F397" s="7"/>
@@ -9004,7 +9040,7 @@
     <row r="398" spans="1:18">
       <c r="A398" s="8"/>
       <c r="B398" s="10"/>
-      <c r="C398" s="16"/>
+      <c r="C398" s="15"/>
       <c r="D398" s="5"/>
       <c r="E398" s="6"/>
       <c r="F398" s="7"/>
@@ -9024,7 +9060,7 @@
     <row r="399" spans="1:18">
       <c r="A399" s="8"/>
       <c r="B399" s="10"/>
-      <c r="C399" s="16"/>
+      <c r="C399" s="15"/>
       <c r="D399" s="5"/>
       <c r="E399" s="6"/>
       <c r="F399" s="7"/>
@@ -9044,7 +9080,7 @@
     <row r="400" spans="1:18">
       <c r="A400" s="8"/>
       <c r="B400" s="10"/>
-      <c r="C400" s="16"/>
+      <c r="C400" s="15"/>
       <c r="D400" s="5"/>
       <c r="E400" s="6"/>
       <c r="F400" s="7"/>
@@ -9064,7 +9100,7 @@
     <row r="401" spans="1:18">
       <c r="A401" s="8"/>
       <c r="B401" s="10"/>
-      <c r="C401" s="16"/>
+      <c r="C401" s="15"/>
       <c r="D401" s="5"/>
       <c r="E401" s="6"/>
       <c r="F401" s="7"/>
@@ -9084,7 +9120,7 @@
     <row r="402" spans="1:18">
       <c r="A402" s="8"/>
       <c r="B402" s="10"/>
-      <c r="C402" s="16"/>
+      <c r="C402" s="15"/>
       <c r="D402" s="5"/>
       <c r="E402" s="6"/>
       <c r="F402" s="7"/>
@@ -9104,7 +9140,7 @@
     <row r="403" spans="1:18">
       <c r="A403" s="8"/>
       <c r="B403" s="10"/>
-      <c r="C403" s="16"/>
+      <c r="C403" s="15"/>
       <c r="D403" s="5"/>
       <c r="E403" s="6"/>
       <c r="F403" s="7"/>
@@ -9124,7 +9160,7 @@
     <row r="404" spans="1:18">
       <c r="A404" s="8"/>
       <c r="B404" s="10"/>
-      <c r="C404" s="16"/>
+      <c r="C404" s="15"/>
       <c r="D404" s="5"/>
       <c r="E404" s="6"/>
       <c r="F404" s="7"/>
@@ -9144,7 +9180,7 @@
     <row r="405" spans="1:18">
       <c r="A405" s="8"/>
       <c r="B405" s="10"/>
-      <c r="C405" s="16"/>
+      <c r="C405" s="15"/>
       <c r="D405" s="5"/>
       <c r="E405" s="6"/>
       <c r="F405" s="7"/>
@@ -9164,7 +9200,7 @@
     <row r="406" spans="1:18">
       <c r="A406" s="8"/>
       <c r="B406" s="10"/>
-      <c r="C406" s="16"/>
+      <c r="C406" s="15"/>
       <c r="D406" s="5"/>
       <c r="E406" s="6"/>
       <c r="F406" s="7"/>
@@ -9184,7 +9220,7 @@
     <row r="407" spans="1:18">
       <c r="A407" s="8"/>
       <c r="B407" s="10"/>
-      <c r="C407" s="16"/>
+      <c r="C407" s="15"/>
       <c r="D407" s="5"/>
       <c r="E407" s="6"/>
       <c r="F407" s="7"/>
@@ -9204,7 +9240,7 @@
     <row r="408" spans="1:18">
       <c r="A408" s="8"/>
       <c r="B408" s="10"/>
-      <c r="C408" s="16"/>
+      <c r="C408" s="15"/>
       <c r="D408" s="5"/>
       <c r="E408" s="6"/>
       <c r="F408" s="7"/>
@@ -9224,7 +9260,7 @@
     <row r="409" spans="1:18">
       <c r="A409" s="8"/>
       <c r="B409" s="10"/>
-      <c r="C409" s="16"/>
+      <c r="C409" s="15"/>
       <c r="D409" s="5"/>
       <c r="E409" s="6"/>
       <c r="F409" s="7"/>
@@ -9244,7 +9280,7 @@
     <row r="410" spans="1:18">
       <c r="A410" s="8"/>
       <c r="B410" s="10"/>
-      <c r="C410" s="16"/>
+      <c r="C410" s="15"/>
       <c r="D410" s="5"/>
       <c r="E410" s="6"/>
       <c r="F410" s="7"/>
@@ -9264,7 +9300,7 @@
     <row r="411" spans="1:18">
       <c r="A411" s="8"/>
       <c r="B411" s="10"/>
-      <c r="C411" s="16"/>
+      <c r="C411" s="15"/>
       <c r="D411" s="5"/>
       <c r="E411" s="6"/>
       <c r="F411" s="7"/>
@@ -9284,7 +9320,7 @@
     <row r="412" spans="1:18">
       <c r="A412" s="8"/>
       <c r="B412" s="10"/>
-      <c r="C412" s="16"/>
+      <c r="C412" s="15"/>
       <c r="D412" s="5"/>
       <c r="E412" s="6"/>
       <c r="F412" s="7"/>
@@ -9304,7 +9340,7 @@
     <row r="413" spans="1:18">
       <c r="A413" s="8"/>
       <c r="B413" s="10"/>
-      <c r="C413" s="16"/>
+      <c r="C413" s="15"/>
       <c r="D413" s="5"/>
       <c r="E413" s="6"/>
       <c r="F413" s="7"/>
@@ -9324,7 +9360,7 @@
     <row r="414" spans="1:18">
       <c r="A414" s="8"/>
       <c r="B414" s="10"/>
-      <c r="C414" s="16"/>
+      <c r="C414" s="15"/>
       <c r="D414" s="5"/>
       <c r="E414" s="6"/>
       <c r="F414" s="7"/>
@@ -9344,7 +9380,7 @@
     <row r="415" spans="1:18">
       <c r="A415" s="8"/>
       <c r="B415" s="10"/>
-      <c r="C415" s="16"/>
+      <c r="C415" s="15"/>
       <c r="D415" s="5"/>
       <c r="E415" s="6"/>
       <c r="F415" s="7"/>
@@ -9364,7 +9400,7 @@
     <row r="416" spans="1:18">
       <c r="A416" s="8"/>
       <c r="B416" s="10"/>
-      <c r="C416" s="16"/>
+      <c r="C416" s="15"/>
       <c r="D416" s="5"/>
       <c r="E416" s="6"/>
       <c r="F416" s="7"/>
@@ -9384,7 +9420,7 @@
     <row r="417" spans="1:18">
       <c r="A417" s="8"/>
       <c r="B417" s="10"/>
-      <c r="C417" s="16"/>
+      <c r="C417" s="15"/>
       <c r="D417" s="5"/>
       <c r="E417" s="6"/>
       <c r="F417" s="7"/>
@@ -9404,7 +9440,7 @@
     <row r="418" spans="1:18">
       <c r="A418" s="8"/>
       <c r="B418" s="10"/>
-      <c r="C418" s="16"/>
+      <c r="C418" s="15"/>
       <c r="D418" s="5"/>
       <c r="E418" s="6"/>
       <c r="F418" s="7"/>
@@ -9424,7 +9460,7 @@
     <row r="419" spans="1:18">
       <c r="A419" s="8"/>
       <c r="B419" s="10"/>
-      <c r="C419" s="16"/>
+      <c r="C419" s="15"/>
       <c r="D419" s="5"/>
       <c r="E419" s="6"/>
       <c r="F419" s="7"/>
@@ -9444,7 +9480,7 @@
     <row r="420" spans="1:18">
       <c r="A420" s="8"/>
       <c r="B420" s="10"/>
-      <c r="C420" s="16"/>
+      <c r="C420" s="15"/>
       <c r="D420" s="5"/>
       <c r="E420" s="6"/>
       <c r="F420" s="7"/>
@@ -9464,7 +9500,7 @@
     <row r="421" spans="1:18">
       <c r="A421" s="8"/>
       <c r="B421" s="10"/>
-      <c r="C421" s="16"/>
+      <c r="C421" s="15"/>
       <c r="D421" s="5"/>
       <c r="E421" s="6"/>
       <c r="F421" s="7"/>
@@ -9484,7 +9520,7 @@
     <row r="422" spans="1:18">
       <c r="A422" s="8"/>
       <c r="B422" s="10"/>
-      <c r="C422" s="16"/>
+      <c r="C422" s="15"/>
       <c r="D422" s="5"/>
       <c r="E422" s="6"/>
       <c r="F422" s="7"/>
@@ -9504,7 +9540,7 @@
     <row r="423" spans="1:18">
       <c r="A423" s="8"/>
       <c r="B423" s="10"/>
-      <c r="C423" s="16"/>
+      <c r="C423" s="15"/>
       <c r="D423" s="5"/>
       <c r="E423" s="6"/>
       <c r="F423" s="7"/>
@@ -9524,7 +9560,7 @@
     <row r="424" spans="1:18">
       <c r="A424" s="8"/>
       <c r="B424" s="10"/>
-      <c r="C424" s="16"/>
+      <c r="C424" s="15"/>
       <c r="D424" s="5"/>
       <c r="E424" s="6"/>
       <c r="F424" s="7"/>
@@ -9544,7 +9580,7 @@
     <row r="425" spans="1:18">
       <c r="A425" s="8"/>
       <c r="B425" s="10"/>
-      <c r="C425" s="16"/>
+      <c r="C425" s="15"/>
       <c r="D425" s="5"/>
       <c r="E425" s="6"/>
       <c r="F425" s="7"/>
@@ -9564,7 +9600,7 @@
     <row r="426" spans="1:18">
       <c r="A426" s="8"/>
       <c r="B426" s="10"/>
-      <c r="C426" s="16"/>
+      <c r="C426" s="15"/>
       <c r="D426" s="5"/>
       <c r="E426" s="6"/>
       <c r="F426" s="7"/>
@@ -9584,7 +9620,7 @@
     <row r="427" spans="1:18">
       <c r="A427" s="8"/>
       <c r="B427" s="10"/>
-      <c r="C427" s="16"/>
+      <c r="C427" s="15"/>
       <c r="D427" s="5"/>
       <c r="E427" s="6"/>
       <c r="F427" s="7"/>
@@ -9604,7 +9640,7 @@
     <row r="428" spans="1:18">
       <c r="A428" s="8"/>
       <c r="B428" s="10"/>
-      <c r="C428" s="16"/>
+      <c r="C428" s="15"/>
       <c r="D428" s="5"/>
       <c r="E428" s="6"/>
       <c r="F428" s="7"/>
@@ -9624,7 +9660,7 @@
     <row r="429" spans="1:18">
       <c r="A429" s="8"/>
       <c r="B429" s="10"/>
-      <c r="C429" s="16"/>
+      <c r="C429" s="15"/>
       <c r="D429" s="5"/>
       <c r="E429" s="6"/>
       <c r="F429" s="7"/>
@@ -9644,7 +9680,7 @@
     <row r="430" spans="1:18">
       <c r="A430" s="8"/>
       <c r="B430" s="10"/>
-      <c r="C430" s="16"/>
+      <c r="C430" s="15"/>
       <c r="D430" s="5"/>
       <c r="E430" s="6"/>
       <c r="F430" s="7"/>
@@ -9664,7 +9700,7 @@
     <row r="431" spans="1:18">
       <c r="A431" s="8"/>
       <c r="B431" s="10"/>
-      <c r="C431" s="16"/>
+      <c r="C431" s="15"/>
       <c r="D431" s="5"/>
       <c r="E431" s="6"/>
       <c r="F431" s="7"/>
@@ -9684,7 +9720,7 @@
     <row r="432" spans="1:18">
       <c r="A432" s="8"/>
       <c r="B432" s="10"/>
-      <c r="C432" s="16"/>
+      <c r="C432" s="15"/>
       <c r="D432" s="5"/>
       <c r="E432" s="6"/>
       <c r="F432" s="7"/>
@@ -9704,7 +9740,7 @@
     <row r="433" spans="1:18">
       <c r="A433" s="8"/>
       <c r="B433" s="10"/>
-      <c r="C433" s="16"/>
+      <c r="C433" s="15"/>
       <c r="D433" s="5"/>
       <c r="E433" s="6"/>
       <c r="F433" s="7"/>
@@ -9724,7 +9760,7 @@
     <row r="434" spans="1:18">
       <c r="A434" s="8"/>
       <c r="B434" s="10"/>
-      <c r="C434" s="16"/>
+      <c r="C434" s="15"/>
       <c r="D434" s="5"/>
       <c r="E434" s="6"/>
       <c r="F434" s="7"/>
@@ -9744,7 +9780,7 @@
     <row r="435" spans="1:18">
       <c r="A435" s="8"/>
       <c r="B435" s="10"/>
-      <c r="C435" s="16"/>
+      <c r="C435" s="15"/>
       <c r="D435" s="5"/>
       <c r="E435" s="6"/>
       <c r="F435" s="7"/>
@@ -9764,7 +9800,7 @@
     <row r="436" spans="1:18">
       <c r="A436" s="8"/>
       <c r="B436" s="10"/>
-      <c r="C436" s="16"/>
+      <c r="C436" s="15"/>
       <c r="D436" s="5"/>
       <c r="E436" s="6"/>
       <c r="F436" s="7"/>
@@ -9784,7 +9820,7 @@
     <row r="437" spans="1:18">
       <c r="A437" s="8"/>
       <c r="B437" s="10"/>
-      <c r="C437" s="16"/>
+      <c r="C437" s="15"/>
       <c r="D437" s="5"/>
       <c r="E437" s="6"/>
       <c r="F437" s="7"/>
@@ -9804,7 +9840,7 @@
     <row r="438" spans="1:18">
       <c r="A438" s="8"/>
       <c r="B438" s="10"/>
-      <c r="C438" s="16"/>
+      <c r="C438" s="15"/>
       <c r="D438" s="5"/>
       <c r="E438" s="6"/>
       <c r="F438" s="7"/>
@@ -9824,7 +9860,7 @@
     <row r="439" spans="1:18">
       <c r="A439" s="8"/>
       <c r="B439" s="10"/>
-      <c r="C439" s="16"/>
+      <c r="C439" s="15"/>
       <c r="D439" s="5"/>
       <c r="E439" s="6"/>
       <c r="F439" s="7"/>
@@ -9844,7 +9880,7 @@
     <row r="440" spans="1:18">
       <c r="A440" s="8"/>
       <c r="B440" s="10"/>
-      <c r="C440" s="16"/>
+      <c r="C440" s="15"/>
       <c r="D440" s="5"/>
       <c r="E440" s="6"/>
       <c r="F440" s="7"/>
@@ -9864,7 +9900,7 @@
     <row r="441" spans="1:18">
       <c r="A441" s="8"/>
       <c r="B441" s="10"/>
-      <c r="C441" s="16"/>
+      <c r="C441" s="15"/>
       <c r="D441" s="5"/>
       <c r="E441" s="6"/>
       <c r="F441" s="7"/>
@@ -9884,7 +9920,7 @@
     <row r="442" spans="1:18">
       <c r="A442" s="8"/>
       <c r="B442" s="10"/>
-      <c r="C442" s="16"/>
+      <c r="C442" s="15"/>
       <c r="D442" s="5"/>
       <c r="E442" s="6"/>
       <c r="F442" s="7"/>
@@ -9904,7 +9940,7 @@
     <row r="443" spans="1:18">
       <c r="A443" s="8"/>
       <c r="B443" s="10"/>
-      <c r="C443" s="16"/>
+      <c r="C443" s="15"/>
       <c r="D443" s="5"/>
       <c r="E443" s="6"/>
       <c r="F443" s="7"/>
@@ -9924,7 +9960,7 @@
     <row r="444" spans="1:18">
       <c r="A444" s="8"/>
       <c r="B444" s="10"/>
-      <c r="C444" s="16"/>
+      <c r="C444" s="15"/>
       <c r="D444" s="5"/>
       <c r="E444" s="6"/>
       <c r="F444" s="7"/>
@@ -9944,7 +9980,7 @@
     <row r="445" spans="1:18">
       <c r="A445" s="8"/>
       <c r="B445" s="10"/>
-      <c r="C445" s="16"/>
+      <c r="C445" s="15"/>
       <c r="D445" s="5"/>
       <c r="E445" s="6"/>
       <c r="F445" s="7"/>
@@ -9964,7 +10000,7 @@
     <row r="446" spans="1:18">
       <c r="A446" s="8"/>
       <c r="B446" s="10"/>
-      <c r="C446" s="16"/>
+      <c r="C446" s="15"/>
       <c r="D446" s="5"/>
       <c r="E446" s="6"/>
       <c r="F446" s="7"/>
@@ -9984,7 +10020,7 @@
     <row r="447" spans="1:18">
       <c r="A447" s="8"/>
       <c r="B447" s="10"/>
-      <c r="C447" s="16"/>
+      <c r="C447" s="15"/>
       <c r="D447" s="5"/>
       <c r="E447" s="6"/>
       <c r="F447" s="7"/>
@@ -10004,7 +10040,7 @@
     <row r="448" spans="1:18">
       <c r="A448" s="8"/>
       <c r="B448" s="10"/>
-      <c r="C448" s="16"/>
+      <c r="C448" s="15"/>
       <c r="D448" s="5"/>
       <c r="E448" s="6"/>
       <c r="F448" s="7"/>
@@ -10024,7 +10060,7 @@
     <row r="449" spans="1:18">
       <c r="A449" s="8"/>
       <c r="B449" s="10"/>
-      <c r="C449" s="16"/>
+      <c r="C449" s="15"/>
       <c r="D449" s="5"/>
       <c r="E449" s="6"/>
       <c r="F449" s="7"/>
@@ -10044,7 +10080,7 @@
     <row r="450" spans="1:18">
       <c r="A450" s="8"/>
       <c r="B450" s="10"/>
-      <c r="C450" s="16"/>
+      <c r="C450" s="15"/>
       <c r="D450" s="5"/>
       <c r="E450" s="6"/>
       <c r="F450" s="7"/>
@@ -10064,7 +10100,7 @@
     <row r="451" spans="1:18">
       <c r="A451" s="8"/>
       <c r="B451" s="10"/>
-      <c r="C451" s="16"/>
+      <c r="C451" s="15"/>
       <c r="D451" s="5"/>
       <c r="E451" s="6"/>
       <c r="F451" s="7"/>
@@ -10084,7 +10120,7 @@
     <row r="452" spans="1:18">
       <c r="A452" s="8"/>
       <c r="B452" s="10"/>
-      <c r="C452" s="16"/>
+      <c r="C452" s="15"/>
       <c r="D452" s="5"/>
       <c r="E452" s="6"/>
       <c r="F452" s="7"/>
@@ -10104,7 +10140,7 @@
     <row r="453" spans="1:18">
       <c r="A453" s="8"/>
       <c r="B453" s="10"/>
-      <c r="C453" s="16"/>
+      <c r="C453" s="15"/>
       <c r="D453" s="5"/>
       <c r="E453" s="6"/>
       <c r="F453" s="7"/>
@@ -10124,7 +10160,7 @@
     <row r="454" spans="1:18">
       <c r="A454" s="8"/>
       <c r="B454" s="10"/>
-      <c r="C454" s="16"/>
+      <c r="C454" s="15"/>
       <c r="D454" s="5"/>
       <c r="E454" s="6"/>
       <c r="F454" s="7"/>
@@ -10144,7 +10180,7 @@
     <row r="455" spans="1:18">
       <c r="A455" s="8"/>
       <c r="B455" s="10"/>
-      <c r="C455" s="16"/>
+      <c r="C455" s="15"/>
       <c r="D455" s="5"/>
       <c r="E455" s="6"/>
       <c r="F455" s="7"/>
@@ -10164,7 +10200,7 @@
     <row r="456" spans="1:18">
       <c r="A456" s="8"/>
       <c r="B456" s="10"/>
-      <c r="C456" s="16"/>
+      <c r="C456" s="15"/>
       <c r="D456" s="5"/>
       <c r="E456" s="6"/>
       <c r="F456" s="7"/>
@@ -10184,7 +10220,7 @@
     <row r="457" spans="1:18">
       <c r="A457" s="8"/>
       <c r="B457" s="10"/>
-      <c r="C457" s="16"/>
+      <c r="C457" s="15"/>
       <c r="D457" s="5"/>
       <c r="E457" s="6"/>
       <c r="F457" s="7"/>
@@ -10204,7 +10240,7 @@
     <row r="458" spans="1:18">
       <c r="A458" s="8"/>
       <c r="B458" s="10"/>
-      <c r="C458" s="16"/>
+      <c r="C458" s="15"/>
       <c r="D458" s="5"/>
       <c r="E458" s="6"/>
       <c r="F458" s="7"/>
@@ -10224,7 +10260,7 @@
     <row r="459" spans="1:18">
       <c r="A459" s="8"/>
       <c r="B459" s="10"/>
-      <c r="C459" s="16"/>
+      <c r="C459" s="15"/>
       <c r="D459" s="5"/>
       <c r="E459" s="6"/>
       <c r="F459" s="7"/>
@@ -10244,7 +10280,7 @@
     <row r="460" spans="1:18">
       <c r="A460" s="8"/>
       <c r="B460" s="10"/>
-      <c r="C460" s="16"/>
+      <c r="C460" s="15"/>
       <c r="D460" s="5"/>
       <c r="E460" s="6"/>
       <c r="F460" s="7"/>
@@ -10264,7 +10300,7 @@
     <row r="461" spans="1:18">
       <c r="A461" s="8"/>
       <c r="B461" s="10"/>
-      <c r="C461" s="16"/>
+      <c r="C461" s="15"/>
       <c r="D461" s="5"/>
       <c r="E461" s="6"/>
       <c r="F461" s="7"/>
@@ -10284,7 +10320,7 @@
     <row r="462" spans="1:18">
       <c r="A462" s="8"/>
       <c r="B462" s="10"/>
-      <c r="C462" s="16"/>
+      <c r="C462" s="15"/>
       <c r="D462" s="5"/>
       <c r="E462" s="6"/>
       <c r="F462" s="7"/>
@@ -10304,7 +10340,7 @@
     <row r="463" spans="1:18">
       <c r="A463" s="8"/>
       <c r="B463" s="10"/>
-      <c r="C463" s="16"/>
+      <c r="C463" s="15"/>
       <c r="D463" s="5"/>
       <c r="E463" s="6"/>
       <c r="F463" s="7"/>
@@ -10324,7 +10360,7 @@
     <row r="464" spans="1:18">
       <c r="A464" s="8"/>
       <c r="B464" s="10"/>
-      <c r="C464" s="16"/>
+      <c r="C464" s="15"/>
       <c r="D464" s="5"/>
       <c r="E464" s="6"/>
       <c r="F464" s="7"/>
@@ -10344,7 +10380,7 @@
     <row r="465" spans="1:18">
       <c r="A465" s="8"/>
       <c r="B465" s="10"/>
-      <c r="C465" s="16"/>
+      <c r="C465" s="15"/>
       <c r="D465" s="5"/>
       <c r="E465" s="6"/>
       <c r="F465" s="7"/>
@@ -10364,7 +10400,7 @@
     <row r="466" spans="1:18">
       <c r="A466" s="8"/>
       <c r="B466" s="10"/>
-      <c r="C466" s="16"/>
+      <c r="C466" s="15"/>
       <c r="D466" s="5"/>
       <c r="E466" s="6"/>
       <c r="F466" s="7"/>
@@ -10384,7 +10420,7 @@
     <row r="467" spans="1:18">
       <c r="A467" s="8"/>
       <c r="B467" s="10"/>
-      <c r="C467" s="16"/>
+      <c r="C467" s="15"/>
       <c r="D467" s="5"/>
       <c r="E467" s="6"/>
       <c r="F467" s="7"/>
@@ -10404,7 +10440,7 @@
     <row r="468" spans="1:18">
       <c r="A468" s="8"/>
       <c r="B468" s="10"/>
-      <c r="C468" s="16"/>
+      <c r="C468" s="15"/>
       <c r="D468" s="5"/>
       <c r="E468" s="6"/>
       <c r="F468" s="7"/>
@@ -10424,7 +10460,7 @@
     <row r="469" spans="1:18">
       <c r="A469" s="8"/>
       <c r="B469" s="10"/>
-      <c r="C469" s="16"/>
+      <c r="C469" s="15"/>
       <c r="D469" s="5"/>
       <c r="E469" s="6"/>
       <c r="F469" s="7"/>
@@ -10444,7 +10480,7 @@
     <row r="470" spans="1:18">
       <c r="A470" s="8"/>
       <c r="B470" s="10"/>
-      <c r="C470" s="16"/>
+      <c r="C470" s="15"/>
       <c r="D470" s="5"/>
       <c r="E470" s="6"/>
       <c r="F470" s="7"/>
@@ -10464,7 +10500,7 @@
     <row r="471" spans="1:18">
       <c r="A471" s="8"/>
       <c r="B471" s="10"/>
-      <c r="C471" s="16"/>
+      <c r="C471" s="15"/>
       <c r="D471" s="5"/>
       <c r="E471" s="6"/>
       <c r="F471" s="7"/>
@@ -10484,7 +10520,7 @@
     <row r="472" spans="1:18">
       <c r="A472" s="8"/>
       <c r="B472" s="10"/>
-      <c r="C472" s="16"/>
+      <c r="C472" s="15"/>
       <c r="D472" s="5"/>
       <c r="E472" s="6"/>
       <c r="F472" s="7"/>
@@ -10504,7 +10540,7 @@
     <row r="473" spans="1:18">
       <c r="A473" s="8"/>
       <c r="B473" s="10"/>
-      <c r="C473" s="16"/>
+      <c r="C473" s="15"/>
       <c r="D473" s="5"/>
       <c r="E473" s="6"/>
       <c r="F473" s="7"/>
@@ -10524,7 +10560,7 @@
     <row r="474" spans="1:18">
       <c r="A474" s="8"/>
       <c r="B474" s="10"/>
-      <c r="C474" s="16"/>
+      <c r="C474" s="15"/>
       <c r="D474" s="5"/>
       <c r="E474" s="6"/>
       <c r="F474" s="7"/>
@@ -10544,7 +10580,7 @@
     <row r="475" spans="1:18">
       <c r="A475" s="8"/>
       <c r="B475" s="10"/>
-      <c r="C475" s="16"/>
+      <c r="C475" s="15"/>
       <c r="D475" s="5"/>
       <c r="E475" s="6"/>
       <c r="F475" s="7"/>
@@ -10564,7 +10600,7 @@
     <row r="476" spans="1:18">
       <c r="A476" s="8"/>
       <c r="B476" s="10"/>
-      <c r="C476" s="16"/>
+      <c r="C476" s="15"/>
       <c r="D476" s="5"/>
       <c r="E476" s="6"/>
       <c r="F476" s="7"/>
@@ -10584,7 +10620,7 @@
     <row r="477" spans="1:18">
       <c r="A477" s="8"/>
       <c r="B477" s="10"/>
-      <c r="C477" s="16"/>
+      <c r="C477" s="15"/>
       <c r="D477" s="5"/>
       <c r="E477" s="6"/>
       <c r="F477" s="7"/>
@@ -10604,7 +10640,7 @@
     <row r="478" spans="1:18">
       <c r="A478" s="8"/>
       <c r="B478" s="10"/>
-      <c r="C478" s="16"/>
+      <c r="C478" s="15"/>
       <c r="D478" s="5"/>
       <c r="E478" s="6"/>
       <c r="F478" s="7"/>
@@ -10624,7 +10660,7 @@
     <row r="479" spans="1:18">
       <c r="A479" s="8"/>
       <c r="B479" s="10"/>
-      <c r="C479" s="16"/>
+      <c r="C479" s="15"/>
       <c r="D479" s="5"/>
       <c r="E479" s="6"/>
       <c r="F479" s="7"/>
@@ -10644,7 +10680,7 @@
     <row r="480" spans="1:18">
       <c r="A480" s="8"/>
       <c r="B480" s="10"/>
-      <c r="C480" s="16"/>
+      <c r="C480" s="15"/>
       <c r="D480" s="5"/>
       <c r="E480" s="6"/>
       <c r="F480" s="7"/>
@@ -10664,7 +10700,7 @@
     <row r="481" spans="1:18">
       <c r="A481" s="8"/>
       <c r="B481" s="10"/>
-      <c r="C481" s="16"/>
+      <c r="C481" s="15"/>
       <c r="D481" s="5"/>
       <c r="E481" s="6"/>
       <c r="F481" s="7"/>
@@ -10684,7 +10720,7 @@
     <row r="482" spans="1:18">
       <c r="A482" s="8"/>
       <c r="B482" s="10"/>
-      <c r="C482" s="16"/>
+      <c r="C482" s="15"/>
       <c r="D482" s="5"/>
       <c r="E482" s="6"/>
       <c r="F482" s="7"/>
@@ -10704,7 +10740,7 @@
     <row r="483" spans="1:18">
       <c r="A483" s="8"/>
       <c r="B483" s="10"/>
-      <c r="C483" s="16"/>
+      <c r="C483" s="15"/>
       <c r="D483" s="5"/>
       <c r="E483" s="6"/>
       <c r="F483" s="7"/>
@@ -10724,7 +10760,7 @@
     <row r="484" spans="1:18">
       <c r="A484" s="8"/>
       <c r="B484" s="10"/>
-      <c r="C484" s="16"/>
+      <c r="C484" s="15"/>
       <c r="D484" s="5"/>
       <c r="E484" s="6"/>
       <c r="F484" s="7"/>
@@ -10744,7 +10780,7 @@
     <row r="485" spans="1:18">
       <c r="A485" s="8"/>
       <c r="B485" s="10"/>
-      <c r="C485" s="16"/>
+      <c r="C485" s="15"/>
       <c r="D485" s="5"/>
       <c r="E485" s="6"/>
       <c r="F485" s="7"/>
@@ -10764,7 +10800,7 @@
     <row r="486" spans="1:18">
       <c r="A486" s="8"/>
       <c r="B486" s="10"/>
-      <c r="C486" s="16"/>
+      <c r="C486" s="15"/>
       <c r="D486" s="5"/>
       <c r="E486" s="6"/>
       <c r="F486" s="7"/>
@@ -10784,7 +10820,7 @@
     <row r="487" spans="1:18">
       <c r="A487" s="8"/>
       <c r="B487" s="10"/>
-      <c r="C487" s="16"/>
+      <c r="C487" s="15"/>
       <c r="D487" s="5"/>
       <c r="E487" s="6"/>
       <c r="F487" s="7"/>
@@ -10804,7 +10840,7 @@
     <row r="488" spans="1:18">
       <c r="A488" s="8"/>
       <c r="B488" s="10"/>
-      <c r="C488" s="16"/>
+      <c r="C488" s="15"/>
       <c r="D488" s="5"/>
       <c r="E488" s="6"/>
       <c r="F488" s="7"/>
@@ -10824,7 +10860,7 @@
     <row r="489" spans="1:18">
       <c r="A489" s="8"/>
       <c r="B489" s="10"/>
-      <c r="C489" s="16"/>
+      <c r="C489" s="15"/>
       <c r="D489" s="5"/>
       <c r="E489" s="6"/>
       <c r="F489" s="7"/>
@@ -10844,7 +10880,7 @@
     <row r="490" spans="1:18">
       <c r="A490" s="8"/>
       <c r="B490" s="10"/>
-      <c r="C490" s="16"/>
+      <c r="C490" s="15"/>
       <c r="D490" s="5"/>
       <c r="E490" s="6"/>
       <c r="F490" s="7"/>
@@ -10864,7 +10900,7 @@
     <row r="491" spans="1:18">
       <c r="A491" s="8"/>
       <c r="B491" s="10"/>
-      <c r="C491" s="16"/>
+      <c r="C491" s="15"/>
       <c r="D491" s="5"/>
       <c r="E491" s="6"/>
       <c r="F491" s="7"/>
@@ -10884,7 +10920,7 @@
     <row r="492" spans="1:18">
       <c r="A492" s="8"/>
       <c r="B492" s="10"/>
-      <c r="C492" s="16"/>
+      <c r="C492" s="15"/>
       <c r="D492" s="5"/>
       <c r="E492" s="6"/>
       <c r="F492" s="7"/>
@@ -10904,7 +10940,7 @@
     <row r="493" spans="1:18">
       <c r="A493" s="8"/>
       <c r="B493" s="10"/>
-      <c r="C493" s="16"/>
+      <c r="C493" s="15"/>
       <c r="D493" s="5"/>
       <c r="E493" s="6"/>
       <c r="F493" s="7"/>
@@ -10924,7 +10960,7 @@
     <row r="494" spans="1:18">
       <c r="A494" s="8"/>
       <c r="B494" s="10"/>
-      <c r="C494" s="16"/>
+      <c r="C494" s="15"/>
       <c r="D494" s="5"/>
       <c r="E494" s="6"/>
       <c r="F494" s="7"/>
@@ -10944,7 +10980,7 @@
     <row r="495" spans="1:18">
       <c r="A495" s="8"/>
       <c r="B495" s="10"/>
-      <c r="C495" s="16"/>
+      <c r="C495" s="15"/>
       <c r="D495" s="5"/>
       <c r="E495" s="6"/>
       <c r="F495" s="7"/>
@@ -10964,7 +11000,7 @@
     <row r="496" spans="1:18">
       <c r="A496" s="8"/>
       <c r="B496" s="10"/>
-      <c r="C496" s="16"/>
+      <c r="C496" s="15"/>
       <c r="D496" s="5"/>
       <c r="E496" s="6"/>
       <c r="F496" s="7"/>
@@ -10984,7 +11020,7 @@
     <row r="497" spans="1:18">
       <c r="A497" s="8"/>
       <c r="B497" s="10"/>
-      <c r="C497" s="16"/>
+      <c r="C497" s="15"/>
       <c r="D497" s="5"/>
       <c r="E497" s="6"/>
       <c r="F497" s="7"/>
@@ -11004,7 +11040,7 @@
     <row r="498" spans="1:18">
       <c r="A498" s="8"/>
       <c r="B498" s="10"/>
-      <c r="C498" s="16"/>
+      <c r="C498" s="15"/>
       <c r="D498" s="5"/>
       <c r="E498" s="6"/>
       <c r="F498" s="7"/>
@@ -11024,7 +11060,7 @@
     <row r="499" spans="1:18">
       <c r="A499" s="8"/>
       <c r="B499" s="10"/>
-      <c r="C499" s="16"/>
+      <c r="C499" s="15"/>
       <c r="D499" s="5"/>
       <c r="E499" s="6"/>
       <c r="F499" s="7"/>
@@ -11044,7 +11080,7 @@
     <row r="500" spans="1:18">
       <c r="A500" s="8"/>
       <c r="B500" s="10"/>
-      <c r="C500" s="16"/>
+      <c r="C500" s="15"/>
       <c r="D500" s="5"/>
       <c r="E500" s="6"/>
       <c r="F500" s="7"/>
@@ -12148,67 +12184,67 @@
     <row r="17" spans="1:16">
       <c r="A17" s="10" t="str">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!B17)</f>
-        <v/>
+        <v>HSB</v>
       </c>
       <c r="B17" s="10" t="str">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!C17)</f>
-        <v/>
+        <v>HP1045</v>
       </c>
       <c r="C17" s="5" t="str">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!D17)</f>
-        <v/>
-      </c>
-      <c r="D17" s="11" t="str">
+        <v>Колодки тормозные передние</v>
+      </c>
+      <c r="D17" s="11">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!E17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!F17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!G17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="12" t="str">
+        <v>4000</v>
+      </c>
+      <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H17" s="13" t="str">
+        <v>4000</v>
+      </c>
+      <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I17" s="12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I17" s="12">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J17" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K17" s="12" t="str">
+        <v>4000</v>
+      </c>
+      <c r="K17" s="12">
         <f t="shared" si="4"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!M17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="10" t="str">
+        <v>Да</v>
+      </c>
+      <c r="M17" s="10">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!N17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="10" t="str">
+        <v>173207490</v>
+      </c>
+      <c r="N17" s="10">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!O17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!P17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
         <f>IF(Инвентаризация!C17="","",Инвентаризация!Q17)</f>
-        <v/>
+        <v>46242</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -44106,12 +44142,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="1" t="s">
@@ -44133,7 +44169,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Инвентаризация!C2:C500,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -44149,14 +44185,14 @@
       </c>
       <c r="B5">
         <f>SUM(Инвентаризация!E2:E500)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
         <f>COUNTIFS(Инвентаризация!E2:E500,"&gt;=1",Инвентаризация!E2:E500,"&lt;=2")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -44181,7 +44217,7 @@
       </c>
       <c r="B7" s="4">
         <f>SUMPRODUCT(Инвентаризация!E2:E500,Инвентаризация!G2:G500)</f>
-        <v>157800</v>
+        <v>161800</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
@@ -44197,7 +44233,7 @@
       </c>
       <c r="B8" s="4">
         <f>B7-B6</f>
-        <v>157800</v>
+        <v>161800</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -44206,7 +44242,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -44223,7 +44259,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Инвентаризация!H2:H500,"Да")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -44232,7 +44268,7 @@
       </c>
       <c r="B13">
         <f>COUNTIF(Инвентаризация!I2:I500,"Да")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -44241,7 +44277,7 @@
       </c>
       <c r="B14">
         <f>COUNTIF(Инвентаризация!J2:J500,"Да")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -44250,7 +44286,7 @@
       </c>
       <c r="B15">
         <f>COUNTIF(Инвентаризация!K2:K500,"Да")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -44259,7 +44295,7 @@
       </c>
       <c r="B16">
         <f>COUNTIF(Инвентаризация!L2:L500,"Да")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -44268,7 +44304,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF(Инвентаризация!M2:M500,"Да")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
